--- a/committee_minutes_template.xlsx
+++ b/committee_minutes_template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nissinkohgyo-my.sharepoint.com/personal/yutaka_takahagi_nissinkohgyo_co_jp/Documents/安全管理室/作業用/Cursor_作業box/03_安全衛生管理ｼｽﾃﾑ/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="21" documentId="13_ncr:1_{DA037F8E-7987-4536-B79C-52337214A8C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{07A02FC8-20F8-4301-B412-825FD947C9A0}"/>
+  <xr:revisionPtr revIDLastSave="26" documentId="13_ncr:1_{DA037F8E-7987-4536-B79C-52337214A8C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{164AAF50-E3FE-4453-8184-5AA14CF75CD4}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="18720" xr2:uid="{2FA0CB56-C7BA-4D8F-B412-6C8047491E48}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{2FA0CB56-C7BA-4D8F-B412-6C8047491E48}"/>
   </bookViews>
   <sheets>
     <sheet name="議事録" sheetId="1" r:id="rId1"/>
@@ -4416,7 +4416,7 @@
     <numFmt numFmtId="176" formatCode="[$-411]ggge&quot;年&quot;m&quot;月&quot;d&quot;日&quot;;@"/>
     <numFmt numFmtId="177" formatCode="m/d;@"/>
   </numFmts>
-  <fonts count="48">
+  <fonts count="49">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4790,8 +4790,16 @@
       <family val="1"/>
       <charset val="128"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -4801,6 +4809,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5128,12 +5142,6 @@
     <xf numFmtId="20" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -5395,25 +5403,13 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="32" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="32" fontId="4" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" indent="15"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" indent="15"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" indent="15"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -5432,58 +5428,76 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" indent="15"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" indent="15"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" indent="15"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="48" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -7045,47 +7059,47 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="16.149999999999999" customHeight="1">
-      <c r="A1" s="107" t="s">
+      <c r="A1" s="99" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="107"/>
-      <c r="C1" s="107"/>
-      <c r="D1" s="107"/>
-      <c r="E1" s="107"/>
-      <c r="F1" s="107"/>
-      <c r="G1" s="107"/>
-      <c r="H1" s="107"/>
-      <c r="I1" s="107" t="s">
+      <c r="B1" s="99"/>
+      <c r="C1" s="99"/>
+      <c r="D1" s="99"/>
+      <c r="E1" s="99"/>
+      <c r="F1" s="99"/>
+      <c r="G1" s="99"/>
+      <c r="H1" s="99"/>
+      <c r="I1" s="99" t="s">
         <v>0</v>
       </c>
-      <c r="J1" s="107"/>
-      <c r="K1" s="107"/>
-      <c r="L1" s="107"/>
-      <c r="M1" s="107"/>
-      <c r="N1" s="107"/>
-      <c r="O1" s="107"/>
-      <c r="P1" s="107"/>
+      <c r="J1" s="99"/>
+      <c r="K1" s="99"/>
+      <c r="L1" s="99"/>
+      <c r="M1" s="99"/>
+      <c r="N1" s="99"/>
+      <c r="O1" s="99"/>
+      <c r="P1" s="99"/>
     </row>
     <row r="2" spans="1:16" ht="16.149999999999999" customHeight="1" thickBot="1">
-      <c r="A2" s="107"/>
-      <c r="B2" s="107"/>
-      <c r="C2" s="107"/>
-      <c r="D2" s="107"/>
-      <c r="E2" s="107"/>
-      <c r="F2" s="107"/>
-      <c r="G2" s="107"/>
-      <c r="H2" s="107"/>
-      <c r="I2" s="107"/>
-      <c r="J2" s="107"/>
-      <c r="K2" s="107"/>
-      <c r="L2" s="107"/>
-      <c r="M2" s="107"/>
-      <c r="N2" s="107"/>
-      <c r="O2" s="107"/>
-      <c r="P2" s="107"/>
+      <c r="A2" s="99"/>
+      <c r="B2" s="99"/>
+      <c r="C2" s="99"/>
+      <c r="D2" s="99"/>
+      <c r="E2" s="99"/>
+      <c r="F2" s="99"/>
+      <c r="G2" s="99"/>
+      <c r="H2" s="99"/>
+      <c r="I2" s="99"/>
+      <c r="J2" s="99"/>
+      <c r="K2" s="99"/>
+      <c r="L2" s="99"/>
+      <c r="M2" s="99"/>
+      <c r="N2" s="99"/>
+      <c r="O2" s="99"/>
+      <c r="P2" s="99"/>
     </row>
     <row r="3" spans="1:16" ht="16.149999999999999" customHeight="1">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="128" t="s">
         <v>1</v>
       </c>
       <c r="B3" s="7"/>
@@ -7094,14 +7108,14 @@
         <v>2</v>
       </c>
       <c r="E3" s="10"/>
-      <c r="F3" s="11" t="s">
+      <c r="F3" s="130" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="101" t="s">
+      <c r="G3" s="100" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="102"/>
-      <c r="I3" s="12" t="s">
+      <c r="H3" s="101"/>
+      <c r="I3" s="128" t="s">
         <v>1</v>
       </c>
       <c r="J3" s="7"/>
@@ -7110,1195 +7124,1213 @@
         <v>2</v>
       </c>
       <c r="M3" s="10"/>
-      <c r="N3" s="11" t="s">
+      <c r="N3" s="130" t="s">
         <v>3</v>
       </c>
-      <c r="O3" s="101" t="s">
+      <c r="O3" s="100" t="s">
         <v>4</v>
       </c>
-      <c r="P3" s="102"/>
+      <c r="P3" s="101"/>
     </row>
     <row r="4" spans="1:16" ht="16.149999999999999" customHeight="1">
-      <c r="A4" s="103" t="s">
+      <c r="A4" s="129" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="113"/>
-      <c r="C4" s="114"/>
-      <c r="D4" s="114"/>
-      <c r="E4" s="114"/>
-      <c r="F4" s="114"/>
-      <c r="G4" s="114"/>
-      <c r="H4" s="115"/>
-      <c r="I4" s="103" t="s">
+      <c r="B4" s="107"/>
+      <c r="C4" s="108"/>
+      <c r="D4" s="108"/>
+      <c r="E4" s="108"/>
+      <c r="F4" s="108"/>
+      <c r="G4" s="108"/>
+      <c r="H4" s="109"/>
+      <c r="I4" s="129" t="s">
         <v>5</v>
       </c>
-      <c r="J4" s="113"/>
-      <c r="K4" s="114"/>
-      <c r="L4" s="114"/>
-      <c r="M4" s="114"/>
-      <c r="N4" s="114"/>
-      <c r="O4" s="114"/>
-      <c r="P4" s="115"/>
+      <c r="J4" s="107"/>
+      <c r="K4" s="108"/>
+      <c r="L4" s="108"/>
+      <c r="M4" s="108"/>
+      <c r="N4" s="108"/>
+      <c r="O4" s="108"/>
+      <c r="P4" s="109"/>
     </row>
     <row r="5" spans="1:16" ht="16.149999999999999" customHeight="1">
-      <c r="A5" s="103"/>
-      <c r="B5" s="116"/>
-      <c r="C5" s="117"/>
-      <c r="D5" s="117"/>
-      <c r="E5" s="117"/>
-      <c r="F5" s="117"/>
-      <c r="G5" s="117"/>
-      <c r="H5" s="118"/>
-      <c r="I5" s="103"/>
-      <c r="J5" s="116"/>
-      <c r="K5" s="117"/>
-      <c r="L5" s="117"/>
-      <c r="M5" s="117"/>
-      <c r="N5" s="117"/>
-      <c r="O5" s="117"/>
-      <c r="P5" s="118"/>
+      <c r="A5" s="129"/>
+      <c r="B5" s="110"/>
+      <c r="C5" s="111"/>
+      <c r="D5" s="111"/>
+      <c r="E5" s="111"/>
+      <c r="F5" s="111"/>
+      <c r="G5" s="111"/>
+      <c r="H5" s="112"/>
+      <c r="I5" s="129"/>
+      <c r="J5" s="110"/>
+      <c r="K5" s="111"/>
+      <c r="L5" s="111"/>
+      <c r="M5" s="111"/>
+      <c r="N5" s="111"/>
+      <c r="O5" s="111"/>
+      <c r="P5" s="112"/>
     </row>
     <row r="6" spans="1:16" ht="16.149999999999999" customHeight="1">
-      <c r="A6" s="103"/>
-      <c r="B6" s="116"/>
-      <c r="C6" s="117"/>
-      <c r="D6" s="117"/>
-      <c r="E6" s="117"/>
-      <c r="F6" s="117"/>
-      <c r="G6" s="117"/>
-      <c r="H6" s="118"/>
-      <c r="I6" s="103"/>
-      <c r="J6" s="116"/>
-      <c r="K6" s="117"/>
-      <c r="L6" s="117"/>
-      <c r="M6" s="117"/>
-      <c r="N6" s="117"/>
-      <c r="O6" s="117"/>
-      <c r="P6" s="118"/>
+      <c r="A6" s="129"/>
+      <c r="B6" s="110"/>
+      <c r="C6" s="111"/>
+      <c r="D6" s="111"/>
+      <c r="E6" s="111"/>
+      <c r="F6" s="111"/>
+      <c r="G6" s="111"/>
+      <c r="H6" s="112"/>
+      <c r="I6" s="129"/>
+      <c r="J6" s="110"/>
+      <c r="K6" s="111"/>
+      <c r="L6" s="111"/>
+      <c r="M6" s="111"/>
+      <c r="N6" s="111"/>
+      <c r="O6" s="111"/>
+      <c r="P6" s="112"/>
     </row>
     <row r="7" spans="1:16" ht="16.149999999999999" customHeight="1">
-      <c r="A7" s="103"/>
-      <c r="B7" s="119"/>
-      <c r="C7" s="120"/>
-      <c r="D7" s="120"/>
-      <c r="E7" s="120"/>
-      <c r="F7" s="120"/>
-      <c r="G7" s="120"/>
-      <c r="H7" s="121"/>
-      <c r="I7" s="103"/>
-      <c r="J7" s="119"/>
-      <c r="K7" s="120"/>
-      <c r="L7" s="120"/>
-      <c r="M7" s="120"/>
-      <c r="N7" s="120"/>
-      <c r="O7" s="120"/>
-      <c r="P7" s="121"/>
+      <c r="A7" s="129"/>
+      <c r="B7" s="113"/>
+      <c r="C7" s="114"/>
+      <c r="D7" s="114"/>
+      <c r="E7" s="114"/>
+      <c r="F7" s="114"/>
+      <c r="G7" s="114"/>
+      <c r="H7" s="115"/>
+      <c r="I7" s="129"/>
+      <c r="J7" s="113"/>
+      <c r="K7" s="114"/>
+      <c r="L7" s="114"/>
+      <c r="M7" s="114"/>
+      <c r="N7" s="114"/>
+      <c r="O7" s="114"/>
+      <c r="P7" s="115"/>
     </row>
     <row r="8" spans="1:16" ht="16.149999999999999" customHeight="1">
-      <c r="A8" s="103" t="s">
+      <c r="A8" s="129" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="113"/>
-      <c r="C8" s="114"/>
-      <c r="D8" s="114"/>
-      <c r="E8" s="114"/>
-      <c r="F8" s="114"/>
-      <c r="G8" s="114"/>
-      <c r="H8" s="115"/>
-      <c r="I8" s="103" t="s">
+      <c r="B8" s="107"/>
+      <c r="C8" s="108"/>
+      <c r="D8" s="108"/>
+      <c r="E8" s="108"/>
+      <c r="F8" s="108"/>
+      <c r="G8" s="108"/>
+      <c r="H8" s="109"/>
+      <c r="I8" s="129" t="s">
         <v>6</v>
       </c>
-      <c r="J8" s="113"/>
-      <c r="K8" s="114"/>
-      <c r="L8" s="114"/>
-      <c r="M8" s="114"/>
-      <c r="N8" s="114"/>
-      <c r="O8" s="114"/>
-      <c r="P8" s="115"/>
+      <c r="J8" s="107"/>
+      <c r="K8" s="108"/>
+      <c r="L8" s="108"/>
+      <c r="M8" s="108"/>
+      <c r="N8" s="108"/>
+      <c r="O8" s="108"/>
+      <c r="P8" s="109"/>
     </row>
     <row r="9" spans="1:16" ht="16.149999999999999" customHeight="1">
-      <c r="A9" s="103"/>
-      <c r="B9" s="116"/>
-      <c r="C9" s="117"/>
-      <c r="D9" s="117"/>
-      <c r="E9" s="117"/>
-      <c r="F9" s="117"/>
-      <c r="G9" s="117"/>
-      <c r="H9" s="118"/>
-      <c r="I9" s="103"/>
-      <c r="J9" s="116"/>
-      <c r="K9" s="117"/>
-      <c r="L9" s="117"/>
-      <c r="M9" s="117"/>
-      <c r="N9" s="117"/>
-      <c r="O9" s="117"/>
-      <c r="P9" s="118"/>
+      <c r="A9" s="129"/>
+      <c r="B9" s="110"/>
+      <c r="C9" s="111"/>
+      <c r="D9" s="111"/>
+      <c r="E9" s="111"/>
+      <c r="F9" s="111"/>
+      <c r="G9" s="111"/>
+      <c r="H9" s="112"/>
+      <c r="I9" s="129"/>
+      <c r="J9" s="110"/>
+      <c r="K9" s="111"/>
+      <c r="L9" s="111"/>
+      <c r="M9" s="111"/>
+      <c r="N9" s="111"/>
+      <c r="O9" s="111"/>
+      <c r="P9" s="112"/>
     </row>
     <row r="10" spans="1:16" ht="16.149999999999999" customHeight="1">
-      <c r="A10" s="103"/>
-      <c r="B10" s="119"/>
-      <c r="C10" s="120"/>
-      <c r="D10" s="120"/>
-      <c r="E10" s="120"/>
-      <c r="F10" s="120"/>
-      <c r="G10" s="120"/>
-      <c r="H10" s="121"/>
-      <c r="I10" s="103"/>
-      <c r="J10" s="119"/>
-      <c r="K10" s="120"/>
-      <c r="L10" s="120"/>
-      <c r="M10" s="120"/>
-      <c r="N10" s="120"/>
-      <c r="O10" s="120"/>
-      <c r="P10" s="121"/>
+      <c r="A10" s="129"/>
+      <c r="B10" s="113"/>
+      <c r="C10" s="114"/>
+      <c r="D10" s="114"/>
+      <c r="E10" s="114"/>
+      <c r="F10" s="114"/>
+      <c r="G10" s="114"/>
+      <c r="H10" s="115"/>
+      <c r="I10" s="129"/>
+      <c r="J10" s="113"/>
+      <c r="K10" s="114"/>
+      <c r="L10" s="114"/>
+      <c r="M10" s="114"/>
+      <c r="N10" s="114"/>
+      <c r="O10" s="114"/>
+      <c r="P10" s="115"/>
     </row>
     <row r="11" spans="1:16" ht="16.149999999999999" customHeight="1">
-      <c r="A11" s="103" t="s">
+      <c r="A11" s="129" t="s">
         <v>371</v>
       </c>
-      <c r="B11" s="113"/>
-      <c r="C11" s="114"/>
-      <c r="D11" s="114"/>
-      <c r="E11" s="114"/>
-      <c r="F11" s="114"/>
-      <c r="G11" s="114"/>
-      <c r="H11" s="115"/>
-      <c r="I11" s="103" t="s">
+      <c r="B11" s="107"/>
+      <c r="C11" s="108"/>
+      <c r="D11" s="108"/>
+      <c r="E11" s="108"/>
+      <c r="F11" s="108"/>
+      <c r="G11" s="108"/>
+      <c r="H11" s="109"/>
+      <c r="I11" s="129" t="s">
         <v>371</v>
       </c>
-      <c r="J11" s="113"/>
-      <c r="K11" s="114"/>
-      <c r="L11" s="114"/>
-      <c r="M11" s="114"/>
-      <c r="N11" s="114"/>
-      <c r="O11" s="114"/>
-      <c r="P11" s="115"/>
+      <c r="J11" s="107"/>
+      <c r="K11" s="108"/>
+      <c r="L11" s="108"/>
+      <c r="M11" s="108"/>
+      <c r="N11" s="108"/>
+      <c r="O11" s="108"/>
+      <c r="P11" s="109"/>
     </row>
     <row r="12" spans="1:16" ht="16.149999999999999" customHeight="1">
-      <c r="A12" s="103"/>
-      <c r="B12" s="116"/>
-      <c r="C12" s="117"/>
-      <c r="D12" s="117"/>
-      <c r="E12" s="117"/>
-      <c r="F12" s="117"/>
-      <c r="G12" s="117"/>
-      <c r="H12" s="118"/>
-      <c r="I12" s="103"/>
-      <c r="J12" s="116"/>
-      <c r="K12" s="117"/>
-      <c r="L12" s="117"/>
-      <c r="M12" s="117"/>
-      <c r="N12" s="117"/>
-      <c r="O12" s="117"/>
-      <c r="P12" s="118"/>
+      <c r="A12" s="129"/>
+      <c r="B12" s="110"/>
+      <c r="C12" s="111"/>
+      <c r="D12" s="111"/>
+      <c r="E12" s="111"/>
+      <c r="F12" s="111"/>
+      <c r="G12" s="111"/>
+      <c r="H12" s="112"/>
+      <c r="I12" s="129"/>
+      <c r="J12" s="110"/>
+      <c r="K12" s="111"/>
+      <c r="L12" s="111"/>
+      <c r="M12" s="111"/>
+      <c r="N12" s="111"/>
+      <c r="O12" s="111"/>
+      <c r="P12" s="112"/>
     </row>
     <row r="13" spans="1:16" ht="16.149999999999999" customHeight="1">
-      <c r="A13" s="103"/>
-      <c r="B13" s="119"/>
-      <c r="C13" s="120"/>
-      <c r="D13" s="120"/>
-      <c r="E13" s="120"/>
-      <c r="F13" s="120"/>
-      <c r="G13" s="120"/>
-      <c r="H13" s="121"/>
-      <c r="I13" s="103"/>
-      <c r="J13" s="119"/>
-      <c r="K13" s="120"/>
-      <c r="L13" s="120"/>
-      <c r="M13" s="120"/>
-      <c r="N13" s="120"/>
-      <c r="O13" s="120"/>
-      <c r="P13" s="121"/>
+      <c r="A13" s="129"/>
+      <c r="B13" s="113"/>
+      <c r="C13" s="114"/>
+      <c r="D13" s="114"/>
+      <c r="E13" s="114"/>
+      <c r="F13" s="114"/>
+      <c r="G13" s="114"/>
+      <c r="H13" s="115"/>
+      <c r="I13" s="129"/>
+      <c r="J13" s="113"/>
+      <c r="K13" s="114"/>
+      <c r="L13" s="114"/>
+      <c r="M13" s="114"/>
+      <c r="N13" s="114"/>
+      <c r="O13" s="114"/>
+      <c r="P13" s="115"/>
     </row>
     <row r="14" spans="1:16" ht="16.149999999999999" customHeight="1" thickBot="1">
-      <c r="A14" s="104" t="s">
+      <c r="A14" s="125" t="s">
         <v>372</v>
       </c>
-      <c r="B14" s="105"/>
-      <c r="C14" s="105"/>
-      <c r="D14" s="105"/>
-      <c r="E14" s="105"/>
-      <c r="F14" s="105"/>
-      <c r="G14" s="105"/>
-      <c r="H14" s="106"/>
-      <c r="I14" s="104" t="s">
+      <c r="B14" s="126"/>
+      <c r="C14" s="126"/>
+      <c r="D14" s="126"/>
+      <c r="E14" s="126"/>
+      <c r="F14" s="126"/>
+      <c r="G14" s="126"/>
+      <c r="H14" s="127"/>
+      <c r="I14" s="125" t="s">
         <v>372</v>
       </c>
-      <c r="J14" s="105"/>
-      <c r="K14" s="105"/>
-      <c r="L14" s="105"/>
-      <c r="M14" s="105"/>
-      <c r="N14" s="105"/>
-      <c r="O14" s="105"/>
-      <c r="P14" s="106"/>
+      <c r="J14" s="126"/>
+      <c r="K14" s="126"/>
+      <c r="L14" s="126"/>
+      <c r="M14" s="126"/>
+      <c r="N14" s="126"/>
+      <c r="O14" s="126"/>
+      <c r="P14" s="127"/>
     </row>
     <row r="15" spans="1:16" ht="16.149999999999999" customHeight="1">
-      <c r="A15" s="122"/>
-      <c r="B15" s="123"/>
-      <c r="C15" s="123"/>
-      <c r="D15" s="123"/>
-      <c r="E15" s="123"/>
-      <c r="F15" s="123"/>
-      <c r="G15" s="123"/>
-      <c r="H15" s="124"/>
-      <c r="I15" s="122"/>
-      <c r="J15" s="123"/>
-      <c r="K15" s="123"/>
-      <c r="L15" s="123"/>
-      <c r="M15" s="123"/>
-      <c r="N15" s="123"/>
-      <c r="O15" s="123"/>
-      <c r="P15" s="124"/>
+      <c r="A15" s="116"/>
+      <c r="B15" s="117"/>
+      <c r="C15" s="117"/>
+      <c r="D15" s="117"/>
+      <c r="E15" s="117"/>
+      <c r="F15" s="117"/>
+      <c r="G15" s="117"/>
+      <c r="H15" s="118"/>
+      <c r="I15" s="116"/>
+      <c r="J15" s="117"/>
+      <c r="K15" s="117"/>
+      <c r="L15" s="117"/>
+      <c r="M15" s="117"/>
+      <c r="N15" s="117"/>
+      <c r="O15" s="117"/>
+      <c r="P15" s="118"/>
     </row>
     <row r="16" spans="1:16" ht="16.149999999999999" customHeight="1">
-      <c r="A16" s="125"/>
-      <c r="B16" s="126"/>
-      <c r="C16" s="126"/>
-      <c r="D16" s="126"/>
-      <c r="E16" s="126"/>
-      <c r="F16" s="126"/>
-      <c r="G16" s="126"/>
-      <c r="H16" s="127"/>
-      <c r="I16" s="125"/>
-      <c r="J16" s="126"/>
-      <c r="K16" s="126"/>
-      <c r="L16" s="126"/>
-      <c r="M16" s="126"/>
-      <c r="N16" s="126"/>
-      <c r="O16" s="126"/>
-      <c r="P16" s="127"/>
+      <c r="A16" s="119"/>
+      <c r="B16" s="120"/>
+      <c r="C16" s="120"/>
+      <c r="D16" s="120"/>
+      <c r="E16" s="120"/>
+      <c r="F16" s="120"/>
+      <c r="G16" s="120"/>
+      <c r="H16" s="121"/>
+      <c r="I16" s="119"/>
+      <c r="J16" s="120"/>
+      <c r="K16" s="120"/>
+      <c r="L16" s="120"/>
+      <c r="M16" s="120"/>
+      <c r="N16" s="120"/>
+      <c r="O16" s="120"/>
+      <c r="P16" s="121"/>
     </row>
     <row r="17" spans="1:18" ht="16.149999999999999" customHeight="1">
-      <c r="A17" s="125"/>
-      <c r="B17" s="126"/>
-      <c r="C17" s="126"/>
-      <c r="D17" s="126"/>
-      <c r="E17" s="126"/>
-      <c r="F17" s="126"/>
-      <c r="G17" s="126"/>
-      <c r="H17" s="127"/>
-      <c r="I17" s="125"/>
-      <c r="J17" s="126"/>
-      <c r="K17" s="126"/>
-      <c r="L17" s="126"/>
-      <c r="M17" s="126"/>
-      <c r="N17" s="126"/>
-      <c r="O17" s="126"/>
-      <c r="P17" s="127"/>
+      <c r="A17" s="119"/>
+      <c r="B17" s="120"/>
+      <c r="C17" s="120"/>
+      <c r="D17" s="120"/>
+      <c r="E17" s="120"/>
+      <c r="F17" s="120"/>
+      <c r="G17" s="120"/>
+      <c r="H17" s="121"/>
+      <c r="I17" s="119"/>
+      <c r="J17" s="120"/>
+      <c r="K17" s="120"/>
+      <c r="L17" s="120"/>
+      <c r="M17" s="120"/>
+      <c r="N17" s="120"/>
+      <c r="O17" s="120"/>
+      <c r="P17" s="121"/>
     </row>
     <row r="18" spans="1:18" ht="16.149999999999999" customHeight="1">
-      <c r="A18" s="125"/>
-      <c r="B18" s="126"/>
-      <c r="C18" s="126"/>
-      <c r="D18" s="126"/>
-      <c r="E18" s="126"/>
-      <c r="F18" s="126"/>
-      <c r="G18" s="126"/>
-      <c r="H18" s="127"/>
-      <c r="I18" s="125"/>
-      <c r="J18" s="126"/>
-      <c r="K18" s="126"/>
-      <c r="L18" s="126"/>
-      <c r="M18" s="126"/>
-      <c r="N18" s="126"/>
-      <c r="O18" s="126"/>
-      <c r="P18" s="127"/>
+      <c r="A18" s="119"/>
+      <c r="B18" s="120"/>
+      <c r="C18" s="120"/>
+      <c r="D18" s="120"/>
+      <c r="E18" s="120"/>
+      <c r="F18" s="120"/>
+      <c r="G18" s="120"/>
+      <c r="H18" s="121"/>
+      <c r="I18" s="119"/>
+      <c r="J18" s="120"/>
+      <c r="K18" s="120"/>
+      <c r="L18" s="120"/>
+      <c r="M18" s="120"/>
+      <c r="N18" s="120"/>
+      <c r="O18" s="120"/>
+      <c r="P18" s="121"/>
     </row>
     <row r="19" spans="1:18" ht="16.149999999999999" customHeight="1">
-      <c r="A19" s="125"/>
-      <c r="B19" s="126"/>
-      <c r="C19" s="126"/>
-      <c r="D19" s="126"/>
-      <c r="E19" s="126"/>
-      <c r="F19" s="126"/>
-      <c r="G19" s="126"/>
-      <c r="H19" s="127"/>
-      <c r="I19" s="125"/>
-      <c r="J19" s="126"/>
-      <c r="K19" s="126"/>
-      <c r="L19" s="126"/>
-      <c r="M19" s="126"/>
-      <c r="N19" s="126"/>
-      <c r="O19" s="126"/>
-      <c r="P19" s="127"/>
+      <c r="A19" s="119"/>
+      <c r="B19" s="120"/>
+      <c r="C19" s="120"/>
+      <c r="D19" s="120"/>
+      <c r="E19" s="120"/>
+      <c r="F19" s="120"/>
+      <c r="G19" s="120"/>
+      <c r="H19" s="121"/>
+      <c r="I19" s="119"/>
+      <c r="J19" s="120"/>
+      <c r="K19" s="120"/>
+      <c r="L19" s="120"/>
+      <c r="M19" s="120"/>
+      <c r="N19" s="120"/>
+      <c r="O19" s="120"/>
+      <c r="P19" s="121"/>
     </row>
     <row r="20" spans="1:18" ht="16.149999999999999" customHeight="1">
-      <c r="A20" s="125"/>
-      <c r="B20" s="126"/>
-      <c r="C20" s="126"/>
-      <c r="D20" s="126"/>
-      <c r="E20" s="126"/>
-      <c r="F20" s="126"/>
-      <c r="G20" s="126"/>
-      <c r="H20" s="127"/>
-      <c r="I20" s="125"/>
-      <c r="J20" s="126"/>
-      <c r="K20" s="126"/>
-      <c r="L20" s="126"/>
-      <c r="M20" s="126"/>
-      <c r="N20" s="126"/>
-      <c r="O20" s="126"/>
-      <c r="P20" s="127"/>
+      <c r="A20" s="119"/>
+      <c r="B20" s="120"/>
+      <c r="C20" s="120"/>
+      <c r="D20" s="120"/>
+      <c r="E20" s="120"/>
+      <c r="F20" s="120"/>
+      <c r="G20" s="120"/>
+      <c r="H20" s="121"/>
+      <c r="I20" s="119"/>
+      <c r="J20" s="120"/>
+      <c r="K20" s="120"/>
+      <c r="L20" s="120"/>
+      <c r="M20" s="120"/>
+      <c r="N20" s="120"/>
+      <c r="O20" s="120"/>
+      <c r="P20" s="121"/>
     </row>
     <row r="21" spans="1:18" ht="16.149999999999999" customHeight="1">
-      <c r="A21" s="125"/>
-      <c r="B21" s="126"/>
-      <c r="C21" s="126"/>
-      <c r="D21" s="126"/>
-      <c r="E21" s="126"/>
-      <c r="F21" s="126"/>
-      <c r="G21" s="126"/>
-      <c r="H21" s="127"/>
-      <c r="I21" s="125"/>
-      <c r="J21" s="126"/>
-      <c r="K21" s="126"/>
-      <c r="L21" s="126"/>
-      <c r="M21" s="126"/>
-      <c r="N21" s="126"/>
-      <c r="O21" s="126"/>
-      <c r="P21" s="127"/>
+      <c r="A21" s="119"/>
+      <c r="B21" s="120"/>
+      <c r="C21" s="120"/>
+      <c r="D21" s="120"/>
+      <c r="E21" s="120"/>
+      <c r="F21" s="120"/>
+      <c r="G21" s="120"/>
+      <c r="H21" s="121"/>
+      <c r="I21" s="119"/>
+      <c r="J21" s="120"/>
+      <c r="K21" s="120"/>
+      <c r="L21" s="120"/>
+      <c r="M21" s="120"/>
+      <c r="N21" s="120"/>
+      <c r="O21" s="120"/>
+      <c r="P21" s="121"/>
       <c r="Q21" s="2"/>
     </row>
     <row r="22" spans="1:18" ht="16.149999999999999" customHeight="1">
-      <c r="A22" s="125"/>
-      <c r="B22" s="126"/>
-      <c r="C22" s="126"/>
-      <c r="D22" s="126"/>
-      <c r="E22" s="126"/>
-      <c r="F22" s="126"/>
-      <c r="G22" s="126"/>
-      <c r="H22" s="127"/>
-      <c r="I22" s="125"/>
-      <c r="J22" s="126"/>
-      <c r="K22" s="126"/>
-      <c r="L22" s="126"/>
-      <c r="M22" s="126"/>
-      <c r="N22" s="126"/>
-      <c r="O22" s="126"/>
-      <c r="P22" s="127"/>
+      <c r="A22" s="119"/>
+      <c r="B22" s="120"/>
+      <c r="C22" s="120"/>
+      <c r="D22" s="120"/>
+      <c r="E22" s="120"/>
+      <c r="F22" s="120"/>
+      <c r="G22" s="120"/>
+      <c r="H22" s="121"/>
+      <c r="I22" s="119"/>
+      <c r="J22" s="120"/>
+      <c r="K22" s="120"/>
+      <c r="L22" s="120"/>
+      <c r="M22" s="120"/>
+      <c r="N22" s="120"/>
+      <c r="O22" s="120"/>
+      <c r="P22" s="121"/>
     </row>
     <row r="23" spans="1:18" ht="16.149999999999999" customHeight="1">
-      <c r="A23" s="125"/>
-      <c r="B23" s="126"/>
-      <c r="C23" s="126"/>
-      <c r="D23" s="126"/>
-      <c r="E23" s="126"/>
-      <c r="F23" s="126"/>
-      <c r="G23" s="126"/>
-      <c r="H23" s="127"/>
-      <c r="I23" s="125"/>
-      <c r="J23" s="126"/>
-      <c r="K23" s="126"/>
-      <c r="L23" s="126"/>
-      <c r="M23" s="126"/>
-      <c r="N23" s="126"/>
-      <c r="O23" s="126"/>
-      <c r="P23" s="127"/>
+      <c r="A23" s="119"/>
+      <c r="B23" s="120"/>
+      <c r="C23" s="120"/>
+      <c r="D23" s="120"/>
+      <c r="E23" s="120"/>
+      <c r="F23" s="120"/>
+      <c r="G23" s="120"/>
+      <c r="H23" s="121"/>
+      <c r="I23" s="119"/>
+      <c r="J23" s="120"/>
+      <c r="K23" s="120"/>
+      <c r="L23" s="120"/>
+      <c r="M23" s="120"/>
+      <c r="N23" s="120"/>
+      <c r="O23" s="120"/>
+      <c r="P23" s="121"/>
     </row>
     <row r="24" spans="1:18" ht="16.149999999999999" customHeight="1">
-      <c r="A24" s="125"/>
-      <c r="B24" s="126"/>
-      <c r="C24" s="126"/>
-      <c r="D24" s="126"/>
-      <c r="E24" s="126"/>
-      <c r="F24" s="126"/>
-      <c r="G24" s="126"/>
-      <c r="H24" s="127"/>
-      <c r="I24" s="125"/>
-      <c r="J24" s="126"/>
-      <c r="K24" s="126"/>
-      <c r="L24" s="126"/>
-      <c r="M24" s="126"/>
-      <c r="N24" s="126"/>
-      <c r="O24" s="126"/>
-      <c r="P24" s="127"/>
+      <c r="A24" s="119"/>
+      <c r="B24" s="120"/>
+      <c r="C24" s="120"/>
+      <c r="D24" s="120"/>
+      <c r="E24" s="120"/>
+      <c r="F24" s="120"/>
+      <c r="G24" s="120"/>
+      <c r="H24" s="121"/>
+      <c r="I24" s="119"/>
+      <c r="J24" s="120"/>
+      <c r="K24" s="120"/>
+      <c r="L24" s="120"/>
+      <c r="M24" s="120"/>
+      <c r="N24" s="120"/>
+      <c r="O24" s="120"/>
+      <c r="P24" s="121"/>
     </row>
     <row r="25" spans="1:18" ht="16.149999999999999" customHeight="1">
-      <c r="A25" s="125"/>
-      <c r="B25" s="126"/>
-      <c r="C25" s="126"/>
-      <c r="D25" s="126"/>
-      <c r="E25" s="126"/>
-      <c r="F25" s="126"/>
-      <c r="G25" s="126"/>
-      <c r="H25" s="127"/>
-      <c r="I25" s="125"/>
-      <c r="J25" s="126"/>
-      <c r="K25" s="126"/>
-      <c r="L25" s="126"/>
-      <c r="M25" s="126"/>
-      <c r="N25" s="126"/>
-      <c r="O25" s="126"/>
-      <c r="P25" s="127"/>
+      <c r="A25" s="119"/>
+      <c r="B25" s="120"/>
+      <c r="C25" s="120"/>
+      <c r="D25" s="120"/>
+      <c r="E25" s="120"/>
+      <c r="F25" s="120"/>
+      <c r="G25" s="120"/>
+      <c r="H25" s="121"/>
+      <c r="I25" s="119"/>
+      <c r="J25" s="120"/>
+      <c r="K25" s="120"/>
+      <c r="L25" s="120"/>
+      <c r="M25" s="120"/>
+      <c r="N25" s="120"/>
+      <c r="O25" s="120"/>
+      <c r="P25" s="121"/>
     </row>
     <row r="26" spans="1:18" ht="16.149999999999999" customHeight="1">
-      <c r="A26" s="125"/>
-      <c r="B26" s="126"/>
-      <c r="C26" s="126"/>
-      <c r="D26" s="126"/>
-      <c r="E26" s="126"/>
-      <c r="F26" s="126"/>
-      <c r="G26" s="126"/>
-      <c r="H26" s="127"/>
-      <c r="I26" s="125"/>
-      <c r="J26" s="126"/>
-      <c r="K26" s="126"/>
-      <c r="L26" s="126"/>
-      <c r="M26" s="126"/>
-      <c r="N26" s="126"/>
-      <c r="O26" s="126"/>
-      <c r="P26" s="127"/>
+      <c r="A26" s="119"/>
+      <c r="B26" s="120"/>
+      <c r="C26" s="120"/>
+      <c r="D26" s="120"/>
+      <c r="E26" s="120"/>
+      <c r="F26" s="120"/>
+      <c r="G26" s="120"/>
+      <c r="H26" s="121"/>
+      <c r="I26" s="119"/>
+      <c r="J26" s="120"/>
+      <c r="K26" s="120"/>
+      <c r="L26" s="120"/>
+      <c r="M26" s="120"/>
+      <c r="N26" s="120"/>
+      <c r="O26" s="120"/>
+      <c r="P26" s="121"/>
     </row>
     <row r="27" spans="1:18" ht="16.149999999999999" customHeight="1">
-      <c r="A27" s="125"/>
-      <c r="B27" s="126"/>
-      <c r="C27" s="126"/>
-      <c r="D27" s="126"/>
-      <c r="E27" s="126"/>
-      <c r="F27" s="126"/>
-      <c r="G27" s="126"/>
-      <c r="H27" s="127"/>
-      <c r="I27" s="125"/>
-      <c r="J27" s="126"/>
-      <c r="K27" s="126"/>
-      <c r="L27" s="126"/>
-      <c r="M27" s="126"/>
-      <c r="N27" s="126"/>
-      <c r="O27" s="126"/>
-      <c r="P27" s="127"/>
+      <c r="A27" s="119"/>
+      <c r="B27" s="120"/>
+      <c r="C27" s="120"/>
+      <c r="D27" s="120"/>
+      <c r="E27" s="120"/>
+      <c r="F27" s="120"/>
+      <c r="G27" s="120"/>
+      <c r="H27" s="121"/>
+      <c r="I27" s="119"/>
+      <c r="J27" s="120"/>
+      <c r="K27" s="120"/>
+      <c r="L27" s="120"/>
+      <c r="M27" s="120"/>
+      <c r="N27" s="120"/>
+      <c r="O27" s="120"/>
+      <c r="P27" s="121"/>
     </row>
     <row r="28" spans="1:18" ht="16.149999999999999" customHeight="1">
-      <c r="A28" s="125"/>
-      <c r="B28" s="126"/>
-      <c r="C28" s="126"/>
-      <c r="D28" s="126"/>
-      <c r="E28" s="126"/>
-      <c r="F28" s="126"/>
-      <c r="G28" s="126"/>
-      <c r="H28" s="127"/>
-      <c r="I28" s="125"/>
-      <c r="J28" s="126"/>
-      <c r="K28" s="126"/>
-      <c r="L28" s="126"/>
-      <c r="M28" s="126"/>
-      <c r="N28" s="126"/>
-      <c r="O28" s="126"/>
-      <c r="P28" s="127"/>
+      <c r="A28" s="119"/>
+      <c r="B28" s="120"/>
+      <c r="C28" s="120"/>
+      <c r="D28" s="120"/>
+      <c r="E28" s="120"/>
+      <c r="F28" s="120"/>
+      <c r="G28" s="120"/>
+      <c r="H28" s="121"/>
+      <c r="I28" s="119"/>
+      <c r="J28" s="120"/>
+      <c r="K28" s="120"/>
+      <c r="L28" s="120"/>
+      <c r="M28" s="120"/>
+      <c r="N28" s="120"/>
+      <c r="O28" s="120"/>
+      <c r="P28" s="121"/>
     </row>
     <row r="29" spans="1:18" ht="16.149999999999999" customHeight="1">
-      <c r="A29" s="125"/>
-      <c r="B29" s="126"/>
-      <c r="C29" s="126"/>
-      <c r="D29" s="126"/>
-      <c r="E29" s="126"/>
-      <c r="F29" s="126"/>
-      <c r="G29" s="126"/>
-      <c r="H29" s="127"/>
-      <c r="I29" s="125"/>
-      <c r="J29" s="126"/>
-      <c r="K29" s="126"/>
-      <c r="L29" s="126"/>
-      <c r="M29" s="126"/>
-      <c r="N29" s="126"/>
-      <c r="O29" s="126"/>
-      <c r="P29" s="127"/>
+      <c r="A29" s="119"/>
+      <c r="B29" s="120"/>
+      <c r="C29" s="120"/>
+      <c r="D29" s="120"/>
+      <c r="E29" s="120"/>
+      <c r="F29" s="120"/>
+      <c r="G29" s="120"/>
+      <c r="H29" s="121"/>
+      <c r="I29" s="119"/>
+      <c r="J29" s="120"/>
+      <c r="K29" s="120"/>
+      <c r="L29" s="120"/>
+      <c r="M29" s="120"/>
+      <c r="N29" s="120"/>
+      <c r="O29" s="120"/>
+      <c r="P29" s="121"/>
     </row>
     <row r="30" spans="1:18" ht="16.149999999999999" customHeight="1">
-      <c r="A30" s="125"/>
-      <c r="B30" s="126"/>
-      <c r="C30" s="126"/>
-      <c r="D30" s="126"/>
-      <c r="E30" s="126"/>
-      <c r="F30" s="126"/>
-      <c r="G30" s="126"/>
-      <c r="H30" s="127"/>
-      <c r="I30" s="125"/>
-      <c r="J30" s="126"/>
-      <c r="K30" s="126"/>
-      <c r="L30" s="126"/>
-      <c r="M30" s="126"/>
-      <c r="N30" s="126"/>
-      <c r="O30" s="126"/>
-      <c r="P30" s="127"/>
+      <c r="A30" s="119"/>
+      <c r="B30" s="120"/>
+      <c r="C30" s="120"/>
+      <c r="D30" s="120"/>
+      <c r="E30" s="120"/>
+      <c r="F30" s="120"/>
+      <c r="G30" s="120"/>
+      <c r="H30" s="121"/>
+      <c r="I30" s="119"/>
+      <c r="J30" s="120"/>
+      <c r="K30" s="120"/>
+      <c r="L30" s="120"/>
+      <c r="M30" s="120"/>
+      <c r="N30" s="120"/>
+      <c r="O30" s="120"/>
+      <c r="P30" s="121"/>
     </row>
     <row r="31" spans="1:18" ht="16.149999999999999" customHeight="1">
-      <c r="A31" s="125"/>
-      <c r="B31" s="126"/>
-      <c r="C31" s="126"/>
-      <c r="D31" s="126"/>
-      <c r="E31" s="126"/>
-      <c r="F31" s="126"/>
-      <c r="G31" s="126"/>
-      <c r="H31" s="127"/>
-      <c r="I31" s="125"/>
-      <c r="J31" s="126"/>
-      <c r="K31" s="126"/>
-      <c r="L31" s="126"/>
-      <c r="M31" s="126"/>
-      <c r="N31" s="126"/>
-      <c r="O31" s="126"/>
-      <c r="P31" s="127"/>
+      <c r="A31" s="119"/>
+      <c r="B31" s="120"/>
+      <c r="C31" s="120"/>
+      <c r="D31" s="120"/>
+      <c r="E31" s="120"/>
+      <c r="F31" s="120"/>
+      <c r="G31" s="120"/>
+      <c r="H31" s="121"/>
+      <c r="I31" s="119"/>
+      <c r="J31" s="120"/>
+      <c r="K31" s="120"/>
+      <c r="L31" s="120"/>
+      <c r="M31" s="120"/>
+      <c r="N31" s="120"/>
+      <c r="O31" s="120"/>
+      <c r="P31" s="121"/>
       <c r="R31"/>
     </row>
     <row r="32" spans="1:18" ht="16.149999999999999" customHeight="1" thickBot="1">
-      <c r="A32" s="104" t="s">
+      <c r="A32" s="125" t="s">
         <v>373</v>
       </c>
-      <c r="B32" s="105"/>
-      <c r="C32" s="105"/>
-      <c r="D32" s="105"/>
-      <c r="E32" s="105"/>
-      <c r="F32" s="105"/>
-      <c r="G32" s="105"/>
-      <c r="H32" s="106"/>
-      <c r="I32" s="104" t="s">
+      <c r="B32" s="126"/>
+      <c r="C32" s="126"/>
+      <c r="D32" s="126"/>
+      <c r="E32" s="126"/>
+      <c r="F32" s="126"/>
+      <c r="G32" s="126"/>
+      <c r="H32" s="127"/>
+      <c r="I32" s="125" t="s">
         <v>373</v>
       </c>
-      <c r="J32" s="105"/>
-      <c r="K32" s="105"/>
-      <c r="L32" s="105"/>
-      <c r="M32" s="105"/>
-      <c r="N32" s="105"/>
-      <c r="O32" s="105"/>
-      <c r="P32" s="106"/>
+      <c r="J32" s="126"/>
+      <c r="K32" s="126"/>
+      <c r="L32" s="126"/>
+      <c r="M32" s="126"/>
+      <c r="N32" s="126"/>
+      <c r="O32" s="126"/>
+      <c r="P32" s="127"/>
     </row>
     <row r="33" spans="1:18" ht="16.149999999999999" customHeight="1">
-      <c r="A33" s="122"/>
-      <c r="B33" s="123"/>
-      <c r="C33" s="123"/>
-      <c r="D33" s="123"/>
-      <c r="E33" s="123"/>
-      <c r="F33" s="123"/>
-      <c r="G33" s="123"/>
-      <c r="H33" s="124"/>
-      <c r="I33" s="122"/>
-      <c r="J33" s="123"/>
-      <c r="K33" s="123"/>
-      <c r="L33" s="123"/>
-      <c r="M33" s="123"/>
-      <c r="N33" s="123"/>
-      <c r="O33" s="123"/>
-      <c r="P33" s="124"/>
+      <c r="A33" s="116"/>
+      <c r="B33" s="117"/>
+      <c r="C33" s="117"/>
+      <c r="D33" s="117"/>
+      <c r="E33" s="117"/>
+      <c r="F33" s="117"/>
+      <c r="G33" s="117"/>
+      <c r="H33" s="118"/>
+      <c r="I33" s="116"/>
+      <c r="J33" s="117"/>
+      <c r="K33" s="117"/>
+      <c r="L33" s="117"/>
+      <c r="M33" s="117"/>
+      <c r="N33" s="117"/>
+      <c r="O33" s="117"/>
+      <c r="P33" s="118"/>
       <c r="R33"/>
     </row>
     <row r="34" spans="1:18" ht="16.149999999999999" customHeight="1">
-      <c r="A34" s="125"/>
-      <c r="B34" s="126"/>
-      <c r="C34" s="126"/>
-      <c r="D34" s="126"/>
-      <c r="E34" s="126"/>
-      <c r="F34" s="126"/>
-      <c r="G34" s="126"/>
-      <c r="H34" s="127"/>
-      <c r="I34" s="125"/>
-      <c r="J34" s="126"/>
-      <c r="K34" s="126"/>
-      <c r="L34" s="126"/>
-      <c r="M34" s="126"/>
-      <c r="N34" s="126"/>
-      <c r="O34" s="126"/>
-      <c r="P34" s="127"/>
+      <c r="A34" s="119"/>
+      <c r="B34" s="120"/>
+      <c r="C34" s="120"/>
+      <c r="D34" s="120"/>
+      <c r="E34" s="120"/>
+      <c r="F34" s="120"/>
+      <c r="G34" s="120"/>
+      <c r="H34" s="121"/>
+      <c r="I34" s="119"/>
+      <c r="J34" s="120"/>
+      <c r="K34" s="120"/>
+      <c r="L34" s="120"/>
+      <c r="M34" s="120"/>
+      <c r="N34" s="120"/>
+      <c r="O34" s="120"/>
+      <c r="P34" s="121"/>
     </row>
     <row r="35" spans="1:18" ht="16.149999999999999" customHeight="1">
-      <c r="A35" s="125"/>
-      <c r="B35" s="126"/>
-      <c r="C35" s="126"/>
-      <c r="D35" s="126"/>
-      <c r="E35" s="126"/>
-      <c r="F35" s="126"/>
-      <c r="G35" s="126"/>
-      <c r="H35" s="127"/>
-      <c r="I35" s="125"/>
-      <c r="J35" s="126"/>
-      <c r="K35" s="126"/>
-      <c r="L35" s="126"/>
-      <c r="M35" s="126"/>
-      <c r="N35" s="126"/>
-      <c r="O35" s="126"/>
-      <c r="P35" s="127"/>
+      <c r="A35" s="119"/>
+      <c r="B35" s="120"/>
+      <c r="C35" s="120"/>
+      <c r="D35" s="120"/>
+      <c r="E35" s="120"/>
+      <c r="F35" s="120"/>
+      <c r="G35" s="120"/>
+      <c r="H35" s="121"/>
+      <c r="I35" s="119"/>
+      <c r="J35" s="120"/>
+      <c r="K35" s="120"/>
+      <c r="L35" s="120"/>
+      <c r="M35" s="120"/>
+      <c r="N35" s="120"/>
+      <c r="O35" s="120"/>
+      <c r="P35" s="121"/>
     </row>
     <row r="36" spans="1:18" ht="16.149999999999999" customHeight="1">
-      <c r="A36" s="125"/>
-      <c r="B36" s="126"/>
-      <c r="C36" s="126"/>
-      <c r="D36" s="126"/>
-      <c r="E36" s="126"/>
-      <c r="F36" s="126"/>
-      <c r="G36" s="126"/>
-      <c r="H36" s="127"/>
-      <c r="I36" s="125"/>
-      <c r="J36" s="126"/>
-      <c r="K36" s="126"/>
-      <c r="L36" s="126"/>
-      <c r="M36" s="126"/>
-      <c r="N36" s="126"/>
-      <c r="O36" s="126"/>
-      <c r="P36" s="127"/>
+      <c r="A36" s="119"/>
+      <c r="B36" s="120"/>
+      <c r="C36" s="120"/>
+      <c r="D36" s="120"/>
+      <c r="E36" s="120"/>
+      <c r="F36" s="120"/>
+      <c r="G36" s="120"/>
+      <c r="H36" s="121"/>
+      <c r="I36" s="119"/>
+      <c r="J36" s="120"/>
+      <c r="K36" s="120"/>
+      <c r="L36" s="120"/>
+      <c r="M36" s="120"/>
+      <c r="N36" s="120"/>
+      <c r="O36" s="120"/>
+      <c r="P36" s="121"/>
     </row>
     <row r="37" spans="1:18" ht="16.149999999999999" customHeight="1">
-      <c r="A37" s="125"/>
-      <c r="B37" s="126"/>
-      <c r="C37" s="126"/>
-      <c r="D37" s="126"/>
-      <c r="E37" s="126"/>
-      <c r="F37" s="126"/>
-      <c r="G37" s="126"/>
-      <c r="H37" s="127"/>
-      <c r="I37" s="125"/>
-      <c r="J37" s="126"/>
-      <c r="K37" s="126"/>
-      <c r="L37" s="126"/>
-      <c r="M37" s="126"/>
-      <c r="N37" s="126"/>
-      <c r="O37" s="126"/>
-      <c r="P37" s="127"/>
+      <c r="A37" s="119"/>
+      <c r="B37" s="120"/>
+      <c r="C37" s="120"/>
+      <c r="D37" s="120"/>
+      <c r="E37" s="120"/>
+      <c r="F37" s="120"/>
+      <c r="G37" s="120"/>
+      <c r="H37" s="121"/>
+      <c r="I37" s="119"/>
+      <c r="J37" s="120"/>
+      <c r="K37" s="120"/>
+      <c r="L37" s="120"/>
+      <c r="M37" s="120"/>
+      <c r="N37" s="120"/>
+      <c r="O37" s="120"/>
+      <c r="P37" s="121"/>
     </row>
     <row r="38" spans="1:18" ht="16.149999999999999" customHeight="1">
-      <c r="A38" s="125"/>
-      <c r="B38" s="126"/>
-      <c r="C38" s="126"/>
-      <c r="D38" s="126"/>
-      <c r="E38" s="126"/>
-      <c r="F38" s="126"/>
-      <c r="G38" s="126"/>
-      <c r="H38" s="127"/>
-      <c r="I38" s="125"/>
-      <c r="J38" s="126"/>
-      <c r="K38" s="126"/>
-      <c r="L38" s="126"/>
-      <c r="M38" s="126"/>
-      <c r="N38" s="126"/>
-      <c r="O38" s="126"/>
-      <c r="P38" s="127"/>
+      <c r="A38" s="119"/>
+      <c r="B38" s="120"/>
+      <c r="C38" s="120"/>
+      <c r="D38" s="120"/>
+      <c r="E38" s="120"/>
+      <c r="F38" s="120"/>
+      <c r="G38" s="120"/>
+      <c r="H38" s="121"/>
+      <c r="I38" s="119"/>
+      <c r="J38" s="120"/>
+      <c r="K38" s="120"/>
+      <c r="L38" s="120"/>
+      <c r="M38" s="120"/>
+      <c r="N38" s="120"/>
+      <c r="O38" s="120"/>
+      <c r="P38" s="121"/>
     </row>
     <row r="39" spans="1:18" ht="16.149999999999999" customHeight="1">
-      <c r="A39" s="125"/>
-      <c r="B39" s="126"/>
-      <c r="C39" s="126"/>
-      <c r="D39" s="126"/>
-      <c r="E39" s="126"/>
-      <c r="F39" s="126"/>
-      <c r="G39" s="126"/>
-      <c r="H39" s="127"/>
-      <c r="I39" s="125"/>
-      <c r="J39" s="126"/>
-      <c r="K39" s="126"/>
-      <c r="L39" s="126"/>
-      <c r="M39" s="126"/>
-      <c r="N39" s="126"/>
-      <c r="O39" s="126"/>
-      <c r="P39" s="127"/>
+      <c r="A39" s="119"/>
+      <c r="B39" s="120"/>
+      <c r="C39" s="120"/>
+      <c r="D39" s="120"/>
+      <c r="E39" s="120"/>
+      <c r="F39" s="120"/>
+      <c r="G39" s="120"/>
+      <c r="H39" s="121"/>
+      <c r="I39" s="119"/>
+      <c r="J39" s="120"/>
+      <c r="K39" s="120"/>
+      <c r="L39" s="120"/>
+      <c r="M39" s="120"/>
+      <c r="N39" s="120"/>
+      <c r="O39" s="120"/>
+      <c r="P39" s="121"/>
     </row>
     <row r="40" spans="1:18" ht="16.149999999999999" customHeight="1">
-      <c r="A40" s="125"/>
-      <c r="B40" s="126"/>
-      <c r="C40" s="126"/>
-      <c r="D40" s="126"/>
-      <c r="E40" s="126"/>
-      <c r="F40" s="126"/>
-      <c r="G40" s="126"/>
-      <c r="H40" s="127"/>
-      <c r="I40" s="125"/>
-      <c r="J40" s="126"/>
-      <c r="K40" s="126"/>
-      <c r="L40" s="126"/>
-      <c r="M40" s="126"/>
-      <c r="N40" s="126"/>
-      <c r="O40" s="126"/>
-      <c r="P40" s="127"/>
+      <c r="A40" s="119"/>
+      <c r="B40" s="120"/>
+      <c r="C40" s="120"/>
+      <c r="D40" s="120"/>
+      <c r="E40" s="120"/>
+      <c r="F40" s="120"/>
+      <c r="G40" s="120"/>
+      <c r="H40" s="121"/>
+      <c r="I40" s="119"/>
+      <c r="J40" s="120"/>
+      <c r="K40" s="120"/>
+      <c r="L40" s="120"/>
+      <c r="M40" s="120"/>
+      <c r="N40" s="120"/>
+      <c r="O40" s="120"/>
+      <c r="P40" s="121"/>
     </row>
     <row r="41" spans="1:18" ht="16.149999999999999" customHeight="1">
-      <c r="A41" s="125"/>
-      <c r="B41" s="126"/>
-      <c r="C41" s="126"/>
-      <c r="D41" s="126"/>
-      <c r="E41" s="126"/>
-      <c r="F41" s="126"/>
-      <c r="G41" s="126"/>
-      <c r="H41" s="127"/>
-      <c r="I41" s="125"/>
-      <c r="J41" s="126"/>
-      <c r="K41" s="126"/>
-      <c r="L41" s="126"/>
-      <c r="M41" s="126"/>
-      <c r="N41" s="126"/>
-      <c r="O41" s="126"/>
-      <c r="P41" s="127"/>
+      <c r="A41" s="119"/>
+      <c r="B41" s="120"/>
+      <c r="C41" s="120"/>
+      <c r="D41" s="120"/>
+      <c r="E41" s="120"/>
+      <c r="F41" s="120"/>
+      <c r="G41" s="120"/>
+      <c r="H41" s="121"/>
+      <c r="I41" s="119"/>
+      <c r="J41" s="120"/>
+      <c r="K41" s="120"/>
+      <c r="L41" s="120"/>
+      <c r="M41" s="120"/>
+      <c r="N41" s="120"/>
+      <c r="O41" s="120"/>
+      <c r="P41" s="121"/>
     </row>
     <row r="42" spans="1:18" ht="16.149999999999999" customHeight="1">
-      <c r="A42" s="125"/>
-      <c r="B42" s="126"/>
-      <c r="C42" s="126"/>
-      <c r="D42" s="126"/>
-      <c r="E42" s="126"/>
-      <c r="F42" s="126"/>
-      <c r="G42" s="126"/>
-      <c r="H42" s="127"/>
-      <c r="I42" s="125"/>
-      <c r="J42" s="126"/>
-      <c r="K42" s="126"/>
-      <c r="L42" s="126"/>
-      <c r="M42" s="126"/>
-      <c r="N42" s="126"/>
-      <c r="O42" s="126"/>
-      <c r="P42" s="127"/>
+      <c r="A42" s="119"/>
+      <c r="B42" s="120"/>
+      <c r="C42" s="120"/>
+      <c r="D42" s="120"/>
+      <c r="E42" s="120"/>
+      <c r="F42" s="120"/>
+      <c r="G42" s="120"/>
+      <c r="H42" s="121"/>
+      <c r="I42" s="119"/>
+      <c r="J42" s="120"/>
+      <c r="K42" s="120"/>
+      <c r="L42" s="120"/>
+      <c r="M42" s="120"/>
+      <c r="N42" s="120"/>
+      <c r="O42" s="120"/>
+      <c r="P42" s="121"/>
     </row>
     <row r="43" spans="1:18" ht="16.149999999999999" customHeight="1">
-      <c r="A43" s="125"/>
-      <c r="B43" s="126"/>
-      <c r="C43" s="126"/>
-      <c r="D43" s="126"/>
-      <c r="E43" s="126"/>
-      <c r="F43" s="126"/>
-      <c r="G43" s="126"/>
-      <c r="H43" s="127"/>
-      <c r="I43" s="125"/>
-      <c r="J43" s="126"/>
-      <c r="K43" s="126"/>
-      <c r="L43" s="126"/>
-      <c r="M43" s="126"/>
-      <c r="N43" s="126"/>
-      <c r="O43" s="126"/>
-      <c r="P43" s="127"/>
+      <c r="A43" s="119"/>
+      <c r="B43" s="120"/>
+      <c r="C43" s="120"/>
+      <c r="D43" s="120"/>
+      <c r="E43" s="120"/>
+      <c r="F43" s="120"/>
+      <c r="G43" s="120"/>
+      <c r="H43" s="121"/>
+      <c r="I43" s="119"/>
+      <c r="J43" s="120"/>
+      <c r="K43" s="120"/>
+      <c r="L43" s="120"/>
+      <c r="M43" s="120"/>
+      <c r="N43" s="120"/>
+      <c r="O43" s="120"/>
+      <c r="P43" s="121"/>
     </row>
     <row r="44" spans="1:18" ht="16.149999999999999" customHeight="1">
-      <c r="A44" s="125"/>
-      <c r="B44" s="126"/>
-      <c r="C44" s="126"/>
-      <c r="D44" s="126"/>
-      <c r="E44" s="126"/>
-      <c r="F44" s="126"/>
-      <c r="G44" s="126"/>
-      <c r="H44" s="127"/>
-      <c r="I44" s="125"/>
-      <c r="J44" s="126"/>
-      <c r="K44" s="126"/>
-      <c r="L44" s="126"/>
-      <c r="M44" s="126"/>
-      <c r="N44" s="126"/>
-      <c r="O44" s="126"/>
-      <c r="P44" s="127"/>
+      <c r="A44" s="119"/>
+      <c r="B44" s="120"/>
+      <c r="C44" s="120"/>
+      <c r="D44" s="120"/>
+      <c r="E44" s="120"/>
+      <c r="F44" s="120"/>
+      <c r="G44" s="120"/>
+      <c r="H44" s="121"/>
+      <c r="I44" s="119"/>
+      <c r="J44" s="120"/>
+      <c r="K44" s="120"/>
+      <c r="L44" s="120"/>
+      <c r="M44" s="120"/>
+      <c r="N44" s="120"/>
+      <c r="O44" s="120"/>
+      <c r="P44" s="121"/>
     </row>
     <row r="45" spans="1:18" ht="16.149999999999999" customHeight="1">
-      <c r="A45" s="125"/>
-      <c r="B45" s="126"/>
-      <c r="C45" s="126"/>
-      <c r="D45" s="126"/>
-      <c r="E45" s="126"/>
-      <c r="F45" s="126"/>
-      <c r="G45" s="126"/>
-      <c r="H45" s="127"/>
-      <c r="I45" s="125"/>
-      <c r="J45" s="126"/>
-      <c r="K45" s="126"/>
-      <c r="L45" s="126"/>
-      <c r="M45" s="126"/>
-      <c r="N45" s="126"/>
-      <c r="O45" s="126"/>
-      <c r="P45" s="127"/>
+      <c r="A45" s="119"/>
+      <c r="B45" s="120"/>
+      <c r="C45" s="120"/>
+      <c r="D45" s="120"/>
+      <c r="E45" s="120"/>
+      <c r="F45" s="120"/>
+      <c r="G45" s="120"/>
+      <c r="H45" s="121"/>
+      <c r="I45" s="119"/>
+      <c r="J45" s="120"/>
+      <c r="K45" s="120"/>
+      <c r="L45" s="120"/>
+      <c r="M45" s="120"/>
+      <c r="N45" s="120"/>
+      <c r="O45" s="120"/>
+      <c r="P45" s="121"/>
     </row>
     <row r="46" spans="1:18" ht="16.149999999999999" customHeight="1">
-      <c r="A46" s="125"/>
-      <c r="B46" s="126"/>
-      <c r="C46" s="126"/>
-      <c r="D46" s="126"/>
-      <c r="E46" s="126"/>
-      <c r="F46" s="126"/>
-      <c r="G46" s="126"/>
-      <c r="H46" s="127"/>
-      <c r="I46" s="125"/>
-      <c r="J46" s="126"/>
-      <c r="K46" s="126"/>
-      <c r="L46" s="126"/>
-      <c r="M46" s="126"/>
-      <c r="N46" s="126"/>
-      <c r="O46" s="126"/>
-      <c r="P46" s="127"/>
+      <c r="A46" s="119"/>
+      <c r="B46" s="120"/>
+      <c r="C46" s="120"/>
+      <c r="D46" s="120"/>
+      <c r="E46" s="120"/>
+      <c r="F46" s="120"/>
+      <c r="G46" s="120"/>
+      <c r="H46" s="121"/>
+      <c r="I46" s="119"/>
+      <c r="J46" s="120"/>
+      <c r="K46" s="120"/>
+      <c r="L46" s="120"/>
+      <c r="M46" s="120"/>
+      <c r="N46" s="120"/>
+      <c r="O46" s="120"/>
+      <c r="P46" s="121"/>
     </row>
     <row r="47" spans="1:18" ht="16.149999999999999" customHeight="1">
-      <c r="A47" s="125"/>
-      <c r="B47" s="126"/>
-      <c r="C47" s="126"/>
-      <c r="D47" s="126"/>
-      <c r="E47" s="126"/>
-      <c r="F47" s="126"/>
-      <c r="G47" s="126"/>
-      <c r="H47" s="127"/>
-      <c r="I47" s="125"/>
-      <c r="J47" s="126"/>
-      <c r="K47" s="126"/>
-      <c r="L47" s="126"/>
-      <c r="M47" s="126"/>
-      <c r="N47" s="126"/>
-      <c r="O47" s="126"/>
-      <c r="P47" s="127"/>
+      <c r="A47" s="119"/>
+      <c r="B47" s="120"/>
+      <c r="C47" s="120"/>
+      <c r="D47" s="120"/>
+      <c r="E47" s="120"/>
+      <c r="F47" s="120"/>
+      <c r="G47" s="120"/>
+      <c r="H47" s="121"/>
+      <c r="I47" s="119"/>
+      <c r="J47" s="120"/>
+      <c r="K47" s="120"/>
+      <c r="L47" s="120"/>
+      <c r="M47" s="120"/>
+      <c r="N47" s="120"/>
+      <c r="O47" s="120"/>
+      <c r="P47" s="121"/>
     </row>
     <row r="48" spans="1:18" ht="16.149999999999999" customHeight="1">
-      <c r="A48" s="125"/>
-      <c r="B48" s="126"/>
-      <c r="C48" s="126"/>
-      <c r="D48" s="126"/>
-      <c r="E48" s="126"/>
-      <c r="F48" s="126"/>
-      <c r="G48" s="126"/>
-      <c r="H48" s="127"/>
-      <c r="I48" s="125"/>
-      <c r="J48" s="126"/>
-      <c r="K48" s="126"/>
-      <c r="L48" s="126"/>
-      <c r="M48" s="126"/>
-      <c r="N48" s="126"/>
-      <c r="O48" s="126"/>
-      <c r="P48" s="127"/>
+      <c r="A48" s="119"/>
+      <c r="B48" s="120"/>
+      <c r="C48" s="120"/>
+      <c r="D48" s="120"/>
+      <c r="E48" s="120"/>
+      <c r="F48" s="120"/>
+      <c r="G48" s="120"/>
+      <c r="H48" s="121"/>
+      <c r="I48" s="119"/>
+      <c r="J48" s="120"/>
+      <c r="K48" s="120"/>
+      <c r="L48" s="120"/>
+      <c r="M48" s="120"/>
+      <c r="N48" s="120"/>
+      <c r="O48" s="120"/>
+      <c r="P48" s="121"/>
     </row>
     <row r="49" spans="1:16" ht="16.149999999999999" customHeight="1">
-      <c r="A49" s="125"/>
-      <c r="B49" s="126"/>
-      <c r="C49" s="126"/>
-      <c r="D49" s="126"/>
-      <c r="E49" s="126"/>
-      <c r="F49" s="126"/>
-      <c r="G49" s="126"/>
-      <c r="H49" s="127"/>
-      <c r="I49" s="125"/>
-      <c r="J49" s="126"/>
-      <c r="K49" s="126"/>
-      <c r="L49" s="126"/>
-      <c r="M49" s="126"/>
-      <c r="N49" s="126"/>
-      <c r="O49" s="126"/>
-      <c r="P49" s="127"/>
+      <c r="A49" s="119"/>
+      <c r="B49" s="120"/>
+      <c r="C49" s="120"/>
+      <c r="D49" s="120"/>
+      <c r="E49" s="120"/>
+      <c r="F49" s="120"/>
+      <c r="G49" s="120"/>
+      <c r="H49" s="121"/>
+      <c r="I49" s="119"/>
+      <c r="J49" s="120"/>
+      <c r="K49" s="120"/>
+      <c r="L49" s="120"/>
+      <c r="M49" s="120"/>
+      <c r="N49" s="120"/>
+      <c r="O49" s="120"/>
+      <c r="P49" s="121"/>
     </row>
     <row r="50" spans="1:16" ht="16.149999999999999" customHeight="1" thickBot="1">
-      <c r="A50" s="104" t="s">
+      <c r="A50" s="125" t="s">
         <v>374</v>
       </c>
-      <c r="B50" s="105"/>
-      <c r="C50" s="105"/>
-      <c r="D50" s="105"/>
-      <c r="E50" s="105"/>
-      <c r="F50" s="105"/>
-      <c r="G50" s="105"/>
-      <c r="H50" s="106"/>
-      <c r="I50" s="104" t="s">
+      <c r="B50" s="126"/>
+      <c r="C50" s="126"/>
+      <c r="D50" s="126"/>
+      <c r="E50" s="126"/>
+      <c r="F50" s="126"/>
+      <c r="G50" s="126"/>
+      <c r="H50" s="127"/>
+      <c r="I50" s="125" t="s">
         <v>374</v>
       </c>
-      <c r="J50" s="105"/>
-      <c r="K50" s="105"/>
-      <c r="L50" s="105"/>
-      <c r="M50" s="105"/>
-      <c r="N50" s="105"/>
-      <c r="O50" s="105"/>
-      <c r="P50" s="106"/>
+      <c r="J50" s="126"/>
+      <c r="K50" s="126"/>
+      <c r="L50" s="126"/>
+      <c r="M50" s="126"/>
+      <c r="N50" s="126"/>
+      <c r="O50" s="126"/>
+      <c r="P50" s="127"/>
     </row>
     <row r="51" spans="1:16" ht="16.149999999999999" customHeight="1">
-      <c r="A51" s="122"/>
-      <c r="B51" s="123"/>
-      <c r="C51" s="123"/>
-      <c r="D51" s="123"/>
-      <c r="E51" s="123"/>
-      <c r="F51" s="123"/>
-      <c r="G51" s="123"/>
-      <c r="H51" s="124"/>
-      <c r="I51" s="122"/>
-      <c r="J51" s="123"/>
-      <c r="K51" s="123"/>
-      <c r="L51" s="123"/>
-      <c r="M51" s="123"/>
-      <c r="N51" s="123"/>
-      <c r="O51" s="123"/>
-      <c r="P51" s="124"/>
+      <c r="A51" s="116"/>
+      <c r="B51" s="117"/>
+      <c r="C51" s="117"/>
+      <c r="D51" s="117"/>
+      <c r="E51" s="117"/>
+      <c r="F51" s="117"/>
+      <c r="G51" s="117"/>
+      <c r="H51" s="118"/>
+      <c r="I51" s="116"/>
+      <c r="J51" s="117"/>
+      <c r="K51" s="117"/>
+      <c r="L51" s="117"/>
+      <c r="M51" s="117"/>
+      <c r="N51" s="117"/>
+      <c r="O51" s="117"/>
+      <c r="P51" s="118"/>
     </row>
     <row r="52" spans="1:16" ht="16.149999999999999" customHeight="1">
-      <c r="A52" s="125"/>
-      <c r="B52" s="126"/>
-      <c r="C52" s="126"/>
-      <c r="D52" s="126"/>
-      <c r="E52" s="126"/>
-      <c r="F52" s="126"/>
-      <c r="G52" s="126"/>
-      <c r="H52" s="127"/>
-      <c r="I52" s="125"/>
-      <c r="J52" s="126"/>
-      <c r="K52" s="126"/>
-      <c r="L52" s="126"/>
-      <c r="M52" s="126"/>
-      <c r="N52" s="126"/>
-      <c r="O52" s="126"/>
-      <c r="P52" s="127"/>
+      <c r="A52" s="119"/>
+      <c r="B52" s="120"/>
+      <c r="C52" s="120"/>
+      <c r="D52" s="120"/>
+      <c r="E52" s="120"/>
+      <c r="F52" s="120"/>
+      <c r="G52" s="120"/>
+      <c r="H52" s="121"/>
+      <c r="I52" s="119"/>
+      <c r="J52" s="120"/>
+      <c r="K52" s="120"/>
+      <c r="L52" s="120"/>
+      <c r="M52" s="120"/>
+      <c r="N52" s="120"/>
+      <c r="O52" s="120"/>
+      <c r="P52" s="121"/>
     </row>
     <row r="53" spans="1:16" ht="16.149999999999999" customHeight="1">
-      <c r="A53" s="125"/>
-      <c r="B53" s="126"/>
-      <c r="C53" s="126"/>
-      <c r="D53" s="126"/>
-      <c r="E53" s="126"/>
-      <c r="F53" s="126"/>
-      <c r="G53" s="126"/>
-      <c r="H53" s="127"/>
-      <c r="I53" s="125"/>
-      <c r="J53" s="126"/>
-      <c r="K53" s="126"/>
-      <c r="L53" s="126"/>
-      <c r="M53" s="126"/>
-      <c r="N53" s="126"/>
-      <c r="O53" s="126"/>
-      <c r="P53" s="127"/>
+      <c r="A53" s="119"/>
+      <c r="B53" s="120"/>
+      <c r="C53" s="120"/>
+      <c r="D53" s="120"/>
+      <c r="E53" s="120"/>
+      <c r="F53" s="120"/>
+      <c r="G53" s="120"/>
+      <c r="H53" s="121"/>
+      <c r="I53" s="119"/>
+      <c r="J53" s="120"/>
+      <c r="K53" s="120"/>
+      <c r="L53" s="120"/>
+      <c r="M53" s="120"/>
+      <c r="N53" s="120"/>
+      <c r="O53" s="120"/>
+      <c r="P53" s="121"/>
     </row>
     <row r="54" spans="1:16" ht="16.149999999999999" customHeight="1">
-      <c r="A54" s="125"/>
-      <c r="B54" s="126"/>
-      <c r="C54" s="126"/>
-      <c r="D54" s="126"/>
-      <c r="E54" s="126"/>
-      <c r="F54" s="126"/>
-      <c r="G54" s="126"/>
-      <c r="H54" s="127"/>
-      <c r="I54" s="125"/>
-      <c r="J54" s="126"/>
-      <c r="K54" s="126"/>
-      <c r="L54" s="126"/>
-      <c r="M54" s="126"/>
-      <c r="N54" s="126"/>
-      <c r="O54" s="126"/>
-      <c r="P54" s="127"/>
+      <c r="A54" s="119"/>
+      <c r="B54" s="120"/>
+      <c r="C54" s="120"/>
+      <c r="D54" s="120"/>
+      <c r="E54" s="120"/>
+      <c r="F54" s="120"/>
+      <c r="G54" s="120"/>
+      <c r="H54" s="121"/>
+      <c r="I54" s="119"/>
+      <c r="J54" s="120"/>
+      <c r="K54" s="120"/>
+      <c r="L54" s="120"/>
+      <c r="M54" s="120"/>
+      <c r="N54" s="120"/>
+      <c r="O54" s="120"/>
+      <c r="P54" s="121"/>
     </row>
     <row r="55" spans="1:16" ht="16.149999999999999" customHeight="1">
-      <c r="A55" s="125"/>
-      <c r="B55" s="126"/>
-      <c r="C55" s="126"/>
-      <c r="D55" s="126"/>
-      <c r="E55" s="126"/>
-      <c r="F55" s="126"/>
-      <c r="G55" s="126"/>
-      <c r="H55" s="127"/>
-      <c r="I55" s="125"/>
-      <c r="J55" s="126"/>
-      <c r="K55" s="126"/>
-      <c r="L55" s="126"/>
-      <c r="M55" s="126"/>
-      <c r="N55" s="126"/>
-      <c r="O55" s="126"/>
-      <c r="P55" s="127"/>
+      <c r="A55" s="119"/>
+      <c r="B55" s="120"/>
+      <c r="C55" s="120"/>
+      <c r="D55" s="120"/>
+      <c r="E55" s="120"/>
+      <c r="F55" s="120"/>
+      <c r="G55" s="120"/>
+      <c r="H55" s="121"/>
+      <c r="I55" s="119"/>
+      <c r="J55" s="120"/>
+      <c r="K55" s="120"/>
+      <c r="L55" s="120"/>
+      <c r="M55" s="120"/>
+      <c r="N55" s="120"/>
+      <c r="O55" s="120"/>
+      <c r="P55" s="121"/>
     </row>
     <row r="56" spans="1:16" ht="16.149999999999999" customHeight="1">
-      <c r="A56" s="125"/>
-      <c r="B56" s="126"/>
-      <c r="C56" s="126"/>
-      <c r="D56" s="126"/>
-      <c r="E56" s="126"/>
-      <c r="F56" s="126"/>
-      <c r="G56" s="126"/>
-      <c r="H56" s="127"/>
-      <c r="I56" s="125"/>
-      <c r="J56" s="126"/>
-      <c r="K56" s="126"/>
-      <c r="L56" s="126"/>
-      <c r="M56" s="126"/>
-      <c r="N56" s="126"/>
-      <c r="O56" s="126"/>
-      <c r="P56" s="127"/>
+      <c r="A56" s="119"/>
+      <c r="B56" s="120"/>
+      <c r="C56" s="120"/>
+      <c r="D56" s="120"/>
+      <c r="E56" s="120"/>
+      <c r="F56" s="120"/>
+      <c r="G56" s="120"/>
+      <c r="H56" s="121"/>
+      <c r="I56" s="119"/>
+      <c r="J56" s="120"/>
+      <c r="K56" s="120"/>
+      <c r="L56" s="120"/>
+      <c r="M56" s="120"/>
+      <c r="N56" s="120"/>
+      <c r="O56" s="120"/>
+      <c r="P56" s="121"/>
     </row>
     <row r="57" spans="1:16" ht="16.149999999999999" customHeight="1">
-      <c r="A57" s="125"/>
-      <c r="B57" s="126"/>
-      <c r="C57" s="126"/>
-      <c r="D57" s="126"/>
-      <c r="E57" s="126"/>
-      <c r="F57" s="126"/>
-      <c r="G57" s="126"/>
-      <c r="H57" s="127"/>
-      <c r="I57" s="125"/>
-      <c r="J57" s="126"/>
-      <c r="K57" s="126"/>
-      <c r="L57" s="126"/>
-      <c r="M57" s="126"/>
-      <c r="N57" s="126"/>
-      <c r="O57" s="126"/>
-      <c r="P57" s="127"/>
+      <c r="A57" s="119"/>
+      <c r="B57" s="120"/>
+      <c r="C57" s="120"/>
+      <c r="D57" s="120"/>
+      <c r="E57" s="120"/>
+      <c r="F57" s="120"/>
+      <c r="G57" s="120"/>
+      <c r="H57" s="121"/>
+      <c r="I57" s="119"/>
+      <c r="J57" s="120"/>
+      <c r="K57" s="120"/>
+      <c r="L57" s="120"/>
+      <c r="M57" s="120"/>
+      <c r="N57" s="120"/>
+      <c r="O57" s="120"/>
+      <c r="P57" s="121"/>
     </row>
     <row r="58" spans="1:16" ht="16.149999999999999" customHeight="1">
-      <c r="A58" s="125"/>
-      <c r="B58" s="126"/>
-      <c r="C58" s="126"/>
-      <c r="D58" s="126"/>
-      <c r="E58" s="126"/>
-      <c r="F58" s="126"/>
-      <c r="G58" s="126"/>
-      <c r="H58" s="127"/>
-      <c r="I58" s="125"/>
-      <c r="J58" s="126"/>
-      <c r="K58" s="126"/>
-      <c r="L58" s="126"/>
-      <c r="M58" s="126"/>
-      <c r="N58" s="126"/>
-      <c r="O58" s="126"/>
-      <c r="P58" s="127"/>
+      <c r="A58" s="119"/>
+      <c r="B58" s="120"/>
+      <c r="C58" s="120"/>
+      <c r="D58" s="120"/>
+      <c r="E58" s="120"/>
+      <c r="F58" s="120"/>
+      <c r="G58" s="120"/>
+      <c r="H58" s="121"/>
+      <c r="I58" s="119"/>
+      <c r="J58" s="120"/>
+      <c r="K58" s="120"/>
+      <c r="L58" s="120"/>
+      <c r="M58" s="120"/>
+      <c r="N58" s="120"/>
+      <c r="O58" s="120"/>
+      <c r="P58" s="121"/>
     </row>
     <row r="59" spans="1:16" ht="16.149999999999999" customHeight="1">
-      <c r="A59" s="125"/>
-      <c r="B59" s="126"/>
-      <c r="C59" s="126"/>
-      <c r="D59" s="126"/>
-      <c r="E59" s="126"/>
-      <c r="F59" s="126"/>
-      <c r="G59" s="126"/>
-      <c r="H59" s="127"/>
-      <c r="I59" s="125"/>
-      <c r="J59" s="126"/>
-      <c r="K59" s="126"/>
-      <c r="L59" s="126"/>
-      <c r="M59" s="126"/>
-      <c r="N59" s="126"/>
-      <c r="O59" s="126"/>
-      <c r="P59" s="127"/>
+      <c r="A59" s="119"/>
+      <c r="B59" s="120"/>
+      <c r="C59" s="120"/>
+      <c r="D59" s="120"/>
+      <c r="E59" s="120"/>
+      <c r="F59" s="120"/>
+      <c r="G59" s="120"/>
+      <c r="H59" s="121"/>
+      <c r="I59" s="119"/>
+      <c r="J59" s="120"/>
+      <c r="K59" s="120"/>
+      <c r="L59" s="120"/>
+      <c r="M59" s="120"/>
+      <c r="N59" s="120"/>
+      <c r="O59" s="120"/>
+      <c r="P59" s="121"/>
     </row>
     <row r="60" spans="1:16" ht="16.149999999999999" customHeight="1">
-      <c r="A60" s="125"/>
-      <c r="B60" s="126"/>
-      <c r="C60" s="126"/>
-      <c r="D60" s="126"/>
-      <c r="E60" s="126"/>
-      <c r="F60" s="126"/>
-      <c r="G60" s="126"/>
-      <c r="H60" s="127"/>
-      <c r="I60" s="125"/>
-      <c r="J60" s="126"/>
-      <c r="K60" s="126"/>
-      <c r="L60" s="126"/>
-      <c r="M60" s="126"/>
-      <c r="N60" s="126"/>
-      <c r="O60" s="126"/>
-      <c r="P60" s="127"/>
+      <c r="A60" s="119"/>
+      <c r="B60" s="120"/>
+      <c r="C60" s="120"/>
+      <c r="D60" s="120"/>
+      <c r="E60" s="120"/>
+      <c r="F60" s="120"/>
+      <c r="G60" s="120"/>
+      <c r="H60" s="121"/>
+      <c r="I60" s="119"/>
+      <c r="J60" s="120"/>
+      <c r="K60" s="120"/>
+      <c r="L60" s="120"/>
+      <c r="M60" s="120"/>
+      <c r="N60" s="120"/>
+      <c r="O60" s="120"/>
+      <c r="P60" s="121"/>
     </row>
     <row r="61" spans="1:16" ht="16.149999999999999" customHeight="1">
-      <c r="A61" s="125"/>
-      <c r="B61" s="126"/>
-      <c r="C61" s="126"/>
-      <c r="D61" s="126"/>
-      <c r="E61" s="126"/>
-      <c r="F61" s="126"/>
-      <c r="G61" s="126"/>
-      <c r="H61" s="127"/>
-      <c r="I61" s="125"/>
-      <c r="J61" s="126"/>
-      <c r="K61" s="126"/>
-      <c r="L61" s="126"/>
-      <c r="M61" s="126"/>
-      <c r="N61" s="126"/>
-      <c r="O61" s="126"/>
-      <c r="P61" s="127"/>
+      <c r="A61" s="119"/>
+      <c r="B61" s="120"/>
+      <c r="C61" s="120"/>
+      <c r="D61" s="120"/>
+      <c r="E61" s="120"/>
+      <c r="F61" s="120"/>
+      <c r="G61" s="120"/>
+      <c r="H61" s="121"/>
+      <c r="I61" s="119"/>
+      <c r="J61" s="120"/>
+      <c r="K61" s="120"/>
+      <c r="L61" s="120"/>
+      <c r="M61" s="120"/>
+      <c r="N61" s="120"/>
+      <c r="O61" s="120"/>
+      <c r="P61" s="121"/>
     </row>
     <row r="62" spans="1:16" ht="16.149999999999999" customHeight="1">
-      <c r="A62" s="125"/>
-      <c r="B62" s="126"/>
-      <c r="C62" s="126"/>
-      <c r="D62" s="126"/>
-      <c r="E62" s="126"/>
-      <c r="F62" s="126"/>
-      <c r="G62" s="126"/>
-      <c r="H62" s="127"/>
-      <c r="I62" s="125"/>
-      <c r="J62" s="126"/>
-      <c r="K62" s="126"/>
-      <c r="L62" s="126"/>
-      <c r="M62" s="126"/>
-      <c r="N62" s="126"/>
-      <c r="O62" s="126"/>
-      <c r="P62" s="127"/>
+      <c r="A62" s="119"/>
+      <c r="B62" s="120"/>
+      <c r="C62" s="120"/>
+      <c r="D62" s="120"/>
+      <c r="E62" s="120"/>
+      <c r="F62" s="120"/>
+      <c r="G62" s="120"/>
+      <c r="H62" s="121"/>
+      <c r="I62" s="119"/>
+      <c r="J62" s="120"/>
+      <c r="K62" s="120"/>
+      <c r="L62" s="120"/>
+      <c r="M62" s="120"/>
+      <c r="N62" s="120"/>
+      <c r="O62" s="120"/>
+      <c r="P62" s="121"/>
     </row>
     <row r="63" spans="1:16" ht="16.149999999999999" customHeight="1">
-      <c r="A63" s="125"/>
-      <c r="B63" s="126"/>
-      <c r="C63" s="126"/>
-      <c r="D63" s="126"/>
-      <c r="E63" s="126"/>
-      <c r="F63" s="126"/>
-      <c r="G63" s="126"/>
-      <c r="H63" s="127"/>
-      <c r="I63" s="125"/>
-      <c r="J63" s="126"/>
-      <c r="K63" s="126"/>
-      <c r="L63" s="126"/>
-      <c r="M63" s="126"/>
-      <c r="N63" s="126"/>
-      <c r="O63" s="126"/>
-      <c r="P63" s="127"/>
+      <c r="A63" s="119"/>
+      <c r="B63" s="120"/>
+      <c r="C63" s="120"/>
+      <c r="D63" s="120"/>
+      <c r="E63" s="120"/>
+      <c r="F63" s="120"/>
+      <c r="G63" s="120"/>
+      <c r="H63" s="121"/>
+      <c r="I63" s="119"/>
+      <c r="J63" s="120"/>
+      <c r="K63" s="120"/>
+      <c r="L63" s="120"/>
+      <c r="M63" s="120"/>
+      <c r="N63" s="120"/>
+      <c r="O63" s="120"/>
+      <c r="P63" s="121"/>
     </row>
     <row r="64" spans="1:16" ht="16.149999999999999" customHeight="1">
-      <c r="A64" s="125"/>
-      <c r="B64" s="126"/>
-      <c r="C64" s="126"/>
-      <c r="D64" s="126"/>
-      <c r="E64" s="126"/>
-      <c r="F64" s="126"/>
-      <c r="G64" s="126"/>
-      <c r="H64" s="127"/>
-      <c r="I64" s="125"/>
-      <c r="J64" s="126"/>
-      <c r="K64" s="126"/>
-      <c r="L64" s="126"/>
-      <c r="M64" s="126"/>
-      <c r="N64" s="126"/>
-      <c r="O64" s="126"/>
-      <c r="P64" s="127"/>
+      <c r="A64" s="119"/>
+      <c r="B64" s="120"/>
+      <c r="C64" s="120"/>
+      <c r="D64" s="120"/>
+      <c r="E64" s="120"/>
+      <c r="F64" s="120"/>
+      <c r="G64" s="120"/>
+      <c r="H64" s="121"/>
+      <c r="I64" s="119"/>
+      <c r="J64" s="120"/>
+      <c r="K64" s="120"/>
+      <c r="L64" s="120"/>
+      <c r="M64" s="120"/>
+      <c r="N64" s="120"/>
+      <c r="O64" s="120"/>
+      <c r="P64" s="121"/>
     </row>
     <row r="65" spans="1:16" ht="16.149999999999999" customHeight="1">
-      <c r="A65" s="125"/>
-      <c r="B65" s="126"/>
-      <c r="C65" s="126"/>
-      <c r="D65" s="126"/>
-      <c r="E65" s="126"/>
-      <c r="F65" s="126"/>
-      <c r="G65" s="126"/>
-      <c r="H65" s="127"/>
-      <c r="I65" s="125"/>
-      <c r="J65" s="126"/>
-      <c r="K65" s="126"/>
-      <c r="L65" s="126"/>
-      <c r="M65" s="126"/>
-      <c r="N65" s="126"/>
-      <c r="O65" s="126"/>
-      <c r="P65" s="127"/>
+      <c r="A65" s="119"/>
+      <c r="B65" s="120"/>
+      <c r="C65" s="120"/>
+      <c r="D65" s="120"/>
+      <c r="E65" s="120"/>
+      <c r="F65" s="120"/>
+      <c r="G65" s="120"/>
+      <c r="H65" s="121"/>
+      <c r="I65" s="119"/>
+      <c r="J65" s="120"/>
+      <c r="K65" s="120"/>
+      <c r="L65" s="120"/>
+      <c r="M65" s="120"/>
+      <c r="N65" s="120"/>
+      <c r="O65" s="120"/>
+      <c r="P65" s="121"/>
     </row>
     <row r="66" spans="1:16" ht="16.149999999999999" customHeight="1">
-      <c r="A66" s="125"/>
-      <c r="B66" s="126"/>
-      <c r="C66" s="126"/>
-      <c r="D66" s="126"/>
-      <c r="E66" s="126"/>
-      <c r="F66" s="126"/>
-      <c r="G66" s="126"/>
-      <c r="H66" s="127"/>
-      <c r="I66" s="125"/>
-      <c r="J66" s="126"/>
-      <c r="K66" s="126"/>
-      <c r="L66" s="126"/>
-      <c r="M66" s="126"/>
-      <c r="N66" s="126"/>
-      <c r="O66" s="126"/>
-      <c r="P66" s="127"/>
+      <c r="A66" s="119"/>
+      <c r="B66" s="120"/>
+      <c r="C66" s="120"/>
+      <c r="D66" s="120"/>
+      <c r="E66" s="120"/>
+      <c r="F66" s="120"/>
+      <c r="G66" s="120"/>
+      <c r="H66" s="121"/>
+      <c r="I66" s="119"/>
+      <c r="J66" s="120"/>
+      <c r="K66" s="120"/>
+      <c r="L66" s="120"/>
+      <c r="M66" s="120"/>
+      <c r="N66" s="120"/>
+      <c r="O66" s="120"/>
+      <c r="P66" s="121"/>
     </row>
     <row r="67" spans="1:16" ht="16.149999999999999" customHeight="1" thickBot="1">
-      <c r="A67" s="128"/>
-      <c r="B67" s="129"/>
-      <c r="C67" s="129"/>
-      <c r="D67" s="129"/>
-      <c r="E67" s="129"/>
-      <c r="F67" s="129"/>
-      <c r="G67" s="129"/>
-      <c r="H67" s="130"/>
-      <c r="I67" s="128"/>
-      <c r="J67" s="129"/>
-      <c r="K67" s="129"/>
-      <c r="L67" s="129"/>
-      <c r="M67" s="129"/>
-      <c r="N67" s="129"/>
-      <c r="O67" s="129"/>
-      <c r="P67" s="130"/>
+      <c r="A67" s="122"/>
+      <c r="B67" s="123"/>
+      <c r="C67" s="123"/>
+      <c r="D67" s="123"/>
+      <c r="E67" s="123"/>
+      <c r="F67" s="123"/>
+      <c r="G67" s="123"/>
+      <c r="H67" s="124"/>
+      <c r="I67" s="122"/>
+      <c r="J67" s="123"/>
+      <c r="K67" s="123"/>
+      <c r="L67" s="123"/>
+      <c r="M67" s="123"/>
+      <c r="N67" s="123"/>
+      <c r="O67" s="123"/>
+      <c r="P67" s="124"/>
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="A1:H2"/>
+    <mergeCell ref="I14:P14"/>
+    <mergeCell ref="I11:I13"/>
+    <mergeCell ref="I1:P2"/>
+    <mergeCell ref="O3:P3"/>
+    <mergeCell ref="I4:I7"/>
+    <mergeCell ref="A14:H14"/>
+    <mergeCell ref="A11:A13"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="J11:P13"/>
+    <mergeCell ref="J4:P7"/>
+    <mergeCell ref="A8:A10"/>
+    <mergeCell ref="I8:I10"/>
+    <mergeCell ref="J8:P10"/>
+    <mergeCell ref="B4:H7"/>
+    <mergeCell ref="B8:H10"/>
+    <mergeCell ref="B11:H13"/>
     <mergeCell ref="I51:P67"/>
     <mergeCell ref="A15:H31"/>
     <mergeCell ref="A33:H49"/>
@@ -8309,24 +8341,6 @@
     <mergeCell ref="I32:P32"/>
     <mergeCell ref="I33:P49"/>
     <mergeCell ref="I50:P50"/>
-    <mergeCell ref="J11:P13"/>
-    <mergeCell ref="J4:P7"/>
-    <mergeCell ref="A8:A10"/>
-    <mergeCell ref="I8:I10"/>
-    <mergeCell ref="J8:P10"/>
-    <mergeCell ref="B4:H7"/>
-    <mergeCell ref="B8:H10"/>
-    <mergeCell ref="B11:H13"/>
-    <mergeCell ref="A1:H2"/>
-    <mergeCell ref="I14:P14"/>
-    <mergeCell ref="I11:I13"/>
-    <mergeCell ref="I1:P2"/>
-    <mergeCell ref="O3:P3"/>
-    <mergeCell ref="I4:I7"/>
-    <mergeCell ref="A14:H14"/>
-    <mergeCell ref="A11:A13"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="A4:A7"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <printOptions horizontalCentered="1"/>
@@ -8344,4355 +8358,4355 @@
   <dimension ref="A1:N326"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="1.75" style="16" customWidth="1"/>
-    <col min="2" max="2" width="1.375" style="16" customWidth="1"/>
-    <col min="3" max="3" width="3.375" style="16" customWidth="1"/>
-    <col min="4" max="4" width="22.5" style="16" customWidth="1"/>
-    <col min="5" max="5" width="10.75" style="16" customWidth="1"/>
-    <col min="6" max="6" width="14.5" style="16" customWidth="1"/>
-    <col min="7" max="7" width="22.125" style="16" customWidth="1"/>
-    <col min="8" max="8" width="16" style="16" customWidth="1"/>
-    <col min="9" max="9" width="28.875" style="16" customWidth="1"/>
-    <col min="10" max="10" width="3.375" style="16" customWidth="1"/>
-    <col min="11" max="16384" width="9" style="16"/>
+    <col min="1" max="1" width="1.75" style="14" customWidth="1"/>
+    <col min="2" max="2" width="1.375" style="14" customWidth="1"/>
+    <col min="3" max="3" width="3.375" style="14" customWidth="1"/>
+    <col min="4" max="4" width="22.5" style="14" customWidth="1"/>
+    <col min="5" max="5" width="10.75" style="14" customWidth="1"/>
+    <col min="6" max="6" width="14.5" style="14" customWidth="1"/>
+    <col min="7" max="7" width="22.125" style="14" customWidth="1"/>
+    <col min="8" max="8" width="16" style="14" customWidth="1"/>
+    <col min="9" max="9" width="28.875" style="14" customWidth="1"/>
+    <col min="10" max="10" width="3.375" style="14" customWidth="1"/>
+    <col min="11" max="16384" width="9" style="14"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18.75" customHeight="1">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="110">
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
+      <c r="H1" s="104">
         <v>45916</v>
       </c>
-      <c r="I1" s="110"/>
-      <c r="J1" s="15"/>
+      <c r="I1" s="104"/>
+      <c r="J1" s="13"/>
     </row>
     <row r="2" spans="1:10" ht="21">
-      <c r="A2" s="13"/>
-      <c r="B2" s="13"/>
-      <c r="C2" s="13" t="s">
+      <c r="A2" s="11"/>
+      <c r="B2" s="11"/>
+      <c r="C2" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="D2" s="13"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
-      <c r="H2" s="111" t="s">
+      <c r="D2" s="11"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="12"/>
+      <c r="G2" s="12"/>
+      <c r="H2" s="105" t="s">
         <v>62</v>
       </c>
-      <c r="I2" s="111"/>
-      <c r="J2" s="17"/>
+      <c r="I2" s="105"/>
+      <c r="J2" s="15"/>
     </row>
     <row r="3" spans="1:10">
-      <c r="A3" s="14"/>
-      <c r="B3" s="14"/>
-      <c r="C3" s="14"/>
-      <c r="D3" s="14"/>
-      <c r="E3" s="14"/>
-      <c r="F3" s="14"/>
-      <c r="G3" s="14"/>
-      <c r="H3" s="111" t="s">
+      <c r="A3" s="12"/>
+      <c r="B3" s="12"/>
+      <c r="C3" s="12"/>
+      <c r="D3" s="12"/>
+      <c r="E3" s="12"/>
+      <c r="F3" s="12"/>
+      <c r="G3" s="12"/>
+      <c r="H3" s="105" t="s">
         <v>63</v>
       </c>
-      <c r="I3" s="111"/>
-      <c r="J3" s="17"/>
+      <c r="I3" s="105"/>
+      <c r="J3" s="15"/>
     </row>
     <row r="4" spans="1:10" ht="6.75" customHeight="1">
-      <c r="A4" s="14"/>
-      <c r="B4" s="14"/>
-      <c r="C4" s="14"/>
-      <c r="D4" s="14"/>
-      <c r="E4" s="14"/>
-      <c r="F4" s="14"/>
-      <c r="G4" s="14"/>
-      <c r="H4" s="14"/>
-      <c r="I4" s="14"/>
-      <c r="J4" s="14"/>
+      <c r="A4" s="12"/>
+      <c r="B4" s="12"/>
+      <c r="C4" s="12"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="12"/>
+      <c r="G4" s="12"/>
+      <c r="H4" s="12"/>
+      <c r="I4" s="12"/>
+      <c r="J4" s="12"/>
     </row>
     <row r="5" spans="1:10" ht="19.149999999999999" customHeight="1">
-      <c r="A5" s="14"/>
-      <c r="B5" s="14"/>
-      <c r="C5" s="14"/>
-      <c r="D5" s="14"/>
-      <c r="E5" s="14"/>
-      <c r="F5" s="14"/>
-      <c r="G5" s="14"/>
-      <c r="H5" s="14"/>
-      <c r="I5" s="14"/>
-      <c r="J5" s="14"/>
+      <c r="A5" s="12"/>
+      <c r="B5" s="12"/>
+      <c r="C5" s="12"/>
+      <c r="D5" s="12"/>
+      <c r="E5" s="12"/>
+      <c r="F5" s="12"/>
+      <c r="G5" s="12"/>
+      <c r="H5" s="12"/>
+      <c r="I5" s="12"/>
+      <c r="J5" s="12"/>
     </row>
     <row r="6" spans="1:10" ht="25.5">
-      <c r="A6" s="14"/>
-      <c r="B6" s="18" t="s">
+      <c r="A6" s="12"/>
+      <c r="B6" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="C6" s="19"/>
-      <c r="D6" s="19"/>
-      <c r="E6" s="19"/>
-      <c r="F6" s="14"/>
-      <c r="G6" s="14"/>
-      <c r="H6" s="14"/>
-      <c r="I6" s="14"/>
-      <c r="J6" s="14"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="17"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="12"/>
+      <c r="H6" s="12"/>
+      <c r="I6" s="12"/>
+      <c r="J6" s="12"/>
     </row>
     <row r="7" spans="1:10" ht="25.5">
-      <c r="A7" s="14"/>
-      <c r="B7" s="18"/>
-      <c r="C7" s="19"/>
-      <c r="D7" s="19"/>
-      <c r="E7" s="19"/>
-      <c r="F7" s="14"/>
-      <c r="G7" s="14"/>
-      <c r="H7" s="14"/>
-      <c r="I7" s="14"/>
-      <c r="J7" s="14"/>
-    </row>
-    <row r="8" spans="1:10" s="24" customFormat="1" ht="18" customHeight="1">
-      <c r="A8" s="20"/>
-      <c r="B8" s="21"/>
-      <c r="C8" s="22"/>
-      <c r="D8" s="21"/>
-      <c r="E8" s="21"/>
-      <c r="F8" s="21"/>
-      <c r="G8" s="21"/>
-      <c r="H8" s="21"/>
-      <c r="I8" s="21"/>
-      <c r="J8" s="23"/>
-    </row>
-    <row r="9" spans="1:10" s="24" customFormat="1" ht="17.649999999999999" customHeight="1">
-      <c r="A9" s="25" t="s">
+      <c r="A7" s="12"/>
+      <c r="B7" s="16"/>
+      <c r="C7" s="17"/>
+      <c r="D7" s="17"/>
+      <c r="E7" s="17"/>
+      <c r="F7" s="12"/>
+      <c r="G7" s="12"/>
+      <c r="H7" s="12"/>
+      <c r="I7" s="12"/>
+      <c r="J7" s="12"/>
+    </row>
+    <row r="8" spans="1:10" s="22" customFormat="1" ht="18" customHeight="1">
+      <c r="A8" s="18"/>
+      <c r="B8" s="19"/>
+      <c r="C8" s="20"/>
+      <c r="D8" s="19"/>
+      <c r="E8" s="19"/>
+      <c r="F8" s="19"/>
+      <c r="G8" s="19"/>
+      <c r="H8" s="19"/>
+      <c r="I8" s="19"/>
+      <c r="J8" s="21"/>
+    </row>
+    <row r="9" spans="1:10" s="22" customFormat="1" ht="17.649999999999999" customHeight="1">
+      <c r="A9" s="23" t="s">
         <v>65</v>
       </c>
-      <c r="B9" s="21"/>
-      <c r="C9" s="22"/>
-      <c r="D9" s="21"/>
-      <c r="E9" s="21"/>
-      <c r="F9" s="21"/>
-      <c r="G9" s="26"/>
-      <c r="H9" s="26"/>
-      <c r="I9" s="21"/>
-      <c r="J9" s="23"/>
-    </row>
-    <row r="10" spans="1:10" s="24" customFormat="1" ht="17.649999999999999" customHeight="1">
-      <c r="A10" s="27"/>
-      <c r="B10" s="27"/>
-      <c r="C10" s="28" t="s">
+      <c r="B9" s="19"/>
+      <c r="C9" s="20"/>
+      <c r="D9" s="19"/>
+      <c r="E9" s="19"/>
+      <c r="F9" s="19"/>
+      <c r="G9" s="24"/>
+      <c r="H9" s="24"/>
+      <c r="I9" s="19"/>
+      <c r="J9" s="21"/>
+    </row>
+    <row r="10" spans="1:10" s="22" customFormat="1" ht="17.649999999999999" customHeight="1">
+      <c r="A10" s="25"/>
+      <c r="B10" s="25"/>
+      <c r="C10" s="26" t="s">
         <v>66</v>
       </c>
-      <c r="D10" s="28"/>
-      <c r="E10" s="28"/>
-      <c r="F10" s="28"/>
-      <c r="G10" s="29"/>
-      <c r="H10" s="29"/>
-      <c r="I10" s="21"/>
-      <c r="J10" s="30"/>
-    </row>
-    <row r="11" spans="1:10" s="24" customFormat="1" ht="9.6" customHeight="1">
-      <c r="A11" s="27"/>
-      <c r="B11" s="27"/>
-      <c r="C11" s="28"/>
-      <c r="D11" s="28"/>
-      <c r="E11" s="28"/>
-      <c r="F11" s="28"/>
-      <c r="G11" s="29"/>
-      <c r="H11" s="29"/>
-      <c r="I11" s="21"/>
-      <c r="J11" s="30"/>
-    </row>
-    <row r="12" spans="1:10" s="24" customFormat="1" ht="17.649999999999999" customHeight="1">
-      <c r="A12" s="25" t="s">
+      <c r="D10" s="26"/>
+      <c r="E10" s="26"/>
+      <c r="F10" s="26"/>
+      <c r="G10" s="27"/>
+      <c r="H10" s="27"/>
+      <c r="I10" s="19"/>
+      <c r="J10" s="28"/>
+    </row>
+    <row r="11" spans="1:10" s="22" customFormat="1" ht="9.6" customHeight="1">
+      <c r="A11" s="25"/>
+      <c r="B11" s="25"/>
+      <c r="C11" s="26"/>
+      <c r="D11" s="26"/>
+      <c r="E11" s="26"/>
+      <c r="F11" s="26"/>
+      <c r="G11" s="27"/>
+      <c r="H11" s="27"/>
+      <c r="I11" s="19"/>
+      <c r="J11" s="28"/>
+    </row>
+    <row r="12" spans="1:10" s="22" customFormat="1" ht="17.649999999999999" customHeight="1">
+      <c r="A12" s="23" t="s">
         <v>67</v>
       </c>
-      <c r="B12" s="21"/>
-      <c r="C12" s="21"/>
-      <c r="D12" s="21"/>
-      <c r="E12" s="21"/>
-      <c r="F12" s="21"/>
-      <c r="G12" s="26"/>
-      <c r="H12" s="26"/>
-      <c r="I12" s="21"/>
-      <c r="J12" s="30"/>
-    </row>
-    <row r="13" spans="1:10" s="24" customFormat="1" ht="17.649999999999999" customHeight="1">
-      <c r="A13" s="27"/>
-      <c r="B13" s="27"/>
-      <c r="C13" s="28" t="s">
+      <c r="B12" s="19"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="19"/>
+      <c r="G12" s="24"/>
+      <c r="H12" s="24"/>
+      <c r="I12" s="19"/>
+      <c r="J12" s="28"/>
+    </row>
+    <row r="13" spans="1:10" s="22" customFormat="1" ht="17.649999999999999" customHeight="1">
+      <c r="A13" s="25"/>
+      <c r="B13" s="25"/>
+      <c r="C13" s="26" t="s">
         <v>68</v>
       </c>
-      <c r="D13" s="28"/>
-      <c r="E13" s="28"/>
-      <c r="F13" s="31" t="s">
+      <c r="D13" s="26"/>
+      <c r="E13" s="26"/>
+      <c r="F13" s="29" t="s">
         <v>69</v>
       </c>
-      <c r="G13" s="32"/>
-      <c r="H13" s="33"/>
-      <c r="I13" s="33"/>
-      <c r="J13" s="21"/>
-    </row>
-    <row r="14" spans="1:10" s="24" customFormat="1" ht="17.649999999999999" customHeight="1">
-      <c r="A14" s="27"/>
-      <c r="B14" s="27"/>
-      <c r="C14" s="28" t="s">
+      <c r="G13" s="30"/>
+      <c r="H13" s="31"/>
+      <c r="I13" s="31"/>
+      <c r="J13" s="19"/>
+    </row>
+    <row r="14" spans="1:10" s="22" customFormat="1" ht="17.649999999999999" customHeight="1">
+      <c r="A14" s="25"/>
+      <c r="B14" s="25"/>
+      <c r="C14" s="26" t="s">
         <v>70</v>
       </c>
-      <c r="D14" s="28"/>
-      <c r="E14" s="28"/>
-      <c r="F14" s="31" t="s">
+      <c r="D14" s="26"/>
+      <c r="E14" s="26"/>
+      <c r="F14" s="29" t="s">
         <v>69</v>
       </c>
-      <c r="G14" s="32"/>
-      <c r="H14" s="33"/>
-      <c r="I14" s="33"/>
-      <c r="J14" s="21"/>
-    </row>
-    <row r="15" spans="1:10" s="24" customFormat="1" ht="17.649999999999999" customHeight="1">
-      <c r="A15" s="27"/>
-      <c r="B15" s="27"/>
-      <c r="C15" s="28" t="s">
+      <c r="G14" s="30"/>
+      <c r="H14" s="31"/>
+      <c r="I14" s="31"/>
+      <c r="J14" s="19"/>
+    </row>
+    <row r="15" spans="1:10" s="22" customFormat="1" ht="17.649999999999999" customHeight="1">
+      <c r="A15" s="25"/>
+      <c r="B15" s="25"/>
+      <c r="C15" s="26" t="s">
         <v>71</v>
       </c>
-      <c r="D15" s="28"/>
-      <c r="E15" s="28"/>
-      <c r="F15" s="31" t="s">
+      <c r="D15" s="26"/>
+      <c r="E15" s="26"/>
+      <c r="F15" s="29" t="s">
         <v>72</v>
       </c>
-      <c r="G15" s="32"/>
-      <c r="H15" s="33"/>
-      <c r="I15" s="33"/>
-      <c r="J15" s="21"/>
-    </row>
-    <row r="16" spans="1:10" s="24" customFormat="1" ht="17.649999999999999" customHeight="1">
-      <c r="A16" s="27"/>
-      <c r="B16" s="27"/>
-      <c r="C16" s="28" t="s">
+      <c r="G15" s="30"/>
+      <c r="H15" s="31"/>
+      <c r="I15" s="31"/>
+      <c r="J15" s="19"/>
+    </row>
+    <row r="16" spans="1:10" s="22" customFormat="1" ht="17.649999999999999" customHeight="1">
+      <c r="A16" s="25"/>
+      <c r="B16" s="25"/>
+      <c r="C16" s="26" t="s">
         <v>73</v>
       </c>
-      <c r="D16" s="28"/>
-      <c r="E16" s="28"/>
-      <c r="F16" s="31" t="s">
+      <c r="D16" s="26"/>
+      <c r="E16" s="26"/>
+      <c r="F16" s="29" t="s">
         <v>74</v>
       </c>
-      <c r="G16" s="32"/>
-      <c r="H16" s="34"/>
-      <c r="I16" s="35"/>
-      <c r="J16" s="21"/>
-    </row>
-    <row r="17" spans="1:10" s="24" customFormat="1" ht="17.649999999999999" customHeight="1">
-      <c r="A17" s="27"/>
-      <c r="B17" s="27"/>
-      <c r="C17" s="28"/>
-      <c r="D17" s="28"/>
-      <c r="E17" s="28"/>
-      <c r="F17" s="31"/>
-      <c r="G17" s="32"/>
-      <c r="H17" s="34"/>
-      <c r="I17" s="35"/>
-      <c r="J17" s="21"/>
-    </row>
-    <row r="18" spans="1:10" s="24" customFormat="1" ht="10.15" customHeight="1">
-      <c r="A18" s="27"/>
-      <c r="B18" s="27"/>
-      <c r="C18" s="27"/>
-      <c r="D18" s="27"/>
-      <c r="E18" s="27"/>
-      <c r="F18" s="27"/>
-      <c r="G18" s="36"/>
-      <c r="H18" s="26"/>
-      <c r="I18" s="21"/>
-      <c r="J18" s="21"/>
-    </row>
-    <row r="19" spans="1:10" s="24" customFormat="1" ht="17.649999999999999" customHeight="1">
-      <c r="A19" s="25" t="s">
+      <c r="G16" s="30"/>
+      <c r="H16" s="32"/>
+      <c r="I16" s="33"/>
+      <c r="J16" s="19"/>
+    </row>
+    <row r="17" spans="1:10" s="22" customFormat="1" ht="17.649999999999999" customHeight="1">
+      <c r="A17" s="25"/>
+      <c r="B17" s="25"/>
+      <c r="C17" s="26"/>
+      <c r="D17" s="26"/>
+      <c r="E17" s="26"/>
+      <c r="F17" s="29"/>
+      <c r="G17" s="30"/>
+      <c r="H17" s="32"/>
+      <c r="I17" s="33"/>
+      <c r="J17" s="19"/>
+    </row>
+    <row r="18" spans="1:10" s="22" customFormat="1" ht="10.15" customHeight="1">
+      <c r="A18" s="25"/>
+      <c r="B18" s="25"/>
+      <c r="C18" s="25"/>
+      <c r="D18" s="25"/>
+      <c r="E18" s="25"/>
+      <c r="F18" s="25"/>
+      <c r="G18" s="34"/>
+      <c r="H18" s="24"/>
+      <c r="I18" s="19"/>
+      <c r="J18" s="19"/>
+    </row>
+    <row r="19" spans="1:10" s="22" customFormat="1" ht="17.649999999999999" customHeight="1">
+      <c r="A19" s="23" t="s">
         <v>75</v>
       </c>
-      <c r="B19" s="21"/>
-      <c r="C19" s="21"/>
-      <c r="D19" s="21"/>
-      <c r="E19" s="21"/>
-      <c r="F19" s="21"/>
-      <c r="G19" s="26"/>
-      <c r="H19" s="26"/>
-      <c r="I19" s="21"/>
-      <c r="J19" s="21"/>
-    </row>
-    <row r="20" spans="1:10" s="24" customFormat="1" ht="17.649999999999999" customHeight="1">
-      <c r="A20" s="25"/>
-      <c r="B20" s="21"/>
-      <c r="D20" s="21"/>
-      <c r="E20" s="21"/>
-      <c r="F20" s="21"/>
-      <c r="G20" s="26"/>
-      <c r="H20" s="26"/>
-      <c r="I20" s="21"/>
-      <c r="J20" s="21"/>
-    </row>
-    <row r="21" spans="1:10" s="24" customFormat="1" ht="17.649999999999999" customHeight="1">
-      <c r="A21" s="25"/>
-      <c r="B21" s="21"/>
-      <c r="C21" s="28" t="s">
+      <c r="B19" s="19"/>
+      <c r="C19" s="19"/>
+      <c r="D19" s="19"/>
+      <c r="E19" s="19"/>
+      <c r="F19" s="19"/>
+      <c r="G19" s="24"/>
+      <c r="H19" s="24"/>
+      <c r="I19" s="19"/>
+      <c r="J19" s="19"/>
+    </row>
+    <row r="20" spans="1:10" s="22" customFormat="1" ht="17.649999999999999" customHeight="1">
+      <c r="A20" s="23"/>
+      <c r="B20" s="19"/>
+      <c r="D20" s="19"/>
+      <c r="E20" s="19"/>
+      <c r="F20" s="19"/>
+      <c r="G20" s="24"/>
+      <c r="H20" s="24"/>
+      <c r="I20" s="19"/>
+      <c r="J20" s="19"/>
+    </row>
+    <row r="21" spans="1:10" s="22" customFormat="1" ht="17.649999999999999" customHeight="1">
+      <c r="A21" s="23"/>
+      <c r="B21" s="19"/>
+      <c r="C21" s="26" t="s">
         <v>76</v>
       </c>
-      <c r="E21" s="21"/>
-      <c r="F21" s="21"/>
-      <c r="G21" s="26"/>
-      <c r="H21" s="26"/>
-      <c r="I21" s="21"/>
-      <c r="J21" s="21"/>
-    </row>
-    <row r="22" spans="1:10" s="24" customFormat="1" ht="16.899999999999999" customHeight="1">
-      <c r="A22" s="27"/>
-      <c r="B22" s="21"/>
-      <c r="C22" s="37"/>
-      <c r="D22" s="38"/>
-      <c r="E22" s="28"/>
-      <c r="F22" s="28"/>
-      <c r="G22" s="34"/>
-      <c r="H22" s="39"/>
-      <c r="I22" s="40"/>
-      <c r="J22" s="41"/>
+      <c r="E21" s="19"/>
+      <c r="F21" s="19"/>
+      <c r="G21" s="24"/>
+      <c r="H21" s="24"/>
+      <c r="I21" s="19"/>
+      <c r="J21" s="19"/>
+    </row>
+    <row r="22" spans="1:10" s="22" customFormat="1" ht="16.899999999999999" customHeight="1">
+      <c r="A22" s="25"/>
+      <c r="B22" s="19"/>
+      <c r="C22" s="35"/>
+      <c r="D22" s="36"/>
+      <c r="E22" s="26"/>
+      <c r="F22" s="26"/>
+      <c r="G22" s="32"/>
+      <c r="H22" s="37"/>
+      <c r="I22" s="38"/>
+      <c r="J22" s="39"/>
     </row>
     <row r="23" spans="1:10" ht="17.649999999999999" customHeight="1">
-      <c r="A23" s="25" t="s">
+      <c r="A23" s="23" t="s">
         <v>77</v>
       </c>
-      <c r="B23" s="27"/>
-      <c r="C23" s="21"/>
-      <c r="D23" s="21"/>
-      <c r="E23" s="21"/>
-      <c r="F23" s="42"/>
-      <c r="G23" s="43"/>
-      <c r="H23" s="43"/>
-      <c r="I23" s="44"/>
-      <c r="J23" s="21"/>
+      <c r="B23" s="25"/>
+      <c r="C23" s="19"/>
+      <c r="D23" s="19"/>
+      <c r="E23" s="19"/>
+      <c r="F23" s="40"/>
+      <c r="G23" s="41"/>
+      <c r="H23" s="41"/>
+      <c r="I23" s="42"/>
+      <c r="J23" s="19"/>
     </row>
     <row r="24" spans="1:10" ht="9" customHeight="1">
-      <c r="A24" s="27"/>
-      <c r="B24" s="27"/>
-      <c r="C24" s="21"/>
-      <c r="D24" s="21"/>
-      <c r="E24" s="21"/>
-      <c r="F24" s="42"/>
-      <c r="G24" s="43"/>
-      <c r="H24" s="43"/>
-      <c r="I24" s="44"/>
-      <c r="J24" s="21"/>
+      <c r="A24" s="25"/>
+      <c r="B24" s="25"/>
+      <c r="C24" s="19"/>
+      <c r="D24" s="19"/>
+      <c r="E24" s="19"/>
+      <c r="F24" s="40"/>
+      <c r="G24" s="41"/>
+      <c r="H24" s="41"/>
+      <c r="I24" s="42"/>
+      <c r="J24" s="19"/>
     </row>
     <row r="25" spans="1:10" ht="17.649999999999999" customHeight="1">
-      <c r="A25" s="21"/>
-      <c r="B25" s="45"/>
-      <c r="C25" s="20" t="s">
+      <c r="A25" s="19"/>
+      <c r="B25" s="43"/>
+      <c r="C25" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="D25" s="46"/>
-      <c r="E25" s="20"/>
-      <c r="F25" s="42"/>
-      <c r="G25" s="43"/>
-      <c r="H25" s="20"/>
-      <c r="I25" s="47"/>
-      <c r="J25" s="21"/>
+      <c r="D25" s="44"/>
+      <c r="E25" s="18"/>
+      <c r="F25" s="40"/>
+      <c r="G25" s="41"/>
+      <c r="H25" s="18"/>
+      <c r="I25" s="45"/>
+      <c r="J25" s="19"/>
     </row>
     <row r="26" spans="1:10" ht="9" customHeight="1">
-      <c r="A26" s="21"/>
-      <c r="B26" s="45"/>
-      <c r="C26" s="20"/>
-      <c r="D26" s="46"/>
-      <c r="E26" s="20"/>
-      <c r="F26" s="42"/>
-      <c r="G26" s="43"/>
-      <c r="H26" s="20"/>
-      <c r="I26" s="47"/>
-      <c r="J26" s="21"/>
+      <c r="A26" s="19"/>
+      <c r="B26" s="43"/>
+      <c r="C26" s="18"/>
+      <c r="D26" s="44"/>
+      <c r="E26" s="18"/>
+      <c r="F26" s="40"/>
+      <c r="G26" s="41"/>
+      <c r="H26" s="18"/>
+      <c r="I26" s="45"/>
+      <c r="J26" s="19"/>
     </row>
     <row r="27" spans="1:10" ht="17.649999999999999" customHeight="1">
-      <c r="A27" s="21"/>
-      <c r="B27" s="45"/>
-      <c r="C27" s="20" t="s">
+      <c r="A27" s="19"/>
+      <c r="B27" s="43"/>
+      <c r="C27" s="18" t="s">
         <v>79</v>
       </c>
-      <c r="D27" s="20"/>
-      <c r="E27" s="20"/>
-      <c r="F27" s="42"/>
-      <c r="G27" s="43"/>
-      <c r="H27" s="43"/>
-      <c r="I27" s="47"/>
-      <c r="J27" s="21"/>
+      <c r="D27" s="18"/>
+      <c r="E27" s="18"/>
+      <c r="F27" s="40"/>
+      <c r="G27" s="41"/>
+      <c r="H27" s="41"/>
+      <c r="I27" s="45"/>
+      <c r="J27" s="19"/>
     </row>
     <row r="28" spans="1:10" ht="17.649999999999999" customHeight="1">
-      <c r="A28" s="21"/>
-      <c r="B28" s="45"/>
-      <c r="C28" s="20"/>
-      <c r="D28" s="28" t="s">
+      <c r="A28" s="19"/>
+      <c r="B28" s="43"/>
+      <c r="C28" s="18"/>
+      <c r="D28" s="26" t="s">
         <v>80</v>
       </c>
-      <c r="E28" s="20"/>
-      <c r="F28" s="42"/>
-      <c r="G28" s="43"/>
-      <c r="H28" s="43"/>
-      <c r="I28" s="47"/>
-      <c r="J28" s="21"/>
+      <c r="E28" s="18"/>
+      <c r="F28" s="40"/>
+      <c r="G28" s="41"/>
+      <c r="H28" s="41"/>
+      <c r="I28" s="45"/>
+      <c r="J28" s="19"/>
     </row>
     <row r="29" spans="1:10" ht="9.6" customHeight="1">
-      <c r="A29" s="21"/>
-      <c r="B29" s="45"/>
-      <c r="C29" s="20"/>
-      <c r="D29" s="28"/>
-      <c r="E29" s="20"/>
-      <c r="F29" s="42"/>
-      <c r="G29" s="43"/>
-      <c r="H29" s="43"/>
-      <c r="I29" s="47"/>
-      <c r="J29" s="21"/>
+      <c r="A29" s="19"/>
+      <c r="B29" s="43"/>
+      <c r="C29" s="18"/>
+      <c r="D29" s="26"/>
+      <c r="E29" s="18"/>
+      <c r="F29" s="40"/>
+      <c r="G29" s="41"/>
+      <c r="H29" s="41"/>
+      <c r="I29" s="45"/>
+      <c r="J29" s="19"/>
     </row>
     <row r="30" spans="1:10" ht="17.649999999999999" customHeight="1">
-      <c r="A30" s="21"/>
-      <c r="B30" s="45"/>
-      <c r="C30" s="20" t="s">
+      <c r="A30" s="19"/>
+      <c r="B30" s="43"/>
+      <c r="C30" s="18" t="s">
         <v>81</v>
       </c>
-      <c r="D30" s="20"/>
-      <c r="E30" s="20"/>
-      <c r="F30" s="42"/>
-      <c r="G30" s="43"/>
-      <c r="H30" s="43"/>
-      <c r="I30" s="47"/>
-      <c r="J30" s="21"/>
+      <c r="D30" s="18"/>
+      <c r="E30" s="18"/>
+      <c r="F30" s="40"/>
+      <c r="G30" s="41"/>
+      <c r="H30" s="41"/>
+      <c r="I30" s="45"/>
+      <c r="J30" s="19"/>
     </row>
     <row r="31" spans="1:10" ht="17.649999999999999" customHeight="1">
-      <c r="A31" s="21"/>
-      <c r="B31" s="45"/>
-      <c r="C31" s="20"/>
-      <c r="D31" s="28" t="s">
+      <c r="A31" s="19"/>
+      <c r="B31" s="43"/>
+      <c r="C31" s="18"/>
+      <c r="D31" s="26" t="s">
         <v>82</v>
       </c>
-      <c r="E31" s="20"/>
-      <c r="F31" s="42"/>
-      <c r="G31" s="43"/>
-      <c r="H31" s="43"/>
-      <c r="I31" s="47"/>
-      <c r="J31" s="21"/>
+      <c r="E31" s="18"/>
+      <c r="F31" s="40"/>
+      <c r="G31" s="41"/>
+      <c r="H31" s="41"/>
+      <c r="I31" s="45"/>
+      <c r="J31" s="19"/>
     </row>
     <row r="32" spans="1:10" ht="17.649999999999999" customHeight="1">
-      <c r="A32" s="21"/>
-      <c r="B32" s="45"/>
-      <c r="C32" s="20"/>
-      <c r="D32" s="28" t="s">
+      <c r="A32" s="19"/>
+      <c r="B32" s="43"/>
+      <c r="C32" s="18"/>
+      <c r="D32" s="26" t="s">
         <v>83</v>
       </c>
-      <c r="E32" s="20"/>
-      <c r="F32" s="42"/>
-      <c r="G32" s="43"/>
-      <c r="H32" s="43"/>
-      <c r="I32" s="47"/>
-      <c r="J32" s="21"/>
+      <c r="E32" s="18"/>
+      <c r="F32" s="40"/>
+      <c r="G32" s="41"/>
+      <c r="H32" s="41"/>
+      <c r="I32" s="45"/>
+      <c r="J32" s="19"/>
     </row>
     <row r="33" spans="1:10" ht="17.649999999999999" customHeight="1">
-      <c r="A33" s="21"/>
-      <c r="B33" s="45"/>
-      <c r="C33" s="20"/>
-      <c r="D33" s="28" t="s">
+      <c r="A33" s="19"/>
+      <c r="B33" s="43"/>
+      <c r="C33" s="18"/>
+      <c r="D33" s="26" t="s">
         <v>84</v>
       </c>
-      <c r="E33" s="20"/>
-      <c r="F33" s="42"/>
-      <c r="G33" s="43"/>
-      <c r="H33" s="43"/>
-      <c r="I33" s="47"/>
-      <c r="J33" s="21"/>
+      <c r="E33" s="18"/>
+      <c r="F33" s="40"/>
+      <c r="G33" s="41"/>
+      <c r="H33" s="41"/>
+      <c r="I33" s="45"/>
+      <c r="J33" s="19"/>
     </row>
     <row r="34" spans="1:10" ht="9.6" customHeight="1">
-      <c r="A34" s="21"/>
-      <c r="B34" s="45"/>
-      <c r="C34" s="20"/>
-      <c r="D34" s="28"/>
-      <c r="E34" s="20"/>
-      <c r="F34" s="42"/>
-      <c r="H34" s="43"/>
-      <c r="I34" s="47"/>
-      <c r="J34" s="21"/>
+      <c r="A34" s="19"/>
+      <c r="B34" s="43"/>
+      <c r="C34" s="18"/>
+      <c r="D34" s="26"/>
+      <c r="E34" s="18"/>
+      <c r="F34" s="40"/>
+      <c r="H34" s="41"/>
+      <c r="I34" s="45"/>
+      <c r="J34" s="19"/>
     </row>
     <row r="35" spans="1:10" ht="17.649999999999999" customHeight="1">
-      <c r="A35" s="21"/>
-      <c r="B35" s="45"/>
-      <c r="C35" s="20" t="s">
+      <c r="A35" s="19"/>
+      <c r="B35" s="43"/>
+      <c r="C35" s="18" t="s">
         <v>85</v>
       </c>
-      <c r="D35" s="20"/>
-      <c r="E35" s="20"/>
-      <c r="F35" s="42"/>
-      <c r="G35" s="43"/>
-      <c r="H35" s="43"/>
-      <c r="I35" s="47"/>
-      <c r="J35" s="21"/>
+      <c r="D35" s="18"/>
+      <c r="E35" s="18"/>
+      <c r="F35" s="40"/>
+      <c r="G35" s="41"/>
+      <c r="H35" s="41"/>
+      <c r="I35" s="45"/>
+      <c r="J35" s="19"/>
     </row>
     <row r="36" spans="1:10" ht="17.649999999999999" customHeight="1">
-      <c r="A36" s="21"/>
-      <c r="B36" s="45"/>
-      <c r="C36" s="20"/>
-      <c r="D36" s="28" t="s">
+      <c r="A36" s="19"/>
+      <c r="B36" s="43"/>
+      <c r="C36" s="18"/>
+      <c r="D36" s="26" t="s">
         <v>86</v>
       </c>
-      <c r="E36" s="20"/>
-      <c r="F36" s="42"/>
-      <c r="G36" s="43"/>
-      <c r="H36" s="43"/>
-      <c r="I36" s="47"/>
-      <c r="J36" s="21"/>
+      <c r="E36" s="18"/>
+      <c r="F36" s="40"/>
+      <c r="G36" s="41"/>
+      <c r="H36" s="41"/>
+      <c r="I36" s="45"/>
+      <c r="J36" s="19"/>
     </row>
     <row r="37" spans="1:10" ht="17.649999999999999" customHeight="1">
-      <c r="A37" s="21"/>
-      <c r="B37" s="45"/>
-      <c r="C37" s="20"/>
-      <c r="D37" s="28" t="s">
+      <c r="A37" s="19"/>
+      <c r="B37" s="43"/>
+      <c r="C37" s="18"/>
+      <c r="D37" s="26" t="s">
         <v>87</v>
       </c>
-      <c r="E37" s="20"/>
-      <c r="F37" s="42"/>
-      <c r="G37" s="43"/>
-      <c r="H37" s="43"/>
-      <c r="I37" s="47"/>
-      <c r="J37" s="21"/>
+      <c r="E37" s="18"/>
+      <c r="F37" s="40"/>
+      <c r="G37" s="41"/>
+      <c r="H37" s="41"/>
+      <c r="I37" s="45"/>
+      <c r="J37" s="19"/>
     </row>
     <row r="38" spans="1:10" ht="7.9" customHeight="1">
-      <c r="A38" s="21"/>
-      <c r="B38" s="45"/>
-      <c r="C38" s="20"/>
-      <c r="D38" s="28"/>
-      <c r="E38" s="20"/>
-      <c r="F38" s="42"/>
-      <c r="G38" s="43"/>
-      <c r="H38" s="43"/>
-      <c r="I38" s="47"/>
-      <c r="J38" s="21"/>
+      <c r="A38" s="19"/>
+      <c r="B38" s="43"/>
+      <c r="C38" s="18"/>
+      <c r="D38" s="26"/>
+      <c r="E38" s="18"/>
+      <c r="F38" s="40"/>
+      <c r="G38" s="41"/>
+      <c r="H38" s="41"/>
+      <c r="I38" s="45"/>
+      <c r="J38" s="19"/>
     </row>
     <row r="39" spans="1:10" ht="17.649999999999999" customHeight="1">
-      <c r="A39" s="21"/>
-      <c r="B39" s="45"/>
-      <c r="C39" s="20" t="s">
+      <c r="A39" s="19"/>
+      <c r="B39" s="43"/>
+      <c r="C39" s="18" t="s">
         <v>88</v>
       </c>
-      <c r="D39" s="20"/>
-      <c r="E39" s="20"/>
-      <c r="F39" s="42"/>
-      <c r="G39" s="43"/>
-      <c r="H39" s="43"/>
-      <c r="I39" s="47"/>
-      <c r="J39" s="21"/>
+      <c r="D39" s="18"/>
+      <c r="E39" s="18"/>
+      <c r="F39" s="40"/>
+      <c r="G39" s="41"/>
+      <c r="H39" s="41"/>
+      <c r="I39" s="45"/>
+      <c r="J39" s="19"/>
     </row>
     <row r="40" spans="1:10" ht="9.6" customHeight="1">
-      <c r="A40" s="21"/>
-      <c r="B40" s="45"/>
-      <c r="C40" s="45"/>
-      <c r="D40" s="45"/>
-      <c r="E40" s="20"/>
-      <c r="F40" s="42"/>
-      <c r="G40" s="43"/>
-      <c r="H40" s="43"/>
-      <c r="I40" s="47"/>
-      <c r="J40" s="21"/>
+      <c r="A40" s="19"/>
+      <c r="B40" s="43"/>
+      <c r="C40" s="43"/>
+      <c r="D40" s="43"/>
+      <c r="E40" s="18"/>
+      <c r="F40" s="40"/>
+      <c r="G40" s="41"/>
+      <c r="H40" s="41"/>
+      <c r="I40" s="45"/>
+      <c r="J40" s="19"/>
     </row>
     <row r="41" spans="1:10" ht="17.649999999999999" customHeight="1">
-      <c r="A41" s="21"/>
-      <c r="B41" s="27"/>
-      <c r="C41" s="28" t="s">
+      <c r="A41" s="19"/>
+      <c r="B41" s="25"/>
+      <c r="C41" s="26" t="s">
         <v>89</v>
       </c>
-      <c r="D41" s="28"/>
-      <c r="E41" s="21"/>
-      <c r="F41" s="42"/>
-      <c r="G41" s="43"/>
-      <c r="H41" s="43"/>
-      <c r="I41" s="47"/>
-      <c r="J41" s="21"/>
+      <c r="D41" s="26"/>
+      <c r="E41" s="19"/>
+      <c r="F41" s="40"/>
+      <c r="G41" s="41"/>
+      <c r="H41" s="41"/>
+      <c r="I41" s="45"/>
+      <c r="J41" s="19"/>
     </row>
     <row r="42" spans="1:10" ht="17.649999999999999" customHeight="1">
-      <c r="A42" s="21"/>
-      <c r="B42" s="27"/>
-      <c r="C42" s="28"/>
-      <c r="D42" s="28" t="s">
+      <c r="A42" s="19"/>
+      <c r="B42" s="25"/>
+      <c r="C42" s="26"/>
+      <c r="D42" s="26" t="s">
         <v>90</v>
       </c>
-      <c r="E42" s="21"/>
-      <c r="F42" s="42"/>
-      <c r="G42" s="43"/>
-      <c r="H42" s="43"/>
-      <c r="I42" s="47"/>
-      <c r="J42" s="21"/>
+      <c r="E42" s="19"/>
+      <c r="F42" s="40"/>
+      <c r="G42" s="41"/>
+      <c r="H42" s="41"/>
+      <c r="I42" s="45"/>
+      <c r="J42" s="19"/>
     </row>
     <row r="43" spans="1:10" ht="17.649999999999999" customHeight="1">
-      <c r="A43" s="21"/>
-      <c r="B43" s="27"/>
-      <c r="C43" s="28"/>
-      <c r="D43" s="28"/>
-      <c r="E43" s="21"/>
-      <c r="F43" s="42"/>
-      <c r="G43" s="43"/>
-      <c r="H43" s="43"/>
-      <c r="I43" s="47"/>
-      <c r="J43" s="21"/>
+      <c r="A43" s="19"/>
+      <c r="B43" s="25"/>
+      <c r="C43" s="26"/>
+      <c r="D43" s="26"/>
+      <c r="E43" s="19"/>
+      <c r="F43" s="40"/>
+      <c r="G43" s="41"/>
+      <c r="H43" s="41"/>
+      <c r="I43" s="45"/>
+      <c r="J43" s="19"/>
     </row>
     <row r="44" spans="1:10" ht="17.649999999999999" customHeight="1">
-      <c r="A44" s="21"/>
-      <c r="B44" s="27"/>
-      <c r="C44" s="28"/>
-      <c r="D44" s="28"/>
-      <c r="E44" s="21"/>
-      <c r="F44" s="42"/>
-      <c r="G44" s="43"/>
-      <c r="H44" s="43"/>
-      <c r="I44" s="47"/>
-      <c r="J44" s="21"/>
+      <c r="A44" s="19"/>
+      <c r="B44" s="25"/>
+      <c r="C44" s="26"/>
+      <c r="D44" s="26"/>
+      <c r="E44" s="19"/>
+      <c r="F44" s="40"/>
+      <c r="G44" s="41"/>
+      <c r="H44" s="41"/>
+      <c r="I44" s="45"/>
+      <c r="J44" s="19"/>
     </row>
     <row r="45" spans="1:10" ht="17.649999999999999" customHeight="1">
-      <c r="A45" s="21"/>
-      <c r="B45" s="27"/>
-      <c r="C45" s="28"/>
-      <c r="D45" s="28"/>
-      <c r="E45" s="21"/>
-      <c r="F45" s="42"/>
-      <c r="G45" s="43"/>
-      <c r="H45" s="43"/>
-      <c r="I45" s="47"/>
-      <c r="J45" s="21"/>
+      <c r="A45" s="19"/>
+      <c r="B45" s="25"/>
+      <c r="C45" s="26"/>
+      <c r="D45" s="26"/>
+      <c r="E45" s="19"/>
+      <c r="F45" s="40"/>
+      <c r="G45" s="41"/>
+      <c r="H45" s="41"/>
+      <c r="I45" s="45"/>
+      <c r="J45" s="19"/>
     </row>
     <row r="46" spans="1:10" ht="17.649999999999999" customHeight="1">
-      <c r="A46" s="21"/>
-      <c r="B46" s="27"/>
-      <c r="C46" s="28"/>
-      <c r="D46" s="28"/>
-      <c r="E46" s="21"/>
-      <c r="F46" s="42"/>
-      <c r="G46" s="43"/>
-      <c r="H46" s="43"/>
-      <c r="I46" s="47"/>
-      <c r="J46" s="21"/>
+      <c r="A46" s="19"/>
+      <c r="B46" s="25"/>
+      <c r="C46" s="26"/>
+      <c r="D46" s="26"/>
+      <c r="E46" s="19"/>
+      <c r="F46" s="40"/>
+      <c r="G46" s="41"/>
+      <c r="H46" s="41"/>
+      <c r="I46" s="45"/>
+      <c r="J46" s="19"/>
     </row>
     <row r="47" spans="1:10" ht="17.649999999999999" customHeight="1">
-      <c r="A47" s="25" t="s">
+      <c r="A47" s="23" t="s">
         <v>91</v>
       </c>
-      <c r="B47" s="27"/>
-      <c r="C47" s="21"/>
-      <c r="D47" s="27"/>
-      <c r="E47" s="21"/>
-      <c r="F47" s="21"/>
-      <c r="G47" s="21"/>
-      <c r="H47" s="21"/>
-      <c r="I47" s="21"/>
-      <c r="J47" s="21"/>
+      <c r="B47" s="25"/>
+      <c r="C47" s="19"/>
+      <c r="D47" s="25"/>
+      <c r="E47" s="19"/>
+      <c r="F47" s="19"/>
+      <c r="G47" s="19"/>
+      <c r="H47" s="19"/>
+      <c r="I47" s="19"/>
+      <c r="J47" s="19"/>
     </row>
     <row r="48" spans="1:10" ht="17.649999999999999" customHeight="1">
-      <c r="A48" s="20"/>
-      <c r="B48" s="20" t="s">
+      <c r="A48" s="18"/>
+      <c r="B48" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="C48" s="42"/>
-      <c r="D48" s="42"/>
-      <c r="E48" s="42"/>
-      <c r="F48" s="21"/>
-      <c r="G48" s="21"/>
-      <c r="H48" s="21"/>
-      <c r="I48" s="21"/>
-      <c r="J48" s="21"/>
+      <c r="C48" s="40"/>
+      <c r="D48" s="40"/>
+      <c r="E48" s="40"/>
+      <c r="F48" s="19"/>
+      <c r="G48" s="19"/>
+      <c r="H48" s="19"/>
+      <c r="I48" s="19"/>
+      <c r="J48" s="19"/>
     </row>
     <row r="49" spans="1:10" ht="10.15" customHeight="1">
-      <c r="A49" s="20"/>
-      <c r="B49" s="20"/>
-      <c r="C49" s="42"/>
-      <c r="D49" s="42"/>
-      <c r="E49" s="42"/>
-      <c r="F49" s="21"/>
-      <c r="G49" s="21"/>
-      <c r="H49" s="21"/>
-      <c r="I49" s="21"/>
-      <c r="J49" s="21"/>
+      <c r="A49" s="18"/>
+      <c r="B49" s="18"/>
+      <c r="C49" s="40"/>
+      <c r="D49" s="40"/>
+      <c r="E49" s="40"/>
+      <c r="F49" s="19"/>
+      <c r="G49" s="19"/>
+      <c r="H49" s="19"/>
+      <c r="I49" s="19"/>
+      <c r="J49" s="19"/>
     </row>
     <row r="50" spans="1:10" ht="17.649999999999999" customHeight="1">
-      <c r="A50" s="20"/>
-      <c r="B50" s="20" t="s">
+      <c r="A50" s="18"/>
+      <c r="B50" s="18" t="s">
         <v>93</v>
       </c>
-      <c r="C50" s="27"/>
-      <c r="D50" s="27"/>
-      <c r="E50" s="27"/>
-      <c r="F50" s="27"/>
-      <c r="G50" s="27"/>
-      <c r="H50" s="27"/>
-      <c r="I50" s="21"/>
-      <c r="J50" s="21"/>
+      <c r="C50" s="25"/>
+      <c r="D50" s="25"/>
+      <c r="E50" s="25"/>
+      <c r="F50" s="25"/>
+      <c r="G50" s="25"/>
+      <c r="H50" s="25"/>
+      <c r="I50" s="19"/>
+      <c r="J50" s="19"/>
     </row>
     <row r="51" spans="1:10" ht="17.649999999999999" customHeight="1">
-      <c r="A51" s="20"/>
-      <c r="B51" s="27"/>
-      <c r="C51" s="27"/>
-      <c r="D51" s="28" t="s">
+      <c r="A51" s="18"/>
+      <c r="B51" s="25"/>
+      <c r="C51" s="25"/>
+      <c r="D51" s="26" t="s">
         <v>94</v>
       </c>
-      <c r="E51" s="28"/>
-      <c r="G51" s="28" t="s">
+      <c r="E51" s="26"/>
+      <c r="G51" s="26" t="s">
         <v>95</v>
       </c>
-      <c r="H51" s="21"/>
-      <c r="I51" s="21"/>
-      <c r="J51" s="21"/>
+      <c r="H51" s="19"/>
+      <c r="I51" s="19"/>
+      <c r="J51" s="19"/>
     </row>
     <row r="52" spans="1:10" ht="17.649999999999999" customHeight="1">
-      <c r="A52" s="20"/>
-      <c r="B52" s="27"/>
-      <c r="C52" s="27" t="s">
+      <c r="A52" s="18"/>
+      <c r="B52" s="25"/>
+      <c r="C52" s="25" t="s">
         <v>96</v>
       </c>
-      <c r="D52" s="32" t="s">
+      <c r="D52" s="30" t="s">
         <v>97</v>
       </c>
-      <c r="E52" s="28"/>
-      <c r="G52" s="48" t="s">
+      <c r="E52" s="26"/>
+      <c r="G52" s="46" t="s">
         <v>98</v>
       </c>
-      <c r="H52" s="21"/>
-      <c r="I52" s="21"/>
-      <c r="J52" s="21"/>
+      <c r="H52" s="19"/>
+      <c r="I52" s="19"/>
+      <c r="J52" s="19"/>
     </row>
     <row r="53" spans="1:10" ht="17.649999999999999" customHeight="1">
-      <c r="A53" s="20"/>
-      <c r="B53" s="27"/>
-      <c r="C53" s="27" t="s">
+      <c r="A53" s="18"/>
+      <c r="B53" s="25"/>
+      <c r="C53" s="25" t="s">
         <v>96</v>
       </c>
-      <c r="D53" s="28" t="s">
+      <c r="D53" s="26" t="s">
         <v>99</v>
       </c>
-      <c r="E53" s="28"/>
-      <c r="G53" s="28" t="s">
+      <c r="E53" s="26"/>
+      <c r="G53" s="26" t="s">
         <v>100</v>
       </c>
-      <c r="H53" s="21"/>
-      <c r="I53" s="21"/>
-      <c r="J53" s="21"/>
+      <c r="H53" s="19"/>
+      <c r="I53" s="19"/>
+      <c r="J53" s="19"/>
     </row>
     <row r="54" spans="1:10" ht="17.649999999999999" customHeight="1">
-      <c r="A54" s="20"/>
-      <c r="B54" s="27"/>
-      <c r="C54" s="27" t="s">
+      <c r="A54" s="18"/>
+      <c r="B54" s="25"/>
+      <c r="C54" s="25" t="s">
         <v>96</v>
       </c>
-      <c r="D54" s="28" t="s">
+      <c r="D54" s="26" t="s">
         <v>101</v>
       </c>
-      <c r="E54" s="28"/>
-      <c r="G54" s="28" t="s">
+      <c r="E54" s="26"/>
+      <c r="G54" s="26" t="s">
         <v>102</v>
       </c>
-      <c r="H54" s="21"/>
-      <c r="I54" s="21"/>
-      <c r="J54" s="21"/>
+      <c r="H54" s="19"/>
+      <c r="I54" s="19"/>
+      <c r="J54" s="19"/>
     </row>
     <row r="55" spans="1:10" ht="17.649999999999999" customHeight="1">
-      <c r="A55" s="20"/>
-      <c r="B55" s="27"/>
-      <c r="C55" s="27" t="s">
+      <c r="A55" s="18"/>
+      <c r="B55" s="25"/>
+      <c r="C55" s="25" t="s">
         <v>96</v>
       </c>
-      <c r="D55" s="28" t="s">
+      <c r="D55" s="26" t="s">
         <v>103</v>
       </c>
-      <c r="E55" s="28"/>
-      <c r="G55" s="28" t="s">
+      <c r="E55" s="26"/>
+      <c r="G55" s="26" t="s">
         <v>104</v>
       </c>
-      <c r="H55" s="21"/>
-      <c r="I55" s="21"/>
-      <c r="J55" s="21"/>
+      <c r="H55" s="19"/>
+      <c r="I55" s="19"/>
+      <c r="J55" s="19"/>
     </row>
     <row r="56" spans="1:10" ht="10.9" customHeight="1">
-      <c r="A56" s="20"/>
-      <c r="B56" s="27"/>
-      <c r="C56" s="49"/>
-      <c r="D56" s="27"/>
-      <c r="E56" s="27"/>
-      <c r="F56" s="27"/>
-      <c r="G56" s="45"/>
-      <c r="H56" s="27"/>
-      <c r="I56" s="27"/>
-      <c r="J56" s="27"/>
+      <c r="A56" s="18"/>
+      <c r="B56" s="25"/>
+      <c r="C56" s="47"/>
+      <c r="D56" s="25"/>
+      <c r="E56" s="25"/>
+      <c r="F56" s="25"/>
+      <c r="G56" s="43"/>
+      <c r="H56" s="25"/>
+      <c r="I56" s="25"/>
+      <c r="J56" s="25"/>
     </row>
     <row r="57" spans="1:10" ht="17.649999999999999" customHeight="1">
-      <c r="A57" s="20"/>
-      <c r="B57" s="20" t="s">
+      <c r="A57" s="18"/>
+      <c r="B57" s="18" t="s">
         <v>105</v>
       </c>
-      <c r="C57" s="49"/>
-      <c r="D57" s="27"/>
-      <c r="E57" s="27"/>
-      <c r="F57" s="27"/>
-      <c r="G57" s="45"/>
-      <c r="H57" s="27"/>
-      <c r="I57" s="27"/>
-      <c r="J57" s="27"/>
+      <c r="C57" s="47"/>
+      <c r="D57" s="25"/>
+      <c r="E57" s="25"/>
+      <c r="F57" s="25"/>
+      <c r="G57" s="43"/>
+      <c r="H57" s="25"/>
+      <c r="I57" s="25"/>
+      <c r="J57" s="25"/>
     </row>
     <row r="58" spans="1:10" ht="17.649999999999999" customHeight="1">
-      <c r="A58" s="21"/>
-      <c r="B58" s="28"/>
-      <c r="C58" s="50"/>
-      <c r="D58" s="28" t="s">
+      <c r="A58" s="19"/>
+      <c r="B58" s="26"/>
+      <c r="C58" s="48"/>
+      <c r="D58" s="26" t="s">
         <v>94</v>
       </c>
-      <c r="E58" s="51"/>
-      <c r="G58" s="28" t="s">
+      <c r="E58" s="49"/>
+      <c r="G58" s="26" t="s">
         <v>95</v>
       </c>
-      <c r="H58" s="28"/>
-      <c r="I58" s="27"/>
-      <c r="J58" s="27"/>
+      <c r="H58" s="26"/>
+      <c r="I58" s="25"/>
+      <c r="J58" s="25"/>
     </row>
     <row r="59" spans="1:10">
-      <c r="A59" s="52"/>
-      <c r="C59" s="28" t="s">
+      <c r="A59" s="50"/>
+      <c r="C59" s="26" t="s">
         <v>96</v>
       </c>
-      <c r="D59" s="32" t="s">
+      <c r="D59" s="30" t="s">
         <v>106</v>
       </c>
-      <c r="E59" s="32"/>
-      <c r="F59" s="32"/>
-      <c r="G59" s="32" t="s">
+      <c r="E59" s="30"/>
+      <c r="F59" s="30"/>
+      <c r="G59" s="30" t="s">
         <v>107</v>
       </c>
-      <c r="H59" s="53"/>
+      <c r="H59" s="51"/>
     </row>
     <row r="60" spans="1:10">
-      <c r="A60" s="52"/>
-      <c r="C60" s="32"/>
-      <c r="D60" s="32"/>
-      <c r="E60" s="32"/>
-      <c r="F60" s="32"/>
-      <c r="G60" s="32" t="s">
+      <c r="A60" s="50"/>
+      <c r="C60" s="30"/>
+      <c r="D60" s="30"/>
+      <c r="E60" s="30"/>
+      <c r="F60" s="30"/>
+      <c r="G60" s="30" t="s">
         <v>108</v>
       </c>
-      <c r="H60" s="53"/>
+      <c r="H60" s="51"/>
     </row>
     <row r="61" spans="1:10" ht="18" customHeight="1">
-      <c r="A61" s="52"/>
-      <c r="C61" s="32" t="s">
+      <c r="A61" s="50"/>
+      <c r="C61" s="30" t="s">
         <v>96</v>
       </c>
-      <c r="D61" s="32" t="s">
+      <c r="D61" s="30" t="s">
         <v>109</v>
       </c>
-      <c r="E61" s="32"/>
-      <c r="F61" s="32"/>
-      <c r="G61" s="32" t="s">
+      <c r="E61" s="30"/>
+      <c r="F61" s="30"/>
+      <c r="G61" s="30" t="s">
         <v>110</v>
       </c>
-      <c r="H61" s="53"/>
+      <c r="H61" s="51"/>
     </row>
     <row r="62" spans="1:10" ht="18" customHeight="1">
-      <c r="A62" s="21"/>
-      <c r="B62" s="27"/>
-      <c r="C62" s="50"/>
-      <c r="D62" s="28"/>
-      <c r="E62" s="28"/>
-      <c r="F62" s="28"/>
-      <c r="G62" s="28" t="s">
+      <c r="A62" s="19"/>
+      <c r="B62" s="25"/>
+      <c r="C62" s="48"/>
+      <c r="D62" s="26"/>
+      <c r="E62" s="26"/>
+      <c r="F62" s="26"/>
+      <c r="G62" s="26" t="s">
         <v>111</v>
       </c>
-      <c r="H62" s="54"/>
-      <c r="I62" s="21"/>
-      <c r="J62" s="21"/>
+      <c r="H62" s="52"/>
+      <c r="I62" s="19"/>
+      <c r="J62" s="19"/>
     </row>
     <row r="63" spans="1:10" ht="18" customHeight="1">
-      <c r="A63" s="21"/>
-      <c r="B63" s="27"/>
-      <c r="C63" s="50"/>
-      <c r="D63" s="28"/>
-      <c r="E63" s="28"/>
-      <c r="F63" s="28"/>
-      <c r="G63" s="28" t="s">
+      <c r="A63" s="19"/>
+      <c r="B63" s="25"/>
+      <c r="C63" s="48"/>
+      <c r="D63" s="26"/>
+      <c r="E63" s="26"/>
+      <c r="F63" s="26"/>
+      <c r="G63" s="26" t="s">
         <v>112</v>
       </c>
-      <c r="H63" s="54"/>
-      <c r="I63" s="21"/>
-      <c r="J63" s="21"/>
+      <c r="H63" s="52"/>
+      <c r="I63" s="19"/>
+      <c r="J63" s="19"/>
     </row>
     <row r="64" spans="1:10" ht="10.9" customHeight="1">
-      <c r="A64" s="21"/>
-      <c r="B64" s="27"/>
-      <c r="C64" s="49"/>
-      <c r="D64" s="27"/>
-      <c r="E64" s="27"/>
-      <c r="F64" s="27"/>
-      <c r="G64" s="45"/>
-      <c r="H64" s="27"/>
-      <c r="I64" s="21"/>
-      <c r="J64" s="21"/>
+      <c r="A64" s="19"/>
+      <c r="B64" s="25"/>
+      <c r="C64" s="47"/>
+      <c r="D64" s="25"/>
+      <c r="E64" s="25"/>
+      <c r="F64" s="25"/>
+      <c r="G64" s="43"/>
+      <c r="H64" s="25"/>
+      <c r="I64" s="19"/>
+      <c r="J64" s="19"/>
     </row>
     <row r="65" spans="1:10" ht="10.9" customHeight="1">
-      <c r="A65" s="21"/>
-      <c r="B65" s="27"/>
-      <c r="C65" s="49"/>
-      <c r="D65" s="27"/>
-      <c r="E65" s="27"/>
-      <c r="F65" s="27"/>
-      <c r="G65" s="45"/>
-      <c r="H65" s="27"/>
-      <c r="I65" s="21"/>
-      <c r="J65" s="21"/>
+      <c r="A65" s="19"/>
+      <c r="B65" s="25"/>
+      <c r="C65" s="47"/>
+      <c r="D65" s="25"/>
+      <c r="E65" s="25"/>
+      <c r="F65" s="25"/>
+      <c r="G65" s="43"/>
+      <c r="H65" s="25"/>
+      <c r="I65" s="19"/>
+      <c r="J65" s="19"/>
     </row>
     <row r="66" spans="1:10" ht="17.649999999999999" customHeight="1">
-      <c r="A66" s="21"/>
-      <c r="B66" s="20" t="s">
+      <c r="A66" s="19"/>
+      <c r="B66" s="18" t="s">
         <v>113</v>
       </c>
-      <c r="C66" s="49"/>
-      <c r="D66" s="27"/>
-      <c r="E66" s="27"/>
-      <c r="F66" s="27"/>
-      <c r="G66" s="27"/>
-      <c r="H66" s="27"/>
-      <c r="I66" s="21"/>
-      <c r="J66" s="21"/>
+      <c r="C66" s="47"/>
+      <c r="D66" s="25"/>
+      <c r="E66" s="25"/>
+      <c r="F66" s="25"/>
+      <c r="G66" s="25"/>
+      <c r="H66" s="25"/>
+      <c r="I66" s="19"/>
+      <c r="J66" s="19"/>
     </row>
     <row r="67" spans="1:10" ht="17.649999999999999" customHeight="1">
-      <c r="A67" s="21"/>
-      <c r="B67" s="27"/>
-      <c r="C67" s="50"/>
-      <c r="D67" s="28" t="s">
+      <c r="A67" s="19"/>
+      <c r="B67" s="25"/>
+      <c r="C67" s="48"/>
+      <c r="D67" s="26" t="s">
         <v>94</v>
       </c>
-      <c r="E67" s="52"/>
-      <c r="G67" s="28" t="s">
+      <c r="E67" s="50"/>
+      <c r="G67" s="26" t="s">
         <v>95</v>
       </c>
-      <c r="H67" s="27"/>
-      <c r="I67" s="21"/>
-      <c r="J67" s="21"/>
+      <c r="H67" s="25"/>
+      <c r="I67" s="19"/>
+      <c r="J67" s="19"/>
     </row>
     <row r="68" spans="1:10" ht="17.649999999999999" customHeight="1">
-      <c r="A68" s="21"/>
-      <c r="B68" s="28"/>
-      <c r="C68" s="55" t="s">
+      <c r="A68" s="19"/>
+      <c r="B68" s="26"/>
+      <c r="C68" s="53" t="s">
         <v>114</v>
       </c>
-      <c r="D68" s="28" t="s">
+      <c r="D68" s="26" t="s">
         <v>115</v>
       </c>
-      <c r="E68" s="28"/>
-      <c r="F68" s="56"/>
-      <c r="G68" s="32" t="s">
+      <c r="E68" s="26"/>
+      <c r="F68" s="54"/>
+      <c r="G68" s="30" t="s">
         <v>116</v>
       </c>
-      <c r="H68" s="28"/>
-      <c r="I68" s="28"/>
-      <c r="J68" s="27"/>
+      <c r="H68" s="26"/>
+      <c r="I68" s="26"/>
+      <c r="J68" s="25"/>
     </row>
     <row r="69" spans="1:10" ht="17.649999999999999" customHeight="1">
-      <c r="A69" s="21"/>
-      <c r="B69" s="28"/>
-      <c r="C69" s="55" t="s">
+      <c r="A69" s="19"/>
+      <c r="B69" s="26"/>
+      <c r="C69" s="53" t="s">
         <v>117</v>
       </c>
-      <c r="D69" s="32" t="s">
+      <c r="D69" s="30" t="s">
         <v>118</v>
       </c>
-      <c r="E69" s="28"/>
-      <c r="F69" s="56"/>
-      <c r="G69" s="32" t="s">
+      <c r="E69" s="26"/>
+      <c r="F69" s="54"/>
+      <c r="G69" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="H69" s="28"/>
-      <c r="I69" s="28"/>
-      <c r="J69" s="27"/>
+      <c r="H69" s="26"/>
+      <c r="I69" s="26"/>
+      <c r="J69" s="25"/>
     </row>
     <row r="70" spans="1:10" ht="17.649999999999999" customHeight="1">
-      <c r="A70" s="21"/>
-      <c r="B70" s="28"/>
-      <c r="E70" s="28"/>
-      <c r="F70" s="56"/>
-      <c r="G70" s="32" t="s">
+      <c r="A70" s="19"/>
+      <c r="B70" s="26"/>
+      <c r="E70" s="26"/>
+      <c r="F70" s="54"/>
+      <c r="G70" s="30" t="s">
         <v>120</v>
       </c>
-      <c r="H70" s="28"/>
-      <c r="I70" s="27"/>
-      <c r="J70" s="27"/>
+      <c r="H70" s="26"/>
+      <c r="I70" s="25"/>
+      <c r="J70" s="25"/>
     </row>
     <row r="71" spans="1:10" ht="17.649999999999999" customHeight="1">
-      <c r="A71" s="21"/>
-      <c r="B71" s="28"/>
-      <c r="C71" s="55" t="s">
+      <c r="A71" s="19"/>
+      <c r="B71" s="26"/>
+      <c r="C71" s="53" t="s">
         <v>121</v>
       </c>
-      <c r="D71" s="28" t="s">
+      <c r="D71" s="26" t="s">
         <v>122</v>
       </c>
-      <c r="E71" s="28"/>
-      <c r="F71" s="56"/>
-      <c r="G71" s="32" t="s">
+      <c r="E71" s="26"/>
+      <c r="F71" s="54"/>
+      <c r="G71" s="30" t="s">
         <v>123</v>
       </c>
-      <c r="H71" s="28"/>
-      <c r="I71" s="27"/>
-      <c r="J71" s="27"/>
+      <c r="H71" s="26"/>
+      <c r="I71" s="25"/>
+      <c r="J71" s="25"/>
     </row>
     <row r="72" spans="1:10" ht="17.649999999999999" customHeight="1">
-      <c r="A72" s="21"/>
-      <c r="B72" s="28"/>
-      <c r="C72" s="55"/>
-      <c r="D72" s="32"/>
-      <c r="E72" s="28"/>
-      <c r="F72" s="56"/>
-      <c r="G72" s="32" t="s">
+      <c r="A72" s="19"/>
+      <c r="B72" s="26"/>
+      <c r="C72" s="53"/>
+      <c r="D72" s="30"/>
+      <c r="E72" s="26"/>
+      <c r="F72" s="54"/>
+      <c r="G72" s="30" t="s">
         <v>124</v>
       </c>
-      <c r="H72" s="28"/>
-      <c r="I72" s="27"/>
-      <c r="J72" s="27"/>
+      <c r="H72" s="26"/>
+      <c r="I72" s="25"/>
+      <c r="J72" s="25"/>
     </row>
     <row r="73" spans="1:10" ht="17.649999999999999" customHeight="1">
-      <c r="A73" s="21"/>
-      <c r="B73" s="28"/>
-      <c r="C73" s="55"/>
-      <c r="D73" s="32"/>
-      <c r="E73" s="28"/>
-      <c r="F73" s="56"/>
-      <c r="G73" s="32" t="s">
+      <c r="A73" s="19"/>
+      <c r="B73" s="26"/>
+      <c r="C73" s="53"/>
+      <c r="D73" s="30"/>
+      <c r="E73" s="26"/>
+      <c r="F73" s="54"/>
+      <c r="G73" s="30" t="s">
         <v>125</v>
       </c>
-      <c r="H73" s="28"/>
-      <c r="I73" s="27"/>
-      <c r="J73" s="27"/>
+      <c r="H73" s="26"/>
+      <c r="I73" s="25"/>
+      <c r="J73" s="25"/>
     </row>
     <row r="74" spans="1:10" ht="10.9" customHeight="1">
-      <c r="A74" s="21"/>
-      <c r="B74" s="27"/>
-      <c r="C74" s="50"/>
-      <c r="D74" s="28"/>
-      <c r="E74" s="28"/>
-      <c r="F74" s="28"/>
-      <c r="G74" s="28"/>
-      <c r="H74" s="28"/>
-      <c r="I74" s="28"/>
-      <c r="J74" s="28"/>
+      <c r="A74" s="19"/>
+      <c r="B74" s="25"/>
+      <c r="C74" s="48"/>
+      <c r="D74" s="26"/>
+      <c r="E74" s="26"/>
+      <c r="F74" s="26"/>
+      <c r="G74" s="26"/>
+      <c r="H74" s="26"/>
+      <c r="I74" s="26"/>
+      <c r="J74" s="26"/>
     </row>
     <row r="75" spans="1:10" ht="17.649999999999999" customHeight="1">
-      <c r="A75" s="21"/>
-      <c r="B75" s="20" t="s">
+      <c r="A75" s="19"/>
+      <c r="B75" s="18" t="s">
         <v>126</v>
       </c>
-      <c r="C75" s="49"/>
-      <c r="D75" s="57"/>
-      <c r="E75" s="27"/>
-      <c r="F75" s="21"/>
-      <c r="G75" s="27"/>
-      <c r="H75" s="21"/>
-      <c r="I75" s="21"/>
-      <c r="J75" s="21"/>
+      <c r="C75" s="47"/>
+      <c r="D75" s="55"/>
+      <c r="E75" s="25"/>
+      <c r="F75" s="19"/>
+      <c r="G75" s="25"/>
+      <c r="H75" s="19"/>
+      <c r="I75" s="19"/>
+      <c r="J75" s="19"/>
     </row>
     <row r="76" spans="1:10" ht="17.649999999999999" customHeight="1">
-      <c r="A76" s="21"/>
-      <c r="B76" s="27"/>
-      <c r="C76" s="49"/>
-      <c r="D76" s="28" t="s">
+      <c r="A76" s="19"/>
+      <c r="B76" s="25"/>
+      <c r="C76" s="47"/>
+      <c r="D76" s="26" t="s">
         <v>94</v>
       </c>
-      <c r="E76" s="28"/>
-      <c r="G76" s="28" t="s">
+      <c r="E76" s="26"/>
+      <c r="G76" s="26" t="s">
         <v>95</v>
       </c>
-      <c r="H76" s="45"/>
-      <c r="I76" s="21"/>
-      <c r="J76" s="21"/>
+      <c r="H76" s="43"/>
+      <c r="I76" s="19"/>
+      <c r="J76" s="19"/>
     </row>
     <row r="77" spans="1:10" ht="17.649999999999999" customHeight="1">
-      <c r="A77" s="21"/>
-      <c r="B77" s="27"/>
-      <c r="C77" s="49" t="s">
+      <c r="A77" s="19"/>
+      <c r="B77" s="25"/>
+      <c r="C77" s="47" t="s">
         <v>96</v>
       </c>
-      <c r="D77" s="28" t="s">
+      <c r="D77" s="26" t="s">
         <v>127</v>
       </c>
-      <c r="E77" s="28"/>
-      <c r="G77" s="48" t="s">
+      <c r="E77" s="26"/>
+      <c r="G77" s="46" t="s">
         <v>128</v>
       </c>
-      <c r="H77" s="45"/>
-      <c r="I77" s="21"/>
-      <c r="J77" s="21"/>
+      <c r="H77" s="43"/>
+      <c r="I77" s="19"/>
+      <c r="J77" s="19"/>
     </row>
     <row r="78" spans="1:10" ht="17.649999999999999" customHeight="1">
-      <c r="A78" s="21"/>
-      <c r="B78" s="27"/>
-      <c r="C78" s="49" t="s">
+      <c r="A78" s="19"/>
+      <c r="B78" s="25"/>
+      <c r="C78" s="47" t="s">
         <v>96</v>
       </c>
-      <c r="D78" s="28" t="s">
+      <c r="D78" s="26" t="s">
         <v>129</v>
       </c>
-      <c r="E78" s="28"/>
-      <c r="G78" s="48" t="s">
+      <c r="E78" s="26"/>
+      <c r="G78" s="46" t="s">
         <v>130</v>
       </c>
-      <c r="H78" s="45"/>
-      <c r="I78" s="21"/>
-      <c r="J78" s="21"/>
+      <c r="H78" s="43"/>
+      <c r="I78" s="19"/>
+      <c r="J78" s="19"/>
     </row>
     <row r="79" spans="1:10" ht="17.649999999999999" customHeight="1">
-      <c r="A79" s="21"/>
-      <c r="B79" s="27"/>
-      <c r="C79" s="49" t="s">
+      <c r="A79" s="19"/>
+      <c r="B79" s="25"/>
+      <c r="C79" s="47" t="s">
         <v>96</v>
       </c>
-      <c r="D79" s="28" t="s">
+      <c r="D79" s="26" t="s">
         <v>131</v>
       </c>
-      <c r="E79" s="28"/>
-      <c r="G79" s="48" t="s">
+      <c r="E79" s="26"/>
+      <c r="G79" s="46" t="s">
         <v>132</v>
       </c>
-      <c r="H79" s="45"/>
-      <c r="I79" s="21"/>
-      <c r="J79" s="21"/>
+      <c r="H79" s="43"/>
+      <c r="I79" s="19"/>
+      <c r="J79" s="19"/>
     </row>
     <row r="80" spans="1:10" ht="17.649999999999999" customHeight="1">
-      <c r="A80" s="21"/>
-      <c r="B80" s="27"/>
-      <c r="C80" s="49" t="s">
+      <c r="A80" s="19"/>
+      <c r="B80" s="25"/>
+      <c r="C80" s="47" t="s">
         <v>96</v>
       </c>
-      <c r="D80" s="28" t="s">
+      <c r="D80" s="26" t="s">
         <v>133</v>
       </c>
-      <c r="E80" s="28"/>
-      <c r="G80" s="28" t="s">
+      <c r="E80" s="26"/>
+      <c r="G80" s="26" t="s">
         <v>102</v>
       </c>
-      <c r="H80" s="45"/>
-      <c r="I80" s="21"/>
-      <c r="J80" s="21"/>
+      <c r="H80" s="43"/>
+      <c r="I80" s="19"/>
+      <c r="J80" s="19"/>
     </row>
     <row r="81" spans="1:10" ht="17.649999999999999" customHeight="1">
-      <c r="A81" s="21"/>
-      <c r="B81" s="27"/>
-      <c r="C81" s="49" t="s">
+      <c r="A81" s="19"/>
+      <c r="B81" s="25"/>
+      <c r="C81" s="47" t="s">
         <v>96</v>
       </c>
-      <c r="D81" s="28" t="s">
+      <c r="D81" s="26" t="s">
         <v>134</v>
       </c>
-      <c r="E81" s="27"/>
-      <c r="F81" s="28"/>
-      <c r="G81" s="28" t="s">
+      <c r="E81" s="25"/>
+      <c r="F81" s="26"/>
+      <c r="G81" s="26" t="s">
         <v>100</v>
       </c>
-      <c r="H81" s="45"/>
-      <c r="I81" s="45"/>
-      <c r="J81" s="21"/>
+      <c r="H81" s="43"/>
+      <c r="I81" s="43"/>
+      <c r="J81" s="19"/>
     </row>
     <row r="82" spans="1:10" ht="17.649999999999999" customHeight="1">
-      <c r="A82" s="21"/>
-      <c r="B82" s="27"/>
-      <c r="C82" s="49" t="s">
+      <c r="A82" s="19"/>
+      <c r="B82" s="25"/>
+      <c r="C82" s="47" t="s">
         <v>96</v>
       </c>
-      <c r="D82" s="28" t="s">
+      <c r="D82" s="26" t="s">
         <v>135</v>
       </c>
-      <c r="E82" s="27"/>
-      <c r="F82" s="28"/>
-      <c r="G82" s="28" t="s">
+      <c r="E82" s="25"/>
+      <c r="F82" s="26"/>
+      <c r="G82" s="26" t="s">
         <v>136</v>
       </c>
-      <c r="H82" s="45"/>
-      <c r="I82" s="21"/>
-      <c r="J82" s="21"/>
+      <c r="H82" s="43"/>
+      <c r="I82" s="19"/>
+      <c r="J82" s="19"/>
     </row>
     <row r="83" spans="1:10" ht="17.649999999999999" customHeight="1">
-      <c r="A83" s="21"/>
-      <c r="B83" s="27"/>
-      <c r="C83" s="49" t="s">
+      <c r="A83" s="19"/>
+      <c r="B83" s="25"/>
+      <c r="C83" s="47" t="s">
         <v>96</v>
       </c>
-      <c r="D83" s="28" t="s">
+      <c r="D83" s="26" t="s">
         <v>137</v>
       </c>
-      <c r="E83" s="27"/>
-      <c r="F83" s="28"/>
-      <c r="G83" s="28" t="s">
+      <c r="E83" s="25"/>
+      <c r="F83" s="26"/>
+      <c r="G83" s="26" t="s">
         <v>138</v>
       </c>
-      <c r="H83" s="45"/>
-      <c r="I83" s="21"/>
-      <c r="J83" s="21"/>
+      <c r="H83" s="43"/>
+      <c r="I83" s="19"/>
+      <c r="J83" s="19"/>
     </row>
     <row r="84" spans="1:10" ht="9.6" customHeight="1">
-      <c r="A84" s="21"/>
-      <c r="B84" s="27"/>
-      <c r="C84" s="49"/>
-      <c r="D84" s="27"/>
-      <c r="E84" s="27"/>
-      <c r="F84" s="27"/>
-      <c r="G84" s="28"/>
-      <c r="H84" s="27"/>
-      <c r="I84" s="21"/>
-      <c r="J84" s="21"/>
+      <c r="A84" s="19"/>
+      <c r="B84" s="25"/>
+      <c r="C84" s="47"/>
+      <c r="D84" s="25"/>
+      <c r="E84" s="25"/>
+      <c r="F84" s="25"/>
+      <c r="G84" s="26"/>
+      <c r="H84" s="25"/>
+      <c r="I84" s="19"/>
+      <c r="J84" s="19"/>
     </row>
     <row r="85" spans="1:10" ht="17.25" customHeight="1">
-      <c r="A85" s="21"/>
-      <c r="B85" s="20" t="s">
+      <c r="A85" s="19"/>
+      <c r="B85" s="18" t="s">
         <v>139</v>
       </c>
-      <c r="C85" s="27"/>
-      <c r="D85" s="27"/>
-      <c r="E85" s="27"/>
-      <c r="F85" s="27"/>
-      <c r="H85" s="27"/>
-      <c r="I85" s="21"/>
-      <c r="J85" s="21"/>
+      <c r="C85" s="25"/>
+      <c r="D85" s="25"/>
+      <c r="E85" s="25"/>
+      <c r="F85" s="25"/>
+      <c r="H85" s="25"/>
+      <c r="I85" s="19"/>
+      <c r="J85" s="19"/>
     </row>
     <row r="86" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A86" s="21"/>
-      <c r="B86" s="27"/>
-      <c r="C86" s="27"/>
-      <c r="D86" s="28" t="s">
+      <c r="A86" s="19"/>
+      <c r="B86" s="25"/>
+      <c r="C86" s="25"/>
+      <c r="D86" s="26" t="s">
         <v>94</v>
       </c>
-      <c r="E86" s="52"/>
-      <c r="G86" s="28" t="s">
+      <c r="E86" s="50"/>
+      <c r="G86" s="26" t="s">
         <v>95</v>
       </c>
-      <c r="H86" s="27"/>
-      <c r="I86" s="21"/>
-      <c r="J86" s="21"/>
+      <c r="H86" s="25"/>
+      <c r="I86" s="19"/>
+      <c r="J86" s="19"/>
     </row>
     <row r="87" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A87" s="21"/>
-      <c r="B87" s="27"/>
-      <c r="C87" s="55" t="s">
+      <c r="A87" s="19"/>
+      <c r="B87" s="25"/>
+      <c r="C87" s="53" t="s">
         <v>114</v>
       </c>
-      <c r="D87" s="28" t="s">
+      <c r="D87" s="26" t="s">
         <v>140</v>
       </c>
-      <c r="E87" s="28"/>
-      <c r="G87" s="28" t="s">
+      <c r="E87" s="26"/>
+      <c r="G87" s="26" t="s">
         <v>141</v>
       </c>
-      <c r="H87" s="27"/>
-      <c r="I87" s="21"/>
-      <c r="J87" s="21"/>
+      <c r="H87" s="25"/>
+      <c r="I87" s="19"/>
+      <c r="J87" s="19"/>
     </row>
     <row r="88" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A88" s="21"/>
-      <c r="B88" s="27"/>
-      <c r="C88" s="55" t="s">
+      <c r="A88" s="19"/>
+      <c r="B88" s="25"/>
+      <c r="C88" s="53" t="s">
         <v>117</v>
       </c>
-      <c r="D88" s="28" t="s">
+      <c r="D88" s="26" t="s">
         <v>142</v>
       </c>
-      <c r="E88" s="28"/>
-      <c r="G88" s="28" t="s">
+      <c r="E88" s="26"/>
+      <c r="G88" s="26" t="s">
         <v>143</v>
       </c>
-      <c r="H88" s="27"/>
-      <c r="I88" s="21"/>
-      <c r="J88" s="21"/>
+      <c r="H88" s="25"/>
+      <c r="I88" s="19"/>
+      <c r="J88" s="19"/>
     </row>
     <row r="89" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A89" s="21"/>
-      <c r="B89" s="27"/>
-      <c r="C89" s="55" t="s">
+      <c r="A89" s="19"/>
+      <c r="B89" s="25"/>
+      <c r="C89" s="53" t="s">
         <v>121</v>
       </c>
-      <c r="D89" s="28" t="s">
+      <c r="D89" s="26" t="s">
         <v>144</v>
       </c>
-      <c r="E89" s="27"/>
-      <c r="G89" s="32" t="s">
+      <c r="E89" s="25"/>
+      <c r="G89" s="30" t="s">
         <v>145</v>
       </c>
-      <c r="H89" s="27"/>
-      <c r="I89" s="21"/>
-      <c r="J89" s="21"/>
+      <c r="H89" s="25"/>
+      <c r="I89" s="19"/>
+      <c r="J89" s="19"/>
     </row>
     <row r="90" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A90" s="21"/>
-      <c r="B90" s="27"/>
-      <c r="C90" s="27"/>
-      <c r="D90" s="27"/>
-      <c r="E90" s="27"/>
-      <c r="F90" s="27"/>
-      <c r="G90" s="28"/>
-      <c r="H90" s="27"/>
-      <c r="I90" s="21"/>
-      <c r="J90" s="21"/>
+      <c r="A90" s="19"/>
+      <c r="B90" s="25"/>
+      <c r="C90" s="25"/>
+      <c r="D90" s="25"/>
+      <c r="E90" s="25"/>
+      <c r="F90" s="25"/>
+      <c r="G90" s="26"/>
+      <c r="H90" s="25"/>
+      <c r="I90" s="19"/>
+      <c r="J90" s="19"/>
     </row>
     <row r="91" spans="1:10" ht="15" customHeight="1">
-      <c r="A91" s="21"/>
-      <c r="B91" s="20" t="s">
+      <c r="A91" s="19"/>
+      <c r="B91" s="18" t="s">
         <v>146</v>
       </c>
-      <c r="C91" s="27"/>
-      <c r="D91" s="27"/>
-      <c r="E91" s="27"/>
-      <c r="F91" s="27"/>
-      <c r="G91" s="27"/>
-      <c r="H91" s="27"/>
-      <c r="I91" s="21"/>
-      <c r="J91" s="21"/>
+      <c r="C91" s="25"/>
+      <c r="D91" s="25"/>
+      <c r="E91" s="25"/>
+      <c r="F91" s="25"/>
+      <c r="G91" s="25"/>
+      <c r="H91" s="25"/>
+      <c r="I91" s="19"/>
+      <c r="J91" s="19"/>
     </row>
     <row r="92" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A92" s="21"/>
-      <c r="B92" s="27"/>
-      <c r="C92" s="28"/>
-      <c r="D92" s="28" t="s">
+      <c r="A92" s="19"/>
+      <c r="B92" s="25"/>
+      <c r="C92" s="26"/>
+      <c r="D92" s="26" t="s">
         <v>94</v>
       </c>
-      <c r="E92" s="52"/>
-      <c r="F92" s="28" t="s">
+      <c r="E92" s="50"/>
+      <c r="F92" s="26" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="93" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A93" s="21"/>
-      <c r="B93" s="27"/>
-      <c r="C93" s="32" t="s">
+      <c r="A93" s="19"/>
+      <c r="B93" s="25"/>
+      <c r="C93" s="30" t="s">
         <v>147</v>
       </c>
-      <c r="D93" s="56"/>
-      <c r="E93" s="32"/>
-      <c r="F93" s="28"/>
-      <c r="H93" s="52"/>
+      <c r="D93" s="54"/>
+      <c r="E93" s="30"/>
+      <c r="F93" s="26"/>
+      <c r="H93" s="50"/>
     </row>
     <row r="94" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A94" s="21"/>
-      <c r="B94" s="27"/>
-      <c r="D94" s="32" t="s">
+      <c r="A94" s="19"/>
+      <c r="B94" s="25"/>
+      <c r="D94" s="30" t="s">
         <v>148</v>
       </c>
-      <c r="F94" s="32" t="s">
+      <c r="F94" s="30" t="s">
         <v>149</v>
       </c>
-      <c r="H94" s="52"/>
+      <c r="H94" s="50"/>
     </row>
     <row r="95" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A95" s="21"/>
-      <c r="B95" s="27"/>
-      <c r="D95" s="58" t="s">
+      <c r="A95" s="19"/>
+      <c r="B95" s="25"/>
+      <c r="D95" s="56" t="s">
         <v>37</v>
       </c>
-      <c r="F95" s="59" t="s">
+      <c r="F95" s="57" t="s">
         <v>150</v>
       </c>
-      <c r="H95" s="60"/>
+      <c r="H95" s="58"/>
     </row>
     <row r="96" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A96" s="21"/>
-      <c r="B96" s="27"/>
-      <c r="D96" s="56"/>
-      <c r="F96" s="32" t="s">
+      <c r="A96" s="19"/>
+      <c r="B96" s="25"/>
+      <c r="D96" s="54"/>
+      <c r="F96" s="30" t="s">
         <v>151</v>
       </c>
-      <c r="H96" s="60"/>
+      <c r="H96" s="58"/>
     </row>
     <row r="97" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A97" s="21"/>
-      <c r="B97" s="27"/>
-      <c r="D97" s="32" t="s">
+      <c r="A97" s="19"/>
+      <c r="B97" s="25"/>
+      <c r="D97" s="30" t="s">
         <v>152</v>
       </c>
-      <c r="F97" s="61" t="s">
+      <c r="F97" s="59" t="s">
         <v>153</v>
       </c>
-      <c r="H97" s="60"/>
+      <c r="H97" s="58"/>
     </row>
     <row r="98" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A98" s="21"/>
-      <c r="B98" s="27"/>
-      <c r="C98" s="32" t="s">
+      <c r="A98" s="19"/>
+      <c r="B98" s="25"/>
+      <c r="C98" s="30" t="s">
         <v>154</v>
       </c>
-      <c r="D98" s="56"/>
-      <c r="F98" s="32"/>
-      <c r="H98" s="60"/>
+      <c r="D98" s="54"/>
+      <c r="F98" s="30"/>
+      <c r="H98" s="58"/>
     </row>
     <row r="99" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A99" s="21"/>
-      <c r="B99" s="27"/>
-      <c r="D99" s="32" t="s">
+      <c r="A99" s="19"/>
+      <c r="B99" s="25"/>
+      <c r="D99" s="30" t="s">
         <v>155</v>
       </c>
-      <c r="F99" s="61" t="s">
+      <c r="F99" s="59" t="s">
         <v>156</v>
       </c>
-      <c r="H99" s="60"/>
+      <c r="H99" s="58"/>
     </row>
     <row r="100" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A100" s="21"/>
-      <c r="B100" s="27"/>
-      <c r="C100" s="32"/>
-      <c r="D100" s="56"/>
-      <c r="F100" s="32" t="s">
+      <c r="A100" s="19"/>
+      <c r="B100" s="25"/>
+      <c r="C100" s="30"/>
+      <c r="D100" s="54"/>
+      <c r="F100" s="30" t="s">
         <v>157</v>
       </c>
-      <c r="H100" s="60"/>
+      <c r="H100" s="58"/>
     </row>
     <row r="101" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A101" s="21"/>
-      <c r="B101" s="27"/>
-      <c r="D101" s="32" t="s">
+      <c r="A101" s="19"/>
+      <c r="B101" s="25"/>
+      <c r="D101" s="30" t="s">
         <v>158</v>
       </c>
-      <c r="F101" s="32" t="s">
+      <c r="F101" s="30" t="s">
         <v>159</v>
       </c>
-      <c r="H101" s="60"/>
+      <c r="H101" s="58"/>
     </row>
     <row r="102" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A102" s="21"/>
-      <c r="B102" s="27"/>
-      <c r="C102" s="32" t="s">
+      <c r="A102" s="19"/>
+      <c r="B102" s="25"/>
+      <c r="C102" s="30" t="s">
         <v>160</v>
       </c>
-      <c r="D102" s="56"/>
-      <c r="F102" s="32"/>
-      <c r="H102" s="60"/>
+      <c r="D102" s="54"/>
+      <c r="F102" s="30"/>
+      <c r="H102" s="58"/>
     </row>
     <row r="103" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A103" s="21"/>
-      <c r="B103" s="27"/>
-      <c r="D103" s="32" t="s">
+      <c r="A103" s="19"/>
+      <c r="B103" s="25"/>
+      <c r="D103" s="30" t="s">
         <v>161</v>
       </c>
-      <c r="F103" s="32" t="s">
+      <c r="F103" s="30" t="s">
         <v>162</v>
       </c>
-      <c r="H103" s="60"/>
+      <c r="H103" s="58"/>
     </row>
     <row r="104" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A104" s="21"/>
-      <c r="B104" s="27"/>
-      <c r="C104" s="32"/>
-      <c r="D104" s="56"/>
-      <c r="F104" s="32" t="s">
+      <c r="A104" s="19"/>
+      <c r="B104" s="25"/>
+      <c r="C104" s="30"/>
+      <c r="D104" s="54"/>
+      <c r="F104" s="30" t="s">
         <v>163</v>
       </c>
-      <c r="H104" s="60"/>
+      <c r="H104" s="58"/>
     </row>
     <row r="105" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A105" s="21"/>
-      <c r="B105" s="27"/>
-      <c r="C105" s="32" t="s">
+      <c r="A105" s="19"/>
+      <c r="B105" s="25"/>
+      <c r="C105" s="30" t="s">
         <v>164</v>
       </c>
-      <c r="D105" s="56"/>
-      <c r="F105" s="32"/>
+      <c r="D105" s="54"/>
+      <c r="F105" s="30"/>
     </row>
     <row r="106" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A106" s="21"/>
-      <c r="B106" s="27"/>
-      <c r="D106" s="32" t="s">
+      <c r="A106" s="19"/>
+      <c r="B106" s="25"/>
+      <c r="D106" s="30" t="s">
         <v>165</v>
       </c>
-      <c r="F106" s="32" t="s">
+      <c r="F106" s="30" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="107" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A107" s="21"/>
-      <c r="B107" s="27"/>
-      <c r="D107" s="32" t="s">
+      <c r="A107" s="19"/>
+      <c r="B107" s="25"/>
+      <c r="D107" s="30" t="s">
         <v>167</v>
       </c>
-      <c r="F107" s="32" t="s">
+      <c r="F107" s="30" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="108" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A108" s="21"/>
-      <c r="B108" s="27"/>
-      <c r="D108" s="32" t="s">
+      <c r="A108" s="19"/>
+      <c r="B108" s="25"/>
+      <c r="D108" s="30" t="s">
         <v>169</v>
       </c>
-      <c r="F108" s="32" t="s">
+      <c r="F108" s="30" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="109" spans="1:10" s="62" customFormat="1" ht="15" customHeight="1">
-      <c r="A109" s="21"/>
-      <c r="B109" s="27"/>
-      <c r="C109" s="28"/>
-      <c r="D109" s="28"/>
-      <c r="E109" s="28"/>
-      <c r="F109" s="28"/>
-      <c r="G109" s="28"/>
-      <c r="H109" s="53"/>
-      <c r="I109" s="28"/>
-      <c r="J109" s="50"/>
+    <row r="109" spans="1:10" s="60" customFormat="1" ht="15" customHeight="1">
+      <c r="A109" s="19"/>
+      <c r="B109" s="25"/>
+      <c r="C109" s="26"/>
+      <c r="D109" s="26"/>
+      <c r="E109" s="26"/>
+      <c r="F109" s="26"/>
+      <c r="G109" s="26"/>
+      <c r="H109" s="51"/>
+      <c r="I109" s="26"/>
+      <c r="J109" s="48"/>
     </row>
     <row r="110" spans="1:10" ht="15" customHeight="1">
-      <c r="A110" s="21"/>
-      <c r="B110" s="20" t="s">
+      <c r="A110" s="19"/>
+      <c r="B110" s="18" t="s">
         <v>171</v>
       </c>
-      <c r="C110" s="27"/>
-      <c r="D110" s="27"/>
-      <c r="E110" s="27"/>
-      <c r="G110" s="27"/>
-      <c r="H110" s="27"/>
-      <c r="I110" s="21"/>
-      <c r="J110" s="21"/>
-    </row>
-    <row r="111" spans="1:10" s="62" customFormat="1" ht="15" customHeight="1">
-      <c r="A111" s="21"/>
-      <c r="B111" s="27"/>
-      <c r="C111" s="28"/>
-      <c r="D111" s="28" t="s">
+      <c r="C110" s="25"/>
+      <c r="D110" s="25"/>
+      <c r="E110" s="25"/>
+      <c r="G110" s="25"/>
+      <c r="H110" s="25"/>
+      <c r="I110" s="19"/>
+      <c r="J110" s="19"/>
+    </row>
+    <row r="111" spans="1:10" s="60" customFormat="1" ht="15" customHeight="1">
+      <c r="A111" s="19"/>
+      <c r="B111" s="25"/>
+      <c r="C111" s="26"/>
+      <c r="D111" s="26" t="s">
         <v>94</v>
       </c>
-      <c r="E111" s="51"/>
-      <c r="F111" s="16"/>
-      <c r="G111" s="28" t="s">
+      <c r="E111" s="49"/>
+      <c r="F111" s="14"/>
+      <c r="G111" s="26" t="s">
         <v>172</v>
       </c>
-      <c r="H111" s="27"/>
-      <c r="I111" s="16"/>
-      <c r="J111" s="21"/>
-    </row>
-    <row r="112" spans="1:10" s="62" customFormat="1" ht="15" customHeight="1">
-      <c r="A112" s="21"/>
-      <c r="B112" s="27"/>
-      <c r="C112" s="28"/>
-      <c r="D112" s="28" t="s">
+      <c r="H111" s="25"/>
+      <c r="I111" s="14"/>
+      <c r="J111" s="19"/>
+    </row>
+    <row r="112" spans="1:10" s="60" customFormat="1" ht="15" customHeight="1">
+      <c r="A112" s="19"/>
+      <c r="B112" s="25"/>
+      <c r="C112" s="26"/>
+      <c r="D112" s="26" t="s">
         <v>38</v>
       </c>
-      <c r="E112" s="51"/>
-      <c r="F112" s="28"/>
-      <c r="G112" s="32"/>
-      <c r="H112" s="27"/>
-      <c r="I112" s="21"/>
-      <c r="J112" s="21"/>
-    </row>
-    <row r="113" spans="1:10" s="62" customFormat="1" ht="15" customHeight="1">
-      <c r="A113" s="21"/>
-      <c r="B113" s="27"/>
-      <c r="C113" s="28"/>
-      <c r="D113" s="28"/>
-      <c r="E113" s="51"/>
-      <c r="F113" s="28"/>
-      <c r="G113" s="32"/>
-      <c r="H113" s="27"/>
-      <c r="I113" s="28"/>
-      <c r="J113" s="21"/>
-    </row>
-    <row r="114" spans="1:10" s="62" customFormat="1" ht="15" customHeight="1">
-      <c r="A114" s="21"/>
-      <c r="B114" s="27"/>
-      <c r="C114" s="28"/>
-      <c r="D114" s="28"/>
-      <c r="E114" s="51"/>
-      <c r="F114" s="28"/>
-      <c r="G114" s="32"/>
-      <c r="H114" s="27"/>
-      <c r="I114" s="28"/>
-      <c r="J114" s="21"/>
-    </row>
-    <row r="115" spans="1:10" s="62" customFormat="1" ht="15" customHeight="1">
-      <c r="A115" s="21"/>
-      <c r="B115" s="20" t="s">
+      <c r="E112" s="49"/>
+      <c r="F112" s="26"/>
+      <c r="G112" s="30"/>
+      <c r="H112" s="25"/>
+      <c r="I112" s="19"/>
+      <c r="J112" s="19"/>
+    </row>
+    <row r="113" spans="1:10" s="60" customFormat="1" ht="15" customHeight="1">
+      <c r="A113" s="19"/>
+      <c r="B113" s="25"/>
+      <c r="C113" s="26"/>
+      <c r="D113" s="26"/>
+      <c r="E113" s="49"/>
+      <c r="F113" s="26"/>
+      <c r="G113" s="30"/>
+      <c r="H113" s="25"/>
+      <c r="I113" s="26"/>
+      <c r="J113" s="19"/>
+    </row>
+    <row r="114" spans="1:10" s="60" customFormat="1" ht="15" customHeight="1">
+      <c r="A114" s="19"/>
+      <c r="B114" s="25"/>
+      <c r="C114" s="26"/>
+      <c r="D114" s="26"/>
+      <c r="E114" s="49"/>
+      <c r="F114" s="26"/>
+      <c r="G114" s="30"/>
+      <c r="H114" s="25"/>
+      <c r="I114" s="26"/>
+      <c r="J114" s="19"/>
+    </row>
+    <row r="115" spans="1:10" s="60" customFormat="1" ht="15" customHeight="1">
+      <c r="A115" s="19"/>
+      <c r="B115" s="18" t="s">
         <v>173</v>
       </c>
-      <c r="C115" s="27"/>
-      <c r="D115" s="27"/>
-      <c r="E115" s="27"/>
-      <c r="F115" s="27"/>
-      <c r="G115" s="16"/>
-      <c r="H115" s="27"/>
-      <c r="I115" s="21"/>
-      <c r="J115" s="21"/>
-    </row>
-    <row r="116" spans="1:10" s="62" customFormat="1" ht="15" customHeight="1">
-      <c r="A116" s="21"/>
-      <c r="B116" s="27"/>
-      <c r="C116" s="28"/>
-      <c r="D116" s="28" t="s">
+      <c r="C115" s="25"/>
+      <c r="D115" s="25"/>
+      <c r="E115" s="25"/>
+      <c r="F115" s="25"/>
+      <c r="G115" s="14"/>
+      <c r="H115" s="25"/>
+      <c r="I115" s="19"/>
+      <c r="J115" s="19"/>
+    </row>
+    <row r="116" spans="1:10" s="60" customFormat="1" ht="15" customHeight="1">
+      <c r="A116" s="19"/>
+      <c r="B116" s="25"/>
+      <c r="C116" s="26"/>
+      <c r="D116" s="26" t="s">
         <v>94</v>
       </c>
-      <c r="E116" s="51"/>
-      <c r="F116" s="28"/>
-      <c r="G116" s="28" t="s">
+      <c r="E116" s="49"/>
+      <c r="F116" s="26"/>
+      <c r="G116" s="26" t="s">
         <v>95</v>
       </c>
-      <c r="H116" s="16"/>
-      <c r="I116" s="21"/>
-      <c r="J116" s="21"/>
-    </row>
-    <row r="117" spans="1:10" s="62" customFormat="1" ht="15" customHeight="1">
-      <c r="A117" s="21"/>
-      <c r="B117" s="27"/>
-      <c r="C117" s="50" t="s">
+      <c r="H116" s="14"/>
+      <c r="I116" s="19"/>
+      <c r="J116" s="19"/>
+    </row>
+    <row r="117" spans="1:10" s="60" customFormat="1" ht="15" customHeight="1">
+      <c r="A117" s="19"/>
+      <c r="B117" s="25"/>
+      <c r="C117" s="48" t="s">
         <v>96</v>
       </c>
-      <c r="D117" s="28" t="s">
+      <c r="D117" s="26" t="s">
         <v>174</v>
       </c>
-      <c r="E117" s="28"/>
-      <c r="F117" s="28"/>
-      <c r="G117" s="27" t="s">
+      <c r="E117" s="26"/>
+      <c r="F117" s="26"/>
+      <c r="G117" s="25" t="s">
         <v>175</v>
       </c>
-      <c r="H117" s="16"/>
-      <c r="I117" s="60"/>
-      <c r="J117" s="60"/>
-    </row>
-    <row r="118" spans="1:10" s="62" customFormat="1" ht="15" customHeight="1">
-      <c r="A118" s="21"/>
-      <c r="B118" s="27"/>
-      <c r="C118" s="50" t="s">
+      <c r="H117" s="14"/>
+      <c r="I117" s="58"/>
+      <c r="J117" s="58"/>
+    </row>
+    <row r="118" spans="1:10" s="60" customFormat="1" ht="15" customHeight="1">
+      <c r="A118" s="19"/>
+      <c r="B118" s="25"/>
+      <c r="C118" s="48" t="s">
         <v>96</v>
       </c>
-      <c r="D118" s="28" t="s">
+      <c r="D118" s="26" t="s">
         <v>176</v>
       </c>
-      <c r="E118" s="28"/>
-      <c r="F118" s="28"/>
-      <c r="G118" s="27" t="s">
+      <c r="E118" s="26"/>
+      <c r="F118" s="26"/>
+      <c r="G118" s="25" t="s">
         <v>177</v>
       </c>
-      <c r="H118" s="16"/>
-      <c r="I118" s="60"/>
-      <c r="J118" s="60"/>
-    </row>
-    <row r="119" spans="1:10" s="62" customFormat="1" ht="15" customHeight="1">
-      <c r="A119" s="21"/>
-      <c r="B119" s="27"/>
-      <c r="C119" s="50" t="s">
+      <c r="H118" s="14"/>
+      <c r="I118" s="58"/>
+      <c r="J118" s="58"/>
+    </row>
+    <row r="119" spans="1:10" s="60" customFormat="1" ht="15" customHeight="1">
+      <c r="A119" s="19"/>
+      <c r="B119" s="25"/>
+      <c r="C119" s="48" t="s">
         <v>96</v>
       </c>
-      <c r="D119" s="28" t="s">
+      <c r="D119" s="26" t="s">
         <v>178</v>
       </c>
-      <c r="E119" s="28"/>
-      <c r="F119" s="28"/>
-      <c r="G119" s="27" t="s">
+      <c r="E119" s="26"/>
+      <c r="F119" s="26"/>
+      <c r="G119" s="25" t="s">
         <v>179</v>
       </c>
-      <c r="H119" s="16"/>
-      <c r="I119" s="60"/>
-      <c r="J119" s="60"/>
-    </row>
-    <row r="120" spans="1:10" s="62" customFormat="1" ht="15" customHeight="1">
-      <c r="A120" s="21"/>
-      <c r="B120" s="27"/>
-      <c r="C120" s="50"/>
-      <c r="D120" s="28" t="s">
+      <c r="H119" s="14"/>
+      <c r="I119" s="58"/>
+      <c r="J119" s="58"/>
+    </row>
+    <row r="120" spans="1:10" s="60" customFormat="1" ht="15" customHeight="1">
+      <c r="A120" s="19"/>
+      <c r="B120" s="25"/>
+      <c r="C120" s="48"/>
+      <c r="D120" s="26" t="s">
         <v>180</v>
       </c>
-      <c r="E120" s="28"/>
-      <c r="F120" s="28"/>
-      <c r="G120" s="16"/>
-      <c r="H120" s="16"/>
-      <c r="I120" s="60"/>
-      <c r="J120" s="60"/>
-    </row>
-    <row r="121" spans="1:10" s="62" customFormat="1" ht="15" customHeight="1">
-      <c r="A121" s="21"/>
-      <c r="B121" s="27"/>
-      <c r="C121" s="50"/>
-      <c r="D121" s="28" t="s">
+      <c r="E120" s="26"/>
+      <c r="F120" s="26"/>
+      <c r="G120" s="14"/>
+      <c r="H120" s="14"/>
+      <c r="I120" s="58"/>
+      <c r="J120" s="58"/>
+    </row>
+    <row r="121" spans="1:10" s="60" customFormat="1" ht="15" customHeight="1">
+      <c r="A121" s="19"/>
+      <c r="B121" s="25"/>
+      <c r="C121" s="48"/>
+      <c r="D121" s="26" t="s">
         <v>181</v>
       </c>
-      <c r="E121" s="28"/>
-      <c r="F121" s="28"/>
-      <c r="G121" s="16"/>
-      <c r="H121" s="16"/>
-      <c r="I121" s="60"/>
-      <c r="J121" s="60"/>
+      <c r="E121" s="26"/>
+      <c r="F121" s="26"/>
+      <c r="G121" s="14"/>
+      <c r="H121" s="14"/>
+      <c r="I121" s="58"/>
+      <c r="J121" s="58"/>
     </row>
     <row r="122" spans="1:10" ht="13.9" customHeight="1">
-      <c r="A122" s="21"/>
-      <c r="B122" s="27"/>
-      <c r="C122" s="27"/>
-      <c r="D122" s="27"/>
-      <c r="E122" s="27"/>
-      <c r="F122" s="27"/>
-      <c r="G122" s="27"/>
-      <c r="H122" s="27"/>
-      <c r="I122" s="21"/>
-      <c r="J122" s="21"/>
+      <c r="A122" s="19"/>
+      <c r="B122" s="25"/>
+      <c r="C122" s="25"/>
+      <c r="D122" s="25"/>
+      <c r="E122" s="25"/>
+      <c r="F122" s="25"/>
+      <c r="G122" s="25"/>
+      <c r="H122" s="25"/>
+      <c r="I122" s="19"/>
+      <c r="J122" s="19"/>
     </row>
     <row r="123" spans="1:10" ht="15" customHeight="1">
-      <c r="A123" s="21"/>
-      <c r="B123" s="20" t="s">
+      <c r="A123" s="19"/>
+      <c r="B123" s="18" t="s">
         <v>182</v>
       </c>
-      <c r="C123" s="27"/>
-      <c r="D123" s="27"/>
-      <c r="E123" s="27"/>
-      <c r="F123" s="27"/>
-      <c r="G123" s="27"/>
-      <c r="H123" s="27"/>
-      <c r="I123" s="21"/>
-      <c r="J123" s="21"/>
+      <c r="C123" s="25"/>
+      <c r="D123" s="25"/>
+      <c r="E123" s="25"/>
+      <c r="F123" s="25"/>
+      <c r="G123" s="25"/>
+      <c r="H123" s="25"/>
+      <c r="I123" s="19"/>
+      <c r="J123" s="19"/>
     </row>
     <row r="124" spans="1:10" ht="15" customHeight="1">
-      <c r="A124" s="21"/>
-      <c r="B124" s="20"/>
-      <c r="C124" s="28"/>
-      <c r="D124" s="28" t="s">
+      <c r="A124" s="19"/>
+      <c r="B124" s="18"/>
+      <c r="C124" s="26"/>
+      <c r="D124" s="26" t="s">
         <v>94</v>
       </c>
-      <c r="E124" s="28"/>
-      <c r="F124" s="45"/>
-      <c r="G124" s="28" t="s">
+      <c r="E124" s="26"/>
+      <c r="F124" s="43"/>
+      <c r="G124" s="26" t="s">
         <v>95</v>
       </c>
-      <c r="I124" s="21"/>
-      <c r="J124" s="21"/>
+      <c r="I124" s="19"/>
+      <c r="J124" s="19"/>
     </row>
     <row r="125" spans="1:10" ht="15" customHeight="1">
-      <c r="A125" s="21"/>
-      <c r="B125" s="20"/>
-      <c r="C125" s="50" t="s">
+      <c r="A125" s="19"/>
+      <c r="B125" s="18"/>
+      <c r="C125" s="48" t="s">
         <v>114</v>
       </c>
-      <c r="D125" s="28" t="s">
+      <c r="D125" s="26" t="s">
         <v>183</v>
       </c>
-      <c r="E125" s="28"/>
-      <c r="F125" s="56"/>
-      <c r="G125" s="32" t="s">
+      <c r="E125" s="26"/>
+      <c r="F125" s="54"/>
+      <c r="G125" s="30" t="s">
         <v>184</v>
       </c>
-      <c r="H125" s="32"/>
-      <c r="I125" s="21"/>
-      <c r="J125" s="21"/>
+      <c r="H125" s="30"/>
+      <c r="I125" s="19"/>
+      <c r="J125" s="19"/>
     </row>
     <row r="126" spans="1:10" ht="15" customHeight="1">
-      <c r="A126" s="21"/>
-      <c r="B126" s="20"/>
-      <c r="E126" s="28"/>
-      <c r="F126" s="56"/>
-      <c r="G126" s="32" t="s">
+      <c r="A126" s="19"/>
+      <c r="B126" s="18"/>
+      <c r="E126" s="26"/>
+      <c r="F126" s="54"/>
+      <c r="G126" s="30" t="s">
         <v>185</v>
       </c>
-      <c r="H126" s="32"/>
-      <c r="I126" s="21"/>
-      <c r="J126" s="21"/>
+      <c r="H126" s="30"/>
+      <c r="I126" s="19"/>
+      <c r="J126" s="19"/>
     </row>
     <row r="127" spans="1:10" ht="15" customHeight="1">
-      <c r="A127" s="21"/>
-      <c r="B127" s="20"/>
-      <c r="C127" s="50"/>
-      <c r="D127" s="28"/>
-      <c r="E127" s="28"/>
-      <c r="F127" s="56"/>
-      <c r="G127" s="32"/>
-      <c r="H127" s="32"/>
-      <c r="I127" s="21"/>
-      <c r="J127" s="21"/>
+      <c r="A127" s="19"/>
+      <c r="B127" s="18"/>
+      <c r="C127" s="48"/>
+      <c r="D127" s="26"/>
+      <c r="E127" s="26"/>
+      <c r="F127" s="54"/>
+      <c r="G127" s="30"/>
+      <c r="H127" s="30"/>
+      <c r="I127" s="19"/>
+      <c r="J127" s="19"/>
     </row>
     <row r="128" spans="1:10" ht="15" customHeight="1">
-      <c r="A128" s="21"/>
-      <c r="B128" s="20" t="s">
+      <c r="A128" s="19"/>
+      <c r="B128" s="18" t="s">
         <v>186</v>
       </c>
-      <c r="C128" s="50"/>
-      <c r="D128" s="28"/>
-      <c r="E128" s="28"/>
-      <c r="F128" s="56"/>
-      <c r="G128" s="32"/>
-      <c r="H128" s="32"/>
-      <c r="I128" s="21"/>
-      <c r="J128" s="21"/>
+      <c r="C128" s="48"/>
+      <c r="D128" s="26"/>
+      <c r="E128" s="26"/>
+      <c r="F128" s="54"/>
+      <c r="G128" s="30"/>
+      <c r="H128" s="30"/>
+      <c r="I128" s="19"/>
+      <c r="J128" s="19"/>
     </row>
     <row r="129" spans="1:14" ht="15" customHeight="1">
-      <c r="A129" s="21"/>
-      <c r="B129" s="20"/>
-      <c r="C129" s="50" t="s">
+      <c r="A129" s="19"/>
+      <c r="B129" s="18"/>
+      <c r="C129" s="48" t="s">
         <v>96</v>
       </c>
-      <c r="D129" s="28" t="s">
+      <c r="D129" s="26" t="s">
         <v>187</v>
       </c>
-      <c r="E129" s="28"/>
-      <c r="F129" s="56"/>
-      <c r="G129" s="32" t="s">
+      <c r="E129" s="26"/>
+      <c r="F129" s="54"/>
+      <c r="G129" s="30" t="s">
         <v>188</v>
       </c>
-      <c r="H129" s="32"/>
-      <c r="I129" s="21"/>
-      <c r="J129" s="21"/>
+      <c r="H129" s="30"/>
+      <c r="I129" s="19"/>
+      <c r="J129" s="19"/>
     </row>
     <row r="130" spans="1:14" ht="15" customHeight="1">
-      <c r="A130" s="21"/>
-      <c r="B130" s="20"/>
-      <c r="C130" s="50" t="s">
+      <c r="A130" s="19"/>
+      <c r="B130" s="18"/>
+      <c r="C130" s="48" t="s">
         <v>96</v>
       </c>
-      <c r="D130" s="28" t="s">
+      <c r="D130" s="26" t="s">
         <v>189</v>
       </c>
-      <c r="E130" s="28"/>
-      <c r="F130" s="56"/>
-      <c r="G130" s="32" t="s">
+      <c r="E130" s="26"/>
+      <c r="F130" s="54"/>
+      <c r="G130" s="30" t="s">
         <v>190</v>
       </c>
-      <c r="H130" s="32"/>
-      <c r="I130" s="21"/>
-      <c r="J130" s="21"/>
+      <c r="H130" s="30"/>
+      <c r="I130" s="19"/>
+      <c r="J130" s="19"/>
     </row>
     <row r="131" spans="1:14" ht="15" customHeight="1">
-      <c r="A131" s="21"/>
-      <c r="B131" s="20"/>
-      <c r="C131" s="50"/>
-      <c r="D131" s="28"/>
-      <c r="E131" s="28"/>
-      <c r="F131" s="56"/>
-      <c r="G131" s="32"/>
-      <c r="H131" s="32"/>
-      <c r="I131" s="21"/>
-      <c r="J131" s="21"/>
+      <c r="A131" s="19"/>
+      <c r="B131" s="18"/>
+      <c r="C131" s="48"/>
+      <c r="D131" s="26"/>
+      <c r="E131" s="26"/>
+      <c r="F131" s="54"/>
+      <c r="G131" s="30"/>
+      <c r="H131" s="30"/>
+      <c r="I131" s="19"/>
+      <c r="J131" s="19"/>
     </row>
     <row r="132" spans="1:14" ht="15" customHeight="1">
-      <c r="A132" s="21"/>
-      <c r="B132" s="20"/>
-      <c r="C132" s="50"/>
-      <c r="D132" s="28"/>
-      <c r="E132" s="28"/>
-      <c r="F132" s="56"/>
-      <c r="G132" s="32"/>
-      <c r="H132" s="32"/>
-      <c r="I132" s="21"/>
-      <c r="J132" s="21"/>
+      <c r="A132" s="19"/>
+      <c r="B132" s="18"/>
+      <c r="C132" s="48"/>
+      <c r="D132" s="26"/>
+      <c r="E132" s="26"/>
+      <c r="F132" s="54"/>
+      <c r="G132" s="30"/>
+      <c r="H132" s="30"/>
+      <c r="I132" s="19"/>
+      <c r="J132" s="19"/>
     </row>
     <row r="133" spans="1:14" ht="18" customHeight="1">
-      <c r="A133" s="27"/>
-      <c r="B133" s="25" t="s">
+      <c r="A133" s="25"/>
+      <c r="B133" s="23" t="s">
         <v>191</v>
       </c>
-      <c r="C133" s="21"/>
-      <c r="D133" s="21"/>
-      <c r="E133" s="21"/>
-      <c r="F133" s="21"/>
-      <c r="G133" s="21"/>
-      <c r="H133" s="21"/>
-      <c r="I133" s="21"/>
-      <c r="J133" s="21"/>
+      <c r="C133" s="19"/>
+      <c r="D133" s="19"/>
+      <c r="E133" s="19"/>
+      <c r="F133" s="19"/>
+      <c r="G133" s="19"/>
+      <c r="H133" s="19"/>
+      <c r="I133" s="19"/>
+      <c r="J133" s="19"/>
     </row>
     <row r="134" spans="1:14" ht="18" customHeight="1">
-      <c r="A134" s="27"/>
-      <c r="B134" s="25"/>
-      <c r="C134" s="21"/>
-      <c r="D134" s="21"/>
-      <c r="E134" s="21"/>
-      <c r="F134" s="21"/>
-      <c r="G134" s="21"/>
-      <c r="H134" s="21"/>
-      <c r="I134" s="21"/>
-      <c r="J134" s="21"/>
+      <c r="A134" s="25"/>
+      <c r="B134" s="23"/>
+      <c r="C134" s="19"/>
+      <c r="D134" s="19"/>
+      <c r="E134" s="19"/>
+      <c r="F134" s="19"/>
+      <c r="G134" s="19"/>
+      <c r="H134" s="19"/>
+      <c r="I134" s="19"/>
+      <c r="J134" s="19"/>
     </row>
     <row r="135" spans="1:14" ht="18" customHeight="1">
-      <c r="A135" s="21"/>
-      <c r="B135" s="20" t="s">
+      <c r="A135" s="19"/>
+      <c r="B135" s="18" t="s">
         <v>192</v>
       </c>
-      <c r="C135" s="21"/>
-      <c r="D135" s="42"/>
-      <c r="E135" s="42"/>
-      <c r="F135" s="42"/>
-      <c r="G135" s="42"/>
-      <c r="H135" s="14"/>
-      <c r="L135" s="112"/>
-      <c r="M135" s="112"/>
-      <c r="N135" s="112"/>
+      <c r="C135" s="19"/>
+      <c r="D135" s="40"/>
+      <c r="E135" s="40"/>
+      <c r="F135" s="40"/>
+      <c r="G135" s="40"/>
+      <c r="H135" s="12"/>
+      <c r="L135" s="106"/>
+      <c r="M135" s="106"/>
+      <c r="N135" s="106"/>
     </row>
     <row r="136" spans="1:14" ht="18" customHeight="1">
-      <c r="A136" s="21"/>
-      <c r="B136" s="20"/>
-      <c r="C136" s="20" t="s">
+      <c r="A136" s="19"/>
+      <c r="B136" s="18"/>
+      <c r="C136" s="18" t="s">
         <v>193</v>
       </c>
-      <c r="E136" s="42"/>
-      <c r="F136" s="42"/>
-      <c r="G136" s="42"/>
-      <c r="H136" s="14"/>
-      <c r="L136" s="63" t="s">
+      <c r="E136" s="40"/>
+      <c r="F136" s="40"/>
+      <c r="G136" s="40"/>
+      <c r="H136" s="12"/>
+      <c r="L136" s="61" t="s">
         <v>194</v>
       </c>
-      <c r="M136" s="63"/>
-      <c r="N136" s="63"/>
+      <c r="M136" s="61"/>
+      <c r="N136" s="61"/>
     </row>
     <row r="137" spans="1:14" ht="18" customHeight="1">
-      <c r="A137" s="21"/>
-      <c r="B137" s="20"/>
-      <c r="C137" s="21"/>
-      <c r="D137" s="28"/>
-      <c r="E137" s="64"/>
-      <c r="F137" s="28"/>
-      <c r="G137" s="28"/>
-      <c r="H137" s="32"/>
-      <c r="I137" s="28" t="s">
+      <c r="A137" s="19"/>
+      <c r="B137" s="18"/>
+      <c r="C137" s="19"/>
+      <c r="D137" s="26"/>
+      <c r="E137" s="62"/>
+      <c r="F137" s="26"/>
+      <c r="G137" s="26"/>
+      <c r="H137" s="30"/>
+      <c r="I137" s="26" t="s">
         <v>195</v>
       </c>
-      <c r="J137" s="28"/>
+      <c r="J137" s="26"/>
     </row>
     <row r="138" spans="1:14" ht="18" customHeight="1">
-      <c r="A138" s="21"/>
-      <c r="B138" s="21"/>
-      <c r="C138" s="21"/>
-      <c r="D138" s="31" t="s">
+      <c r="A138" s="19"/>
+      <c r="B138" s="19"/>
+      <c r="C138" s="19"/>
+      <c r="D138" s="29" t="s">
         <v>196</v>
       </c>
-      <c r="E138" s="34"/>
-      <c r="F138" s="34"/>
-      <c r="G138" s="34"/>
-      <c r="H138" s="32"/>
-      <c r="I138" s="17" t="s">
+      <c r="E138" s="32"/>
+      <c r="F138" s="32"/>
+      <c r="G138" s="32"/>
+      <c r="H138" s="30"/>
+      <c r="I138" s="15" t="s">
         <v>197</v>
       </c>
-      <c r="J138" s="28"/>
-      <c r="L138" s="65"/>
-      <c r="M138" s="108"/>
-      <c r="N138" s="108"/>
+      <c r="J138" s="26"/>
+      <c r="L138" s="63"/>
+      <c r="M138" s="102"/>
+      <c r="N138" s="102"/>
     </row>
     <row r="139" spans="1:14" ht="18" customHeight="1">
-      <c r="A139" s="21"/>
-      <c r="B139" s="21"/>
-      <c r="C139" s="21"/>
-      <c r="D139" s="31" t="s">
+      <c r="A139" s="19"/>
+      <c r="B139" s="19"/>
+      <c r="C139" s="19"/>
+      <c r="D139" s="29" t="s">
         <v>198</v>
       </c>
-      <c r="E139" s="53"/>
-      <c r="F139" s="53"/>
-      <c r="H139" s="32"/>
-      <c r="I139" s="17" t="s">
+      <c r="E139" s="51"/>
+      <c r="F139" s="51"/>
+      <c r="H139" s="30"/>
+      <c r="I139" s="15" t="s">
         <v>197</v>
       </c>
-      <c r="J139" s="28"/>
-      <c r="L139" s="66"/>
-      <c r="M139" s="108"/>
-      <c r="N139" s="108"/>
+      <c r="J139" s="26"/>
+      <c r="L139" s="64"/>
+      <c r="M139" s="102"/>
+      <c r="N139" s="102"/>
     </row>
     <row r="140" spans="1:14" ht="18" customHeight="1">
-      <c r="A140" s="21"/>
-      <c r="B140" s="21"/>
-      <c r="C140" s="21"/>
-      <c r="D140" s="31" t="s">
+      <c r="A140" s="19"/>
+      <c r="B140" s="19"/>
+      <c r="C140" s="19"/>
+      <c r="D140" s="29" t="s">
         <v>199</v>
       </c>
-      <c r="E140" s="34"/>
-      <c r="F140" s="34"/>
-      <c r="G140" s="34"/>
-      <c r="H140" s="32"/>
-      <c r="I140" s="17" t="s">
+      <c r="E140" s="32"/>
+      <c r="F140" s="32"/>
+      <c r="G140" s="32"/>
+      <c r="H140" s="30"/>
+      <c r="I140" s="15" t="s">
         <v>197</v>
       </c>
-      <c r="J140" s="28"/>
-      <c r="L140" s="67"/>
-      <c r="M140" s="108"/>
-      <c r="N140" s="108"/>
+      <c r="J140" s="26"/>
+      <c r="L140" s="65"/>
+      <c r="M140" s="102"/>
+      <c r="N140" s="102"/>
     </row>
     <row r="141" spans="1:14" ht="18" customHeight="1">
-      <c r="A141" s="21"/>
-      <c r="B141" s="42"/>
-      <c r="C141" s="45"/>
-      <c r="D141" s="31" t="s">
+      <c r="A141" s="19"/>
+      <c r="B141" s="40"/>
+      <c r="C141" s="43"/>
+      <c r="D141" s="29" t="s">
         <v>200</v>
       </c>
-      <c r="E141" s="53"/>
-      <c r="F141" s="53"/>
-      <c r="G141" s="38"/>
-      <c r="H141" s="32"/>
-      <c r="I141" s="17" t="s">
+      <c r="E141" s="51"/>
+      <c r="F141" s="51"/>
+      <c r="G141" s="36"/>
+      <c r="H141" s="30"/>
+      <c r="I141" s="15" t="s">
         <v>197</v>
       </c>
-      <c r="J141" s="28"/>
-      <c r="L141" s="67"/>
-      <c r="M141" s="108"/>
-      <c r="N141" s="108"/>
+      <c r="J141" s="26"/>
+      <c r="L141" s="65"/>
+      <c r="M141" s="102"/>
+      <c r="N141" s="102"/>
     </row>
     <row r="142" spans="1:14" ht="18" customHeight="1">
-      <c r="A142" s="21"/>
-      <c r="B142" s="42"/>
-      <c r="C142" s="45"/>
-      <c r="D142" s="31" t="s">
+      <c r="A142" s="19"/>
+      <c r="B142" s="40"/>
+      <c r="C142" s="43"/>
+      <c r="D142" s="29" t="s">
         <v>201</v>
       </c>
-      <c r="E142" s="53"/>
-      <c r="F142" s="53"/>
-      <c r="G142" s="38"/>
-      <c r="H142" s="32"/>
-      <c r="I142" s="17" t="s">
+      <c r="E142" s="51"/>
+      <c r="F142" s="51"/>
+      <c r="G142" s="36"/>
+      <c r="H142" s="30"/>
+      <c r="I142" s="15" t="s">
         <v>197</v>
       </c>
-      <c r="J142" s="28"/>
+      <c r="J142" s="26"/>
     </row>
     <row r="143" spans="1:14" ht="18" customHeight="1">
-      <c r="A143" s="21"/>
-      <c r="B143" s="42"/>
-      <c r="C143" s="45"/>
-      <c r="D143" s="31" t="s">
+      <c r="A143" s="19"/>
+      <c r="B143" s="40"/>
+      <c r="C143" s="43"/>
+      <c r="D143" s="29" t="s">
         <v>202</v>
       </c>
-      <c r="E143" s="53"/>
-      <c r="F143" s="53"/>
-      <c r="G143" s="38"/>
-      <c r="H143" s="32"/>
-      <c r="I143" s="17" t="s">
+      <c r="E143" s="51"/>
+      <c r="F143" s="51"/>
+      <c r="G143" s="36"/>
+      <c r="H143" s="30"/>
+      <c r="I143" s="15" t="s">
         <v>197</v>
       </c>
-      <c r="J143" s="28"/>
+      <c r="J143" s="26"/>
     </row>
     <row r="144" spans="1:14" ht="18" customHeight="1">
-      <c r="A144" s="21"/>
-      <c r="B144" s="42"/>
-      <c r="C144" s="45"/>
-      <c r="D144" s="31" t="s">
+      <c r="A144" s="19"/>
+      <c r="B144" s="40"/>
+      <c r="C144" s="43"/>
+      <c r="D144" s="29" t="s">
         <v>203</v>
       </c>
-      <c r="E144" s="53"/>
-      <c r="F144" s="53"/>
-      <c r="G144" s="38"/>
-      <c r="H144" s="32"/>
-      <c r="I144" s="17" t="s">
+      <c r="E144" s="51"/>
+      <c r="F144" s="51"/>
+      <c r="G144" s="36"/>
+      <c r="H144" s="30"/>
+      <c r="I144" s="15" t="s">
         <v>197</v>
       </c>
-      <c r="J144" s="28"/>
+      <c r="J144" s="26"/>
     </row>
     <row r="145" spans="1:10" ht="10.9" customHeight="1">
-      <c r="A145" s="21"/>
-      <c r="B145" s="42"/>
-      <c r="C145" s="45"/>
-      <c r="E145" s="68"/>
-      <c r="F145" s="68"/>
-      <c r="G145" s="38"/>
-      <c r="H145" s="32"/>
-      <c r="I145" s="69"/>
-      <c r="J145" s="70"/>
+      <c r="A145" s="19"/>
+      <c r="B145" s="40"/>
+      <c r="C145" s="43"/>
+      <c r="E145" s="66"/>
+      <c r="F145" s="66"/>
+      <c r="G145" s="36"/>
+      <c r="H145" s="30"/>
+      <c r="I145" s="67"/>
+      <c r="J145" s="68"/>
     </row>
     <row r="146" spans="1:10" ht="18" customHeight="1">
-      <c r="A146" s="21"/>
-      <c r="B146" s="42"/>
-      <c r="C146" s="45"/>
-      <c r="D146" s="31"/>
-      <c r="E146" s="67"/>
-      <c r="F146" s="67"/>
-      <c r="G146" s="38"/>
-      <c r="H146" s="14"/>
-      <c r="I146" s="69"/>
-      <c r="J146" s="70"/>
+      <c r="A146" s="19"/>
+      <c r="B146" s="40"/>
+      <c r="C146" s="43"/>
+      <c r="D146" s="29"/>
+      <c r="E146" s="65"/>
+      <c r="F146" s="65"/>
+      <c r="G146" s="36"/>
+      <c r="H146" s="12"/>
+      <c r="I146" s="67"/>
+      <c r="J146" s="68"/>
     </row>
     <row r="147" spans="1:10" ht="18" customHeight="1">
-      <c r="A147" s="21"/>
-      <c r="B147" s="42"/>
-      <c r="C147" s="45"/>
-      <c r="D147" s="28"/>
-      <c r="E147" s="38"/>
-      <c r="F147" s="38"/>
-      <c r="G147" s="38"/>
-      <c r="H147" s="14"/>
-      <c r="I147" s="28"/>
-      <c r="J147" s="28"/>
+      <c r="A147" s="19"/>
+      <c r="B147" s="40"/>
+      <c r="C147" s="43"/>
+      <c r="D147" s="26"/>
+      <c r="E147" s="36"/>
+      <c r="F147" s="36"/>
+      <c r="G147" s="36"/>
+      <c r="H147" s="12"/>
+      <c r="I147" s="26"/>
+      <c r="J147" s="26"/>
     </row>
     <row r="148" spans="1:10" ht="18" customHeight="1">
-      <c r="A148" s="21"/>
-      <c r="B148" s="20" t="s">
+      <c r="A148" s="19"/>
+      <c r="B148" s="18" t="s">
         <v>204</v>
       </c>
-      <c r="C148" s="45"/>
-      <c r="D148" s="28"/>
-      <c r="E148" s="38"/>
-      <c r="F148" s="38"/>
-      <c r="G148" s="38"/>
-      <c r="H148" s="14"/>
-      <c r="I148" s="28"/>
-      <c r="J148" s="28"/>
+      <c r="C148" s="43"/>
+      <c r="D148" s="26"/>
+      <c r="E148" s="36"/>
+      <c r="F148" s="36"/>
+      <c r="G148" s="36"/>
+      <c r="H148" s="12"/>
+      <c r="I148" s="26"/>
+      <c r="J148" s="26"/>
     </row>
     <row r="149" spans="1:10" ht="16.149999999999999" customHeight="1">
-      <c r="A149" s="21"/>
-      <c r="B149" s="20"/>
-      <c r="C149" s="45"/>
-      <c r="D149" s="28"/>
-      <c r="E149" s="38"/>
-      <c r="F149" s="38"/>
-      <c r="G149" s="38"/>
-      <c r="H149" s="14"/>
-      <c r="I149" s="28"/>
-      <c r="J149" s="28"/>
+      <c r="A149" s="19"/>
+      <c r="B149" s="18"/>
+      <c r="C149" s="43"/>
+      <c r="D149" s="26"/>
+      <c r="E149" s="36"/>
+      <c r="F149" s="36"/>
+      <c r="G149" s="36"/>
+      <c r="H149" s="12"/>
+      <c r="I149" s="26"/>
+      <c r="J149" s="26"/>
     </row>
     <row r="150" spans="1:10" ht="16.149999999999999" customHeight="1">
-      <c r="A150" s="21"/>
-      <c r="B150" s="20"/>
-      <c r="C150" s="45"/>
-      <c r="D150" s="28" t="s">
+      <c r="A150" s="19"/>
+      <c r="B150" s="18"/>
+      <c r="C150" s="43"/>
+      <c r="D150" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="E150" s="34" t="s">
+      <c r="E150" s="32" t="s">
         <v>205</v>
       </c>
-      <c r="F150" s="38" t="s">
+      <c r="F150" s="36" t="s">
         <v>206</v>
       </c>
-      <c r="G150" s="38"/>
-      <c r="H150" s="14"/>
-      <c r="I150" s="28"/>
-      <c r="J150" s="28"/>
+      <c r="G150" s="36"/>
+      <c r="H150" s="12"/>
+      <c r="I150" s="26"/>
+      <c r="J150" s="26"/>
     </row>
     <row r="151" spans="1:10" ht="16.149999999999999" customHeight="1">
-      <c r="A151" s="21"/>
-      <c r="B151" s="20"/>
-      <c r="C151" s="45"/>
-      <c r="D151" s="71"/>
-      <c r="E151" s="72" t="s">
+      <c r="A151" s="19"/>
+      <c r="B151" s="18"/>
+      <c r="C151" s="43"/>
+      <c r="D151" s="69"/>
+      <c r="E151" s="70" t="s">
         <v>207</v>
       </c>
-      <c r="F151" s="73" t="s">
+      <c r="F151" s="71" t="s">
         <v>208</v>
       </c>
-      <c r="G151" s="73"/>
-      <c r="H151" s="74"/>
-      <c r="I151" s="71"/>
-      <c r="J151" s="28"/>
+      <c r="G151" s="71"/>
+      <c r="H151" s="72"/>
+      <c r="I151" s="69"/>
+      <c r="J151" s="26"/>
     </row>
     <row r="152" spans="1:10" ht="18" customHeight="1">
-      <c r="A152" s="21"/>
-      <c r="B152" s="42"/>
-      <c r="C152" s="45"/>
-      <c r="D152" s="75" t="s">
+      <c r="A152" s="19"/>
+      <c r="B152" s="40"/>
+      <c r="C152" s="43"/>
+      <c r="D152" s="73" t="s">
         <v>209</v>
       </c>
-      <c r="E152" s="75" t="s">
+      <c r="E152" s="73" t="s">
         <v>205</v>
       </c>
-      <c r="F152" s="75" t="s">
+      <c r="F152" s="73" t="s">
         <v>210</v>
       </c>
-      <c r="G152" s="76"/>
-      <c r="H152" s="77"/>
-      <c r="I152" s="78"/>
-      <c r="J152" s="28"/>
+      <c r="G152" s="74"/>
+      <c r="H152" s="75"/>
+      <c r="I152" s="76"/>
+      <c r="J152" s="26"/>
     </row>
     <row r="153" spans="1:10" ht="18" customHeight="1">
-      <c r="A153" s="21"/>
-      <c r="B153" s="42"/>
-      <c r="C153" s="45"/>
-      <c r="D153" s="72"/>
-      <c r="E153" s="72" t="s">
+      <c r="A153" s="19"/>
+      <c r="B153" s="40"/>
+      <c r="C153" s="43"/>
+      <c r="D153" s="70"/>
+      <c r="E153" s="70" t="s">
         <v>207</v>
       </c>
-      <c r="F153" s="72" t="s">
+      <c r="F153" s="70" t="s">
         <v>211</v>
       </c>
-      <c r="G153" s="73"/>
-      <c r="H153" s="74"/>
-      <c r="I153" s="71"/>
-      <c r="J153" s="28"/>
+      <c r="G153" s="71"/>
+      <c r="H153" s="72"/>
+      <c r="I153" s="69"/>
+      <c r="J153" s="26"/>
     </row>
     <row r="154" spans="1:10" ht="16.149999999999999" customHeight="1">
-      <c r="A154" s="21"/>
-      <c r="B154" s="20"/>
-      <c r="C154" s="45"/>
-      <c r="D154" s="28" t="s">
+      <c r="A154" s="19"/>
+      <c r="B154" s="18"/>
+      <c r="C154" s="43"/>
+      <c r="D154" s="26" t="s">
         <v>40</v>
       </c>
-      <c r="E154" s="34" t="s">
+      <c r="E154" s="32" t="s">
         <v>205</v>
       </c>
-      <c r="F154" s="38" t="s">
+      <c r="F154" s="36" t="s">
         <v>212</v>
       </c>
-      <c r="G154" s="38"/>
-      <c r="H154" s="14"/>
-      <c r="I154" s="28"/>
-      <c r="J154" s="28"/>
+      <c r="G154" s="36"/>
+      <c r="H154" s="12"/>
+      <c r="I154" s="26"/>
+      <c r="J154" s="26"/>
     </row>
     <row r="155" spans="1:10" ht="16.149999999999999" customHeight="1">
-      <c r="A155" s="21"/>
-      <c r="B155" s="20"/>
-      <c r="C155" s="45"/>
-      <c r="D155" s="71"/>
-      <c r="E155" s="72" t="s">
+      <c r="A155" s="19"/>
+      <c r="B155" s="18"/>
+      <c r="C155" s="43"/>
+      <c r="D155" s="69"/>
+      <c r="E155" s="70" t="s">
         <v>207</v>
       </c>
-      <c r="F155" s="73" t="s">
+      <c r="F155" s="71" t="s">
         <v>213</v>
       </c>
-      <c r="G155" s="73"/>
-      <c r="H155" s="74"/>
-      <c r="I155" s="71"/>
-      <c r="J155" s="28"/>
+      <c r="G155" s="71"/>
+      <c r="H155" s="72"/>
+      <c r="I155" s="69"/>
+      <c r="J155" s="26"/>
     </row>
     <row r="156" spans="1:10" ht="16.149999999999999" customHeight="1">
-      <c r="A156" s="21"/>
-      <c r="B156" s="20"/>
-      <c r="C156" s="45"/>
-      <c r="D156" s="28" t="s">
+      <c r="A156" s="19"/>
+      <c r="B156" s="18"/>
+      <c r="C156" s="43"/>
+      <c r="D156" s="26" t="s">
         <v>41</v>
       </c>
-      <c r="E156" s="34" t="s">
+      <c r="E156" s="32" t="s">
         <v>205</v>
       </c>
-      <c r="F156" s="38" t="s">
+      <c r="F156" s="36" t="s">
         <v>214</v>
       </c>
-      <c r="G156" s="38"/>
-      <c r="H156" s="14"/>
-      <c r="I156" s="28"/>
-      <c r="J156" s="28"/>
+      <c r="G156" s="36"/>
+      <c r="H156" s="12"/>
+      <c r="I156" s="26"/>
+      <c r="J156" s="26"/>
     </row>
     <row r="157" spans="1:10" ht="16.149999999999999" customHeight="1">
-      <c r="A157" s="21"/>
-      <c r="B157" s="20"/>
-      <c r="C157" s="45"/>
-      <c r="D157" s="28"/>
-      <c r="E157" s="34"/>
-      <c r="F157" s="38" t="s">
+      <c r="A157" s="19"/>
+      <c r="B157" s="18"/>
+      <c r="C157" s="43"/>
+      <c r="D157" s="26"/>
+      <c r="E157" s="32"/>
+      <c r="F157" s="36" t="s">
         <v>215</v>
       </c>
-      <c r="G157" s="38"/>
-      <c r="H157" s="14"/>
-      <c r="I157" s="28"/>
-      <c r="J157" s="28"/>
+      <c r="G157" s="36"/>
+      <c r="H157" s="12"/>
+      <c r="I157" s="26"/>
+      <c r="J157" s="26"/>
     </row>
     <row r="158" spans="1:10" ht="16.149999999999999" customHeight="1">
-      <c r="A158" s="21"/>
-      <c r="B158" s="20"/>
-      <c r="C158" s="45"/>
-      <c r="D158" s="71"/>
-      <c r="E158" s="72" t="s">
+      <c r="A158" s="19"/>
+      <c r="B158" s="18"/>
+      <c r="C158" s="43"/>
+      <c r="D158" s="69"/>
+      <c r="E158" s="70" t="s">
         <v>207</v>
       </c>
-      <c r="F158" s="79" t="s">
+      <c r="F158" s="77" t="s">
         <v>216</v>
       </c>
-      <c r="G158" s="73"/>
-      <c r="H158" s="74"/>
-      <c r="I158" s="71"/>
-      <c r="J158" s="28"/>
+      <c r="G158" s="71"/>
+      <c r="H158" s="72"/>
+      <c r="I158" s="69"/>
+      <c r="J158" s="26"/>
     </row>
     <row r="159" spans="1:10" ht="18" customHeight="1">
-      <c r="A159" s="21"/>
-      <c r="B159" s="42"/>
-      <c r="C159" s="42"/>
-      <c r="D159" s="34" t="s">
+      <c r="A159" s="19"/>
+      <c r="B159" s="40"/>
+      <c r="C159" s="40"/>
+      <c r="D159" s="32" t="s">
         <v>217</v>
       </c>
-      <c r="E159" s="34" t="s">
+      <c r="E159" s="32" t="s">
         <v>205</v>
       </c>
-      <c r="F159" s="34" t="s">
+      <c r="F159" s="32" t="s">
         <v>218</v>
       </c>
-      <c r="G159" s="28"/>
-      <c r="H159" s="42"/>
-      <c r="I159" s="21"/>
-      <c r="J159" s="21"/>
+      <c r="G159" s="26"/>
+      <c r="H159" s="40"/>
+      <c r="I159" s="19"/>
+      <c r="J159" s="19"/>
     </row>
     <row r="160" spans="1:10" ht="18" customHeight="1">
-      <c r="A160" s="21"/>
-      <c r="B160" s="42"/>
-      <c r="C160" s="42"/>
-      <c r="D160" s="72"/>
-      <c r="E160" s="72" t="s">
+      <c r="A160" s="19"/>
+      <c r="B160" s="40"/>
+      <c r="C160" s="40"/>
+      <c r="D160" s="70"/>
+      <c r="E160" s="70" t="s">
         <v>207</v>
       </c>
-      <c r="F160" s="72" t="s">
+      <c r="F160" s="70" t="s">
         <v>219</v>
       </c>
-      <c r="G160" s="71"/>
-      <c r="H160" s="80"/>
-      <c r="I160" s="81"/>
-      <c r="J160" s="21"/>
+      <c r="G160" s="69"/>
+      <c r="H160" s="78"/>
+      <c r="I160" s="79"/>
+      <c r="J160" s="19"/>
     </row>
     <row r="161" spans="1:10" ht="18" customHeight="1">
-      <c r="A161" s="21"/>
-      <c r="B161" s="42"/>
-      <c r="C161" s="45"/>
-      <c r="D161" s="34" t="s">
+      <c r="A161" s="19"/>
+      <c r="B161" s="40"/>
+      <c r="C161" s="43"/>
+      <c r="D161" s="32" t="s">
         <v>220</v>
       </c>
-      <c r="E161" s="34" t="s">
+      <c r="E161" s="32" t="s">
         <v>205</v>
       </c>
-      <c r="F161" s="34" t="s">
+      <c r="F161" s="32" t="s">
         <v>221</v>
       </c>
-      <c r="G161" s="38"/>
-      <c r="H161" s="14"/>
-      <c r="I161" s="28"/>
-      <c r="J161" s="28"/>
+      <c r="G161" s="36"/>
+      <c r="H161" s="12"/>
+      <c r="I161" s="26"/>
+      <c r="J161" s="26"/>
     </row>
     <row r="162" spans="1:10" ht="18" customHeight="1">
-      <c r="A162" s="21"/>
-      <c r="B162" s="42"/>
-      <c r="C162" s="45"/>
-      <c r="D162" s="34"/>
-      <c r="E162" s="34" t="s">
+      <c r="A162" s="19"/>
+      <c r="B162" s="40"/>
+      <c r="C162" s="43"/>
+      <c r="D162" s="32"/>
+      <c r="E162" s="32" t="s">
         <v>42</v>
       </c>
-      <c r="F162" s="34" t="s">
+      <c r="F162" s="32" t="s">
         <v>222</v>
       </c>
-      <c r="G162" s="38"/>
-      <c r="H162" s="14"/>
-      <c r="I162" s="28"/>
-      <c r="J162" s="28"/>
+      <c r="G162" s="36"/>
+      <c r="H162" s="12"/>
+      <c r="I162" s="26"/>
+      <c r="J162" s="26"/>
     </row>
     <row r="163" spans="1:10" ht="18" customHeight="1">
-      <c r="A163" s="21"/>
-      <c r="B163" s="42"/>
-      <c r="C163" s="45"/>
-      <c r="D163" s="82"/>
-      <c r="E163" s="72"/>
-      <c r="F163" s="83" t="s">
+      <c r="A163" s="19"/>
+      <c r="B163" s="40"/>
+      <c r="C163" s="43"/>
+      <c r="D163" s="80"/>
+      <c r="E163" s="70"/>
+      <c r="F163" s="81" t="s">
         <v>223</v>
       </c>
-      <c r="G163" s="73"/>
-      <c r="H163" s="74"/>
-      <c r="I163" s="71"/>
-      <c r="J163" s="28"/>
+      <c r="G163" s="71"/>
+      <c r="H163" s="72"/>
+      <c r="I163" s="69"/>
+      <c r="J163" s="26"/>
     </row>
     <row r="164" spans="1:10" ht="18" customHeight="1">
-      <c r="A164" s="21"/>
-      <c r="B164" s="42"/>
-      <c r="C164" s="45"/>
-      <c r="D164" s="34" t="s">
+      <c r="A164" s="19"/>
+      <c r="B164" s="40"/>
+      <c r="C164" s="43"/>
+      <c r="D164" s="32" t="s">
         <v>43</v>
       </c>
-      <c r="E164" s="34" t="s">
+      <c r="E164" s="32" t="s">
         <v>205</v>
       </c>
-      <c r="F164" s="34" t="s">
+      <c r="F164" s="32" t="s">
         <v>224</v>
       </c>
-      <c r="G164" s="38"/>
-      <c r="H164" s="14"/>
-      <c r="I164" s="28"/>
-      <c r="J164" s="28"/>
+      <c r="G164" s="36"/>
+      <c r="H164" s="12"/>
+      <c r="I164" s="26"/>
+      <c r="J164" s="26"/>
     </row>
     <row r="165" spans="1:10" ht="18" customHeight="1">
-      <c r="A165" s="21"/>
-      <c r="B165" s="42"/>
-      <c r="C165" s="45"/>
-      <c r="D165" s="82"/>
-      <c r="E165" s="72" t="s">
+      <c r="A165" s="19"/>
+      <c r="B165" s="40"/>
+      <c r="C165" s="43"/>
+      <c r="D165" s="80"/>
+      <c r="E165" s="70" t="s">
         <v>207</v>
       </c>
-      <c r="F165" s="72" t="s">
+      <c r="F165" s="70" t="s">
         <v>225</v>
       </c>
-      <c r="G165" s="73"/>
-      <c r="H165" s="74"/>
-      <c r="I165" s="71"/>
-      <c r="J165" s="28"/>
+      <c r="G165" s="71"/>
+      <c r="H165" s="72"/>
+      <c r="I165" s="69"/>
+      <c r="J165" s="26"/>
     </row>
     <row r="166" spans="1:10" ht="18" customHeight="1">
-      <c r="A166" s="21"/>
-      <c r="B166" s="42"/>
-      <c r="C166" s="45"/>
-      <c r="D166" s="34" t="s">
+      <c r="A166" s="19"/>
+      <c r="B166" s="40"/>
+      <c r="C166" s="43"/>
+      <c r="D166" s="32" t="s">
         <v>44</v>
       </c>
-      <c r="E166" s="34" t="s">
+      <c r="E166" s="32" t="s">
         <v>205</v>
       </c>
-      <c r="F166" s="34" t="s">
+      <c r="F166" s="32" t="s">
         <v>226</v>
       </c>
-      <c r="G166" s="38"/>
-      <c r="H166" s="14"/>
-      <c r="I166" s="28"/>
-      <c r="J166" s="28"/>
+      <c r="G166" s="36"/>
+      <c r="H166" s="12"/>
+      <c r="I166" s="26"/>
+      <c r="J166" s="26"/>
     </row>
     <row r="167" spans="1:10" ht="18" customHeight="1">
-      <c r="A167" s="21"/>
-      <c r="B167" s="42"/>
-      <c r="C167" s="42"/>
-      <c r="D167" s="72"/>
-      <c r="E167" s="72" t="s">
+      <c r="A167" s="19"/>
+      <c r="B167" s="40"/>
+      <c r="C167" s="40"/>
+      <c r="D167" s="70"/>
+      <c r="E167" s="70" t="s">
         <v>207</v>
       </c>
-      <c r="F167" s="72" t="s">
+      <c r="F167" s="70" t="s">
         <v>227</v>
       </c>
-      <c r="G167" s="71"/>
-      <c r="H167" s="80"/>
-      <c r="I167" s="81"/>
-      <c r="J167" s="21"/>
+      <c r="G167" s="69"/>
+      <c r="H167" s="78"/>
+      <c r="I167" s="79"/>
+      <c r="J167" s="19"/>
     </row>
     <row r="168" spans="1:10" ht="18" customHeight="1">
-      <c r="A168" s="21"/>
-      <c r="B168" s="42"/>
-      <c r="C168" s="45"/>
-      <c r="D168" s="75" t="s">
+      <c r="A168" s="19"/>
+      <c r="B168" s="40"/>
+      <c r="C168" s="43"/>
+      <c r="D168" s="73" t="s">
         <v>228</v>
       </c>
-      <c r="E168" s="75" t="s">
+      <c r="E168" s="73" t="s">
         <v>205</v>
       </c>
-      <c r="F168" s="75" t="s">
+      <c r="F168" s="73" t="s">
         <v>229</v>
       </c>
-      <c r="G168" s="76"/>
-      <c r="H168" s="77"/>
-      <c r="I168" s="78"/>
-      <c r="J168" s="28"/>
+      <c r="G168" s="74"/>
+      <c r="H168" s="75"/>
+      <c r="I168" s="76"/>
+      <c r="J168" s="26"/>
     </row>
     <row r="169" spans="1:10" ht="18" customHeight="1">
-      <c r="A169" s="21"/>
-      <c r="B169" s="42"/>
-      <c r="C169" s="45"/>
-      <c r="D169" s="82"/>
-      <c r="E169" s="72" t="s">
+      <c r="A169" s="19"/>
+      <c r="B169" s="40"/>
+      <c r="C169" s="43"/>
+      <c r="D169" s="80"/>
+      <c r="E169" s="70" t="s">
         <v>207</v>
       </c>
-      <c r="F169" s="72" t="s">
+      <c r="F169" s="70" t="s">
         <v>230</v>
       </c>
-      <c r="G169" s="73"/>
-      <c r="H169" s="74"/>
-      <c r="I169" s="71"/>
-      <c r="J169" s="28"/>
+      <c r="G169" s="71"/>
+      <c r="H169" s="72"/>
+      <c r="I169" s="69"/>
+      <c r="J169" s="26"/>
     </row>
     <row r="170" spans="1:10" ht="18" customHeight="1">
-      <c r="A170" s="21"/>
-      <c r="B170" s="42"/>
-      <c r="C170" s="45"/>
-      <c r="D170" s="34" t="s">
+      <c r="A170" s="19"/>
+      <c r="B170" s="40"/>
+      <c r="C170" s="43"/>
+      <c r="D170" s="32" t="s">
         <v>45</v>
       </c>
-      <c r="E170" s="34" t="s">
+      <c r="E170" s="32" t="s">
         <v>205</v>
       </c>
-      <c r="F170" s="34" t="s">
+      <c r="F170" s="32" t="s">
         <v>231</v>
       </c>
-      <c r="G170" s="38"/>
-      <c r="H170" s="14"/>
-      <c r="I170" s="28"/>
-      <c r="J170" s="28"/>
+      <c r="G170" s="36"/>
+      <c r="H170" s="12"/>
+      <c r="I170" s="26"/>
+      <c r="J170" s="26"/>
     </row>
     <row r="171" spans="1:10" ht="18" customHeight="1">
-      <c r="A171" s="21"/>
-      <c r="B171" s="42"/>
-      <c r="C171" s="45"/>
-      <c r="D171" s="72"/>
-      <c r="E171" s="72" t="s">
+      <c r="A171" s="19"/>
+      <c r="B171" s="40"/>
+      <c r="C171" s="43"/>
+      <c r="D171" s="70"/>
+      <c r="E171" s="70" t="s">
         <v>207</v>
       </c>
-      <c r="F171" s="84" t="s">
+      <c r="F171" s="82" t="s">
         <v>232</v>
       </c>
-      <c r="G171" s="73"/>
-      <c r="H171" s="74"/>
-      <c r="I171" s="71"/>
-      <c r="J171" s="28"/>
+      <c r="G171" s="71"/>
+      <c r="H171" s="72"/>
+      <c r="I171" s="69"/>
+      <c r="J171" s="26"/>
     </row>
     <row r="172" spans="1:10" ht="18" customHeight="1">
-      <c r="A172" s="21"/>
-      <c r="B172" s="42"/>
-      <c r="C172" s="45"/>
-      <c r="D172" s="34" t="s">
+      <c r="A172" s="19"/>
+      <c r="B172" s="40"/>
+      <c r="C172" s="43"/>
+      <c r="D172" s="32" t="s">
         <v>233</v>
       </c>
-      <c r="E172" s="34" t="s">
+      <c r="E172" s="32" t="s">
         <v>205</v>
       </c>
-      <c r="F172" s="32" t="s">
+      <c r="F172" s="30" t="s">
         <v>234</v>
       </c>
-      <c r="G172" s="38"/>
-      <c r="H172" s="14"/>
-      <c r="I172" s="28"/>
-      <c r="J172" s="28"/>
+      <c r="G172" s="36"/>
+      <c r="H172" s="12"/>
+      <c r="I172" s="26"/>
+      <c r="J172" s="26"/>
     </row>
     <row r="173" spans="1:10" ht="18" customHeight="1">
-      <c r="A173" s="21"/>
-      <c r="B173" s="42"/>
-      <c r="C173" s="45"/>
-      <c r="D173" s="34"/>
-      <c r="E173" s="34"/>
-      <c r="F173" s="34" t="s">
+      <c r="A173" s="19"/>
+      <c r="B173" s="40"/>
+      <c r="C173" s="43"/>
+      <c r="D173" s="32"/>
+      <c r="E173" s="32"/>
+      <c r="F173" s="32" t="s">
         <v>235</v>
       </c>
-      <c r="G173" s="38"/>
-      <c r="H173" s="14"/>
-      <c r="I173" s="28"/>
-      <c r="J173" s="28"/>
+      <c r="G173" s="36"/>
+      <c r="H173" s="12"/>
+      <c r="I173" s="26"/>
+      <c r="J173" s="26"/>
     </row>
     <row r="174" spans="1:10" ht="18" customHeight="1">
-      <c r="A174" s="21"/>
-      <c r="B174" s="42"/>
-      <c r="C174" s="45"/>
-      <c r="D174" s="34"/>
-      <c r="E174" s="34" t="s">
+      <c r="A174" s="19"/>
+      <c r="B174" s="40"/>
+      <c r="C174" s="43"/>
+      <c r="D174" s="32"/>
+      <c r="E174" s="32" t="s">
         <v>42</v>
       </c>
-      <c r="F174" s="32" t="s">
+      <c r="F174" s="30" t="s">
         <v>236</v>
       </c>
-      <c r="G174" s="38"/>
-      <c r="H174" s="14"/>
-      <c r="I174" s="28"/>
-      <c r="J174" s="28"/>
+      <c r="G174" s="36"/>
+      <c r="H174" s="12"/>
+      <c r="I174" s="26"/>
+      <c r="J174" s="26"/>
     </row>
     <row r="175" spans="1:10" ht="18" customHeight="1">
-      <c r="A175" s="21"/>
-      <c r="B175" s="42"/>
-      <c r="C175" s="45"/>
-      <c r="D175" s="72"/>
-      <c r="E175" s="72"/>
-      <c r="F175" s="72" t="s">
+      <c r="A175" s="19"/>
+      <c r="B175" s="40"/>
+      <c r="C175" s="43"/>
+      <c r="D175" s="70"/>
+      <c r="E175" s="70"/>
+      <c r="F175" s="70" t="s">
         <v>237</v>
       </c>
-      <c r="G175" s="73"/>
-      <c r="H175" s="74"/>
-      <c r="I175" s="71"/>
-      <c r="J175" s="28"/>
+      <c r="G175" s="71"/>
+      <c r="H175" s="72"/>
+      <c r="I175" s="69"/>
+      <c r="J175" s="26"/>
     </row>
     <row r="176" spans="1:10" ht="18" customHeight="1">
-      <c r="A176" s="21"/>
-      <c r="B176" s="42"/>
-      <c r="C176" s="45"/>
-      <c r="D176" s="34" t="s">
+      <c r="A176" s="19"/>
+      <c r="B176" s="40"/>
+      <c r="C176" s="43"/>
+      <c r="D176" s="32" t="s">
         <v>238</v>
       </c>
-      <c r="E176" s="34" t="s">
+      <c r="E176" s="32" t="s">
         <v>205</v>
       </c>
-      <c r="F176" s="38" t="s">
+      <c r="F176" s="36" t="s">
         <v>239</v>
       </c>
-      <c r="G176" s="38"/>
-      <c r="H176" s="14"/>
-      <c r="I176" s="28"/>
-      <c r="J176" s="28"/>
+      <c r="G176" s="36"/>
+      <c r="H176" s="12"/>
+      <c r="I176" s="26"/>
+      <c r="J176" s="26"/>
     </row>
     <row r="177" spans="1:10" ht="18" customHeight="1">
-      <c r="A177" s="21"/>
-      <c r="B177" s="42"/>
-      <c r="C177" s="45"/>
-      <c r="D177" s="72"/>
-      <c r="E177" s="72" t="s">
+      <c r="A177" s="19"/>
+      <c r="B177" s="40"/>
+      <c r="C177" s="43"/>
+      <c r="D177" s="70"/>
+      <c r="E177" s="70" t="s">
         <v>207</v>
       </c>
-      <c r="F177" s="73" t="s">
+      <c r="F177" s="71" t="s">
         <v>240</v>
       </c>
-      <c r="G177" s="73"/>
-      <c r="H177" s="74"/>
-      <c r="I177" s="71"/>
-      <c r="J177" s="28"/>
+      <c r="G177" s="71"/>
+      <c r="H177" s="72"/>
+      <c r="I177" s="69"/>
+      <c r="J177" s="26"/>
     </row>
     <row r="178" spans="1:10" ht="18" customHeight="1">
-      <c r="A178" s="21"/>
-      <c r="B178" s="42"/>
-      <c r="C178" s="45"/>
-      <c r="D178" s="34" t="s">
+      <c r="A178" s="19"/>
+      <c r="B178" s="40"/>
+      <c r="C178" s="43"/>
+      <c r="D178" s="32" t="s">
         <v>46</v>
       </c>
-      <c r="E178" s="34" t="s">
+      <c r="E178" s="32" t="s">
         <v>205</v>
       </c>
-      <c r="F178" s="34" t="s">
+      <c r="F178" s="32" t="s">
         <v>241</v>
       </c>
-      <c r="G178" s="38"/>
-      <c r="H178" s="14"/>
-      <c r="I178" s="28"/>
-      <c r="J178" s="28"/>
+      <c r="G178" s="36"/>
+      <c r="H178" s="12"/>
+      <c r="I178" s="26"/>
+      <c r="J178" s="26"/>
     </row>
     <row r="179" spans="1:10" ht="18" customHeight="1">
-      <c r="A179" s="21"/>
-      <c r="B179" s="42"/>
-      <c r="C179" s="45"/>
-      <c r="D179" s="72"/>
-      <c r="E179" s="72" t="s">
+      <c r="A179" s="19"/>
+      <c r="B179" s="40"/>
+      <c r="C179" s="43"/>
+      <c r="D179" s="70"/>
+      <c r="E179" s="70" t="s">
         <v>42</v>
       </c>
-      <c r="F179" s="72" t="s">
+      <c r="F179" s="70" t="s">
         <v>242</v>
       </c>
-      <c r="G179" s="73"/>
-      <c r="H179" s="74"/>
-      <c r="I179" s="71"/>
-      <c r="J179" s="28"/>
+      <c r="G179" s="71"/>
+      <c r="H179" s="72"/>
+      <c r="I179" s="69"/>
+      <c r="J179" s="26"/>
     </row>
     <row r="180" spans="1:10">
-      <c r="A180" s="52"/>
+      <c r="A180" s="50"/>
     </row>
     <row r="181" spans="1:10" ht="18" customHeight="1">
-      <c r="A181" s="21"/>
-      <c r="B181" s="20" t="s">
+      <c r="A181" s="19"/>
+      <c r="B181" s="18" t="s">
         <v>243</v>
       </c>
-      <c r="C181" s="21"/>
-      <c r="D181" s="42"/>
-      <c r="E181" s="42"/>
-      <c r="F181" s="42"/>
-      <c r="G181" s="42"/>
-      <c r="H181" s="42"/>
-      <c r="I181" s="21"/>
-      <c r="J181" s="21"/>
+      <c r="C181" s="19"/>
+      <c r="D181" s="40"/>
+      <c r="E181" s="40"/>
+      <c r="F181" s="40"/>
+      <c r="G181" s="40"/>
+      <c r="H181" s="40"/>
+      <c r="I181" s="19"/>
+      <c r="J181" s="19"/>
     </row>
     <row r="182" spans="1:10" ht="18" customHeight="1">
-      <c r="A182" s="21"/>
-      <c r="B182" s="20"/>
-      <c r="C182" s="21"/>
-      <c r="D182" s="42"/>
-      <c r="E182" s="42"/>
-      <c r="F182" s="42"/>
-      <c r="G182" s="42"/>
-      <c r="H182" s="42"/>
-      <c r="I182" s="21"/>
-      <c r="J182" s="21"/>
+      <c r="A182" s="19"/>
+      <c r="B182" s="18"/>
+      <c r="C182" s="19"/>
+      <c r="D182" s="40"/>
+      <c r="E182" s="40"/>
+      <c r="F182" s="40"/>
+      <c r="G182" s="40"/>
+      <c r="H182" s="40"/>
+      <c r="I182" s="19"/>
+      <c r="J182" s="19"/>
     </row>
     <row r="183" spans="1:10" ht="18" customHeight="1">
-      <c r="A183" s="21"/>
-      <c r="B183" s="45"/>
-      <c r="C183" s="28" t="s">
+      <c r="A183" s="19"/>
+      <c r="B183" s="43"/>
+      <c r="C183" s="26" t="s">
         <v>244</v>
       </c>
-      <c r="D183" s="28"/>
-      <c r="E183" s="28"/>
-      <c r="F183" s="28"/>
-      <c r="G183" s="28"/>
-      <c r="H183" s="28"/>
-      <c r="I183" s="28"/>
-      <c r="J183" s="28"/>
+      <c r="D183" s="26"/>
+      <c r="E183" s="26"/>
+      <c r="F183" s="26"/>
+      <c r="G183" s="26"/>
+      <c r="H183" s="26"/>
+      <c r="I183" s="26"/>
+      <c r="J183" s="26"/>
     </row>
     <row r="184" spans="1:10" ht="18" customHeight="1">
-      <c r="A184" s="21"/>
-      <c r="B184" s="21"/>
-      <c r="C184" s="69" t="s">
+      <c r="A184" s="19"/>
+      <c r="B184" s="19"/>
+      <c r="C184" s="67" t="s">
         <v>245</v>
       </c>
-      <c r="D184" s="28" t="s">
+      <c r="D184" s="26" t="s">
         <v>246</v>
       </c>
-      <c r="E184" s="28"/>
-      <c r="F184" s="28"/>
-      <c r="G184" s="28"/>
-      <c r="H184" s="28"/>
-      <c r="I184" s="28"/>
-      <c r="J184" s="28"/>
+      <c r="E184" s="26"/>
+      <c r="F184" s="26"/>
+      <c r="G184" s="26"/>
+      <c r="H184" s="26"/>
+      <c r="I184" s="26"/>
+      <c r="J184" s="26"/>
     </row>
     <row r="185" spans="1:10" ht="18" customHeight="1">
-      <c r="A185" s="21"/>
-      <c r="B185" s="21"/>
-      <c r="C185" s="69" t="s">
+      <c r="A185" s="19"/>
+      <c r="B185" s="19"/>
+      <c r="C185" s="67" t="s">
         <v>245</v>
       </c>
-      <c r="D185" s="28" t="s">
+      <c r="D185" s="26" t="s">
         <v>247</v>
       </c>
-      <c r="E185" s="28"/>
-      <c r="F185" s="28"/>
-      <c r="G185" s="28"/>
-      <c r="H185" s="28"/>
-      <c r="I185" s="28"/>
-      <c r="J185" s="28"/>
+      <c r="E185" s="26"/>
+      <c r="F185" s="26"/>
+      <c r="G185" s="26"/>
+      <c r="H185" s="26"/>
+      <c r="I185" s="26"/>
+      <c r="J185" s="26"/>
     </row>
     <row r="186" spans="1:10" ht="18" customHeight="1">
-      <c r="A186" s="21"/>
-      <c r="B186" s="21"/>
-      <c r="C186" s="69" t="s">
+      <c r="A186" s="19"/>
+      <c r="B186" s="19"/>
+      <c r="C186" s="67" t="s">
         <v>245</v>
       </c>
-      <c r="D186" s="28" t="s">
+      <c r="D186" s="26" t="s">
         <v>248</v>
       </c>
-      <c r="E186" s="28"/>
-      <c r="F186" s="28"/>
-      <c r="G186" s="28"/>
-      <c r="H186" s="28"/>
-      <c r="I186" s="28"/>
-      <c r="J186" s="28"/>
+      <c r="E186" s="26"/>
+      <c r="F186" s="26"/>
+      <c r="G186" s="26"/>
+      <c r="H186" s="26"/>
+      <c r="I186" s="26"/>
+      <c r="J186" s="26"/>
     </row>
     <row r="187" spans="1:10" ht="18" customHeight="1">
-      <c r="A187" s="21"/>
-      <c r="B187" s="21"/>
-      <c r="C187" s="69"/>
-      <c r="D187" s="28" t="s">
+      <c r="A187" s="19"/>
+      <c r="B187" s="19"/>
+      <c r="C187" s="67"/>
+      <c r="D187" s="26" t="s">
         <v>249</v>
       </c>
-      <c r="E187" s="28"/>
-      <c r="F187" s="28"/>
-      <c r="G187" s="28"/>
-      <c r="H187" s="28"/>
-      <c r="I187" s="28"/>
-      <c r="J187" s="28"/>
+      <c r="E187" s="26"/>
+      <c r="F187" s="26"/>
+      <c r="G187" s="26"/>
+      <c r="H187" s="26"/>
+      <c r="I187" s="26"/>
+      <c r="J187" s="26"/>
     </row>
     <row r="188" spans="1:10" ht="18" customHeight="1">
-      <c r="A188" s="21"/>
-      <c r="B188" s="21"/>
-      <c r="C188" s="69"/>
-      <c r="D188" s="28"/>
-      <c r="E188" s="28"/>
-      <c r="F188" s="28"/>
-      <c r="G188" s="28"/>
-      <c r="H188" s="28"/>
-      <c r="I188" s="28"/>
-      <c r="J188" s="28"/>
+      <c r="A188" s="19"/>
+      <c r="B188" s="19"/>
+      <c r="C188" s="67"/>
+      <c r="D188" s="26"/>
+      <c r="E188" s="26"/>
+      <c r="F188" s="26"/>
+      <c r="G188" s="26"/>
+      <c r="H188" s="26"/>
+      <c r="I188" s="26"/>
+      <c r="J188" s="26"/>
     </row>
     <row r="189" spans="1:10" ht="18" customHeight="1">
-      <c r="A189" s="21"/>
-      <c r="B189" s="45"/>
-      <c r="C189" s="28" t="s">
+      <c r="A189" s="19"/>
+      <c r="B189" s="43"/>
+      <c r="C189" s="26" t="s">
         <v>250</v>
       </c>
-      <c r="D189" s="28"/>
-      <c r="E189" s="28"/>
-      <c r="F189" s="28"/>
-      <c r="G189" s="28"/>
-      <c r="H189" s="28"/>
-      <c r="I189" s="28"/>
-      <c r="J189" s="28"/>
+      <c r="D189" s="26"/>
+      <c r="E189" s="26"/>
+      <c r="F189" s="26"/>
+      <c r="G189" s="26"/>
+      <c r="H189" s="26"/>
+      <c r="I189" s="26"/>
+      <c r="J189" s="26"/>
     </row>
     <row r="190" spans="1:10" ht="18" customHeight="1">
-      <c r="A190" s="21"/>
-      <c r="B190" s="21"/>
-      <c r="C190" s="69" t="s">
+      <c r="A190" s="19"/>
+      <c r="B190" s="19"/>
+      <c r="C190" s="67" t="s">
         <v>245</v>
       </c>
-      <c r="D190" s="28" t="s">
+      <c r="D190" s="26" t="s">
         <v>251</v>
       </c>
-      <c r="E190" s="28"/>
-      <c r="F190" s="28"/>
-      <c r="G190" s="28"/>
-      <c r="H190" s="28"/>
-      <c r="J190" s="28"/>
+      <c r="E190" s="26"/>
+      <c r="F190" s="26"/>
+      <c r="G190" s="26"/>
+      <c r="H190" s="26"/>
+      <c r="J190" s="26"/>
     </row>
     <row r="191" spans="1:10" ht="18" customHeight="1">
-      <c r="A191" s="21"/>
-      <c r="B191" s="21"/>
-      <c r="C191" s="69" t="s">
+      <c r="A191" s="19"/>
+      <c r="B191" s="19"/>
+      <c r="C191" s="67" t="s">
         <v>245</v>
       </c>
-      <c r="D191" s="28" t="s">
+      <c r="D191" s="26" t="s">
         <v>252</v>
       </c>
-      <c r="E191" s="28"/>
-      <c r="F191" s="28"/>
-      <c r="G191" s="28"/>
-      <c r="H191" s="28"/>
-      <c r="J191" s="28"/>
+      <c r="E191" s="26"/>
+      <c r="F191" s="26"/>
+      <c r="G191" s="26"/>
+      <c r="H191" s="26"/>
+      <c r="J191" s="26"/>
     </row>
     <row r="192" spans="1:10" ht="18" customHeight="1">
-      <c r="A192" s="21"/>
-      <c r="B192" s="21"/>
-      <c r="C192" s="69" t="s">
+      <c r="A192" s="19"/>
+      <c r="B192" s="19"/>
+      <c r="C192" s="67" t="s">
         <v>245</v>
       </c>
-      <c r="D192" s="28" t="s">
+      <c r="D192" s="26" t="s">
         <v>253</v>
       </c>
-      <c r="E192" s="28"/>
-      <c r="F192" s="28"/>
-      <c r="G192" s="28"/>
-      <c r="H192" s="28"/>
-      <c r="J192" s="28"/>
+      <c r="E192" s="26"/>
+      <c r="F192" s="26"/>
+      <c r="G192" s="26"/>
+      <c r="H192" s="26"/>
+      <c r="J192" s="26"/>
     </row>
     <row r="193" spans="1:10" ht="18" customHeight="1">
-      <c r="A193" s="21"/>
-      <c r="B193" s="21"/>
-      <c r="C193" s="69"/>
-      <c r="D193" s="28"/>
-      <c r="E193" s="28"/>
-      <c r="F193" s="28"/>
-      <c r="G193" s="28"/>
-      <c r="H193" s="28"/>
-      <c r="I193" s="28" t="s">
+      <c r="A193" s="19"/>
+      <c r="B193" s="19"/>
+      <c r="C193" s="67"/>
+      <c r="D193" s="26"/>
+      <c r="E193" s="26"/>
+      <c r="F193" s="26"/>
+      <c r="G193" s="26"/>
+      <c r="H193" s="26"/>
+      <c r="I193" s="26" t="s">
         <v>254</v>
       </c>
-      <c r="J193" s="28"/>
+      <c r="J193" s="26"/>
     </row>
     <row r="194" spans="1:10" ht="18" customHeight="1">
-      <c r="A194" s="21"/>
-      <c r="B194" s="45"/>
-      <c r="C194" s="28" t="s">
+      <c r="A194" s="19"/>
+      <c r="B194" s="43"/>
+      <c r="C194" s="26" t="s">
         <v>255</v>
       </c>
-      <c r="D194" s="28"/>
-      <c r="E194" s="28"/>
-      <c r="F194" s="28"/>
-      <c r="G194" s="28"/>
-      <c r="H194" s="51"/>
-      <c r="I194" s="28" t="s">
+      <c r="D194" s="26"/>
+      <c r="E194" s="26"/>
+      <c r="F194" s="26"/>
+      <c r="G194" s="26"/>
+      <c r="H194" s="49"/>
+      <c r="I194" s="26" t="s">
         <v>256</v>
       </c>
-      <c r="J194" s="28"/>
+      <c r="J194" s="26"/>
     </row>
     <row r="195" spans="1:10" ht="18" customHeight="1">
-      <c r="A195" s="21"/>
-      <c r="B195" s="45"/>
-      <c r="C195" s="28"/>
-      <c r="D195" s="28"/>
-      <c r="E195" s="28"/>
-      <c r="F195" s="28"/>
-      <c r="G195" s="28"/>
-      <c r="H195" s="51"/>
-      <c r="I195" s="28"/>
-      <c r="J195" s="28"/>
+      <c r="A195" s="19"/>
+      <c r="B195" s="43"/>
+      <c r="C195" s="26"/>
+      <c r="D195" s="26"/>
+      <c r="E195" s="26"/>
+      <c r="F195" s="26"/>
+      <c r="G195" s="26"/>
+      <c r="H195" s="49"/>
+      <c r="I195" s="26"/>
+      <c r="J195" s="26"/>
     </row>
     <row r="196" spans="1:10" ht="18" customHeight="1">
-      <c r="A196" s="21"/>
-      <c r="B196" s="45"/>
-      <c r="C196" s="28" t="s">
+      <c r="A196" s="19"/>
+      <c r="B196" s="43"/>
+      <c r="C196" s="26" t="s">
         <v>257</v>
       </c>
-      <c r="D196" s="28"/>
-      <c r="E196" s="28"/>
-      <c r="F196" s="28"/>
-      <c r="G196" s="28"/>
-      <c r="H196" s="51"/>
-      <c r="I196" s="28" t="s">
+      <c r="D196" s="26"/>
+      <c r="E196" s="26"/>
+      <c r="F196" s="26"/>
+      <c r="G196" s="26"/>
+      <c r="H196" s="49"/>
+      <c r="I196" s="26" t="s">
         <v>258</v>
       </c>
-      <c r="J196" s="28"/>
+      <c r="J196" s="26"/>
     </row>
     <row r="197" spans="1:10" ht="18" customHeight="1">
-      <c r="A197" s="21"/>
-      <c r="B197" s="45"/>
-      <c r="C197" s="28"/>
-      <c r="D197" s="28" t="s">
+      <c r="A197" s="19"/>
+      <c r="B197" s="43"/>
+      <c r="C197" s="26"/>
+      <c r="D197" s="26" t="s">
         <v>259</v>
       </c>
-      <c r="E197" s="28"/>
-      <c r="F197" s="28"/>
-      <c r="G197" s="28"/>
-      <c r="H197" s="51"/>
-      <c r="I197" s="28"/>
-      <c r="J197" s="28"/>
+      <c r="E197" s="26"/>
+      <c r="F197" s="26"/>
+      <c r="G197" s="26"/>
+      <c r="H197" s="49"/>
+      <c r="I197" s="26"/>
+      <c r="J197" s="26"/>
     </row>
     <row r="198" spans="1:10" ht="18" customHeight="1">
-      <c r="A198" s="21"/>
-      <c r="B198" s="21"/>
-      <c r="C198" s="69" t="s">
+      <c r="A198" s="19"/>
+      <c r="B198" s="19"/>
+      <c r="C198" s="67" t="s">
         <v>245</v>
       </c>
-      <c r="D198" s="28" t="s">
+      <c r="D198" s="26" t="s">
         <v>260</v>
       </c>
-      <c r="E198" s="28"/>
-      <c r="F198" s="28"/>
-      <c r="G198" s="28"/>
-      <c r="H198" s="51"/>
-      <c r="I198" s="51"/>
-      <c r="J198" s="51"/>
+      <c r="E198" s="26"/>
+      <c r="F198" s="26"/>
+      <c r="G198" s="26"/>
+      <c r="H198" s="49"/>
+      <c r="I198" s="49"/>
+      <c r="J198" s="49"/>
     </row>
     <row r="199" spans="1:10" ht="18" customHeight="1">
-      <c r="A199" s="21"/>
-      <c r="B199" s="42"/>
-      <c r="C199" s="69" t="s">
+      <c r="A199" s="19"/>
+      <c r="B199" s="40"/>
+      <c r="C199" s="67" t="s">
         <v>245</v>
       </c>
-      <c r="D199" s="28" t="s">
+      <c r="D199" s="26" t="s">
         <v>261</v>
       </c>
-      <c r="E199" s="28"/>
-      <c r="F199" s="28"/>
-      <c r="G199" s="28"/>
-      <c r="H199" s="28"/>
-      <c r="I199" s="28"/>
-      <c r="J199" s="28"/>
+      <c r="E199" s="26"/>
+      <c r="F199" s="26"/>
+      <c r="G199" s="26"/>
+      <c r="H199" s="26"/>
+      <c r="I199" s="26"/>
+      <c r="J199" s="26"/>
     </row>
     <row r="200" spans="1:10" ht="18" customHeight="1">
-      <c r="A200" s="21"/>
-      <c r="B200" s="42"/>
-      <c r="C200" s="69" t="s">
+      <c r="A200" s="19"/>
+      <c r="B200" s="40"/>
+      <c r="C200" s="67" t="s">
         <v>245</v>
       </c>
-      <c r="D200" s="28" t="s">
+      <c r="D200" s="26" t="s">
         <v>262</v>
       </c>
-      <c r="E200" s="28"/>
-      <c r="F200" s="28"/>
-      <c r="G200" s="28"/>
-      <c r="H200" s="28"/>
-      <c r="I200" s="28"/>
-      <c r="J200" s="28"/>
+      <c r="E200" s="26"/>
+      <c r="F200" s="26"/>
+      <c r="G200" s="26"/>
+      <c r="H200" s="26"/>
+      <c r="I200" s="26"/>
+      <c r="J200" s="26"/>
     </row>
     <row r="201" spans="1:10" ht="18" customHeight="1">
-      <c r="A201" s="21"/>
-      <c r="B201" s="42"/>
-      <c r="C201" s="69"/>
-      <c r="D201" s="28" t="s">
+      <c r="A201" s="19"/>
+      <c r="B201" s="40"/>
+      <c r="C201" s="67"/>
+      <c r="D201" s="26" t="s">
         <v>263</v>
       </c>
-      <c r="E201" s="28"/>
-      <c r="F201" s="28"/>
-      <c r="G201" s="28"/>
-      <c r="H201" s="28"/>
-      <c r="I201" s="28"/>
-      <c r="J201" s="28"/>
+      <c r="E201" s="26"/>
+      <c r="F201" s="26"/>
+      <c r="G201" s="26"/>
+      <c r="H201" s="26"/>
+      <c r="I201" s="26"/>
+      <c r="J201" s="26"/>
     </row>
     <row r="202" spans="1:10" ht="18" customHeight="1">
-      <c r="A202" s="21"/>
-      <c r="B202" s="42"/>
-      <c r="C202" s="69" t="s">
+      <c r="A202" s="19"/>
+      <c r="B202" s="40"/>
+      <c r="C202" s="67" t="s">
         <v>245</v>
       </c>
-      <c r="D202" s="28" t="s">
+      <c r="D202" s="26" t="s">
         <v>264</v>
       </c>
-      <c r="E202" s="28"/>
-      <c r="F202" s="28"/>
-      <c r="G202" s="28"/>
-      <c r="H202" s="28"/>
-      <c r="I202" s="28"/>
-      <c r="J202" s="28"/>
+      <c r="E202" s="26"/>
+      <c r="F202" s="26"/>
+      <c r="G202" s="26"/>
+      <c r="H202" s="26"/>
+      <c r="I202" s="26"/>
+      <c r="J202" s="26"/>
     </row>
     <row r="203" spans="1:10" ht="18" customHeight="1">
-      <c r="A203" s="21"/>
-      <c r="B203" s="42"/>
-      <c r="C203" s="69" t="s">
+      <c r="A203" s="19"/>
+      <c r="B203" s="40"/>
+      <c r="C203" s="67" t="s">
         <v>245</v>
       </c>
-      <c r="D203" s="28" t="s">
+      <c r="D203" s="26" t="s">
         <v>265</v>
       </c>
-      <c r="E203" s="28"/>
-      <c r="F203" s="28"/>
-      <c r="G203" s="28"/>
-      <c r="H203" s="28"/>
-      <c r="I203" s="28"/>
-      <c r="J203" s="28"/>
+      <c r="E203" s="26"/>
+      <c r="F203" s="26"/>
+      <c r="G203" s="26"/>
+      <c r="H203" s="26"/>
+      <c r="I203" s="26"/>
+      <c r="J203" s="26"/>
     </row>
     <row r="204" spans="1:10" ht="18" customHeight="1">
-      <c r="A204" s="21"/>
-      <c r="B204" s="42"/>
-      <c r="C204" s="69" t="s">
+      <c r="A204" s="19"/>
+      <c r="B204" s="40"/>
+      <c r="C204" s="67" t="s">
         <v>245</v>
       </c>
-      <c r="D204" s="28" t="s">
+      <c r="D204" s="26" t="s">
         <v>266</v>
       </c>
-      <c r="E204" s="28"/>
-      <c r="F204" s="28"/>
-      <c r="G204" s="28"/>
-      <c r="H204" s="28"/>
-      <c r="I204" s="28"/>
-      <c r="J204" s="28"/>
+      <c r="E204" s="26"/>
+      <c r="F204" s="26"/>
+      <c r="G204" s="26"/>
+      <c r="H204" s="26"/>
+      <c r="I204" s="26"/>
+      <c r="J204" s="26"/>
     </row>
     <row r="205" spans="1:10" ht="18" customHeight="1">
-      <c r="A205" s="21"/>
-      <c r="B205" s="42"/>
-      <c r="C205" s="69" t="s">
+      <c r="A205" s="19"/>
+      <c r="B205" s="40"/>
+      <c r="C205" s="67" t="s">
         <v>245</v>
       </c>
-      <c r="D205" s="28" t="s">
+      <c r="D205" s="26" t="s">
         <v>267</v>
       </c>
-      <c r="E205" s="28"/>
-      <c r="F205" s="28"/>
-      <c r="G205" s="28"/>
-      <c r="H205" s="28"/>
-      <c r="I205" s="28"/>
-      <c r="J205" s="28"/>
+      <c r="E205" s="26"/>
+      <c r="F205" s="26"/>
+      <c r="G205" s="26"/>
+      <c r="H205" s="26"/>
+      <c r="I205" s="26"/>
+      <c r="J205" s="26"/>
     </row>
     <row r="206" spans="1:10" ht="18" customHeight="1">
-      <c r="A206" s="21"/>
-      <c r="B206" s="42"/>
-      <c r="C206" s="69" t="s">
+      <c r="A206" s="19"/>
+      <c r="B206" s="40"/>
+      <c r="C206" s="67" t="s">
         <v>245</v>
       </c>
-      <c r="D206" s="28" t="s">
+      <c r="D206" s="26" t="s">
         <v>268</v>
       </c>
-      <c r="E206" s="28"/>
-      <c r="F206" s="28"/>
-      <c r="G206" s="28"/>
-      <c r="H206" s="28"/>
-      <c r="I206" s="28"/>
-      <c r="J206" s="28"/>
+      <c r="E206" s="26"/>
+      <c r="F206" s="26"/>
+      <c r="G206" s="26"/>
+      <c r="H206" s="26"/>
+      <c r="I206" s="26"/>
+      <c r="J206" s="26"/>
     </row>
     <row r="207" spans="1:10" ht="18" customHeight="1">
-      <c r="A207" s="21"/>
-      <c r="B207" s="42"/>
-      <c r="C207" s="69" t="s">
+      <c r="A207" s="19"/>
+      <c r="B207" s="40"/>
+      <c r="C207" s="67" t="s">
         <v>245</v>
       </c>
-      <c r="D207" s="28" t="s">
+      <c r="D207" s="26" t="s">
         <v>269</v>
       </c>
-      <c r="E207" s="28"/>
-      <c r="F207" s="28"/>
-      <c r="G207" s="28"/>
-      <c r="H207" s="28"/>
-      <c r="I207" s="28"/>
-      <c r="J207" s="28"/>
+      <c r="E207" s="26"/>
+      <c r="F207" s="26"/>
+      <c r="G207" s="26"/>
+      <c r="H207" s="26"/>
+      <c r="I207" s="26"/>
+      <c r="J207" s="26"/>
     </row>
     <row r="208" spans="1:10" ht="18" customHeight="1">
-      <c r="A208" s="21"/>
-      <c r="B208" s="42"/>
-      <c r="C208" s="69" t="s">
+      <c r="A208" s="19"/>
+      <c r="B208" s="40"/>
+      <c r="C208" s="67" t="s">
         <v>245</v>
       </c>
-      <c r="D208" s="28" t="s">
+      <c r="D208" s="26" t="s">
         <v>270</v>
       </c>
-      <c r="E208" s="28"/>
-      <c r="F208" s="28"/>
-      <c r="G208" s="28"/>
-      <c r="H208" s="28"/>
-      <c r="I208" s="28"/>
-      <c r="J208" s="28"/>
+      <c r="E208" s="26"/>
+      <c r="F208" s="26"/>
+      <c r="G208" s="26"/>
+      <c r="H208" s="26"/>
+      <c r="I208" s="26"/>
+      <c r="J208" s="26"/>
     </row>
     <row r="209" spans="1:10" ht="18" customHeight="1">
-      <c r="A209" s="21"/>
-      <c r="B209" s="42"/>
-      <c r="C209" s="69"/>
-      <c r="D209" s="28"/>
-      <c r="E209" s="28"/>
-      <c r="F209" s="28"/>
-      <c r="G209" s="28"/>
-      <c r="H209" s="28"/>
-      <c r="I209" s="28"/>
-      <c r="J209" s="28"/>
+      <c r="A209" s="19"/>
+      <c r="B209" s="40"/>
+      <c r="C209" s="67"/>
+      <c r="D209" s="26"/>
+      <c r="E209" s="26"/>
+      <c r="F209" s="26"/>
+      <c r="G209" s="26"/>
+      <c r="H209" s="26"/>
+      <c r="I209" s="26"/>
+      <c r="J209" s="26"/>
     </row>
     <row r="210" spans="1:10" ht="18" customHeight="1">
-      <c r="A210" s="21"/>
-      <c r="B210" s="20" t="s">
+      <c r="A210" s="19"/>
+      <c r="B210" s="18" t="s">
         <v>271</v>
       </c>
-      <c r="C210" s="28"/>
-      <c r="D210" s="28"/>
-      <c r="E210" s="28"/>
-      <c r="F210" s="28"/>
-      <c r="G210" s="28"/>
-      <c r="H210" s="28"/>
-      <c r="I210" s="28"/>
-      <c r="J210" s="28"/>
+      <c r="C210" s="26"/>
+      <c r="D210" s="26"/>
+      <c r="E210" s="26"/>
+      <c r="F210" s="26"/>
+      <c r="G210" s="26"/>
+      <c r="H210" s="26"/>
+      <c r="I210" s="26"/>
+      <c r="J210" s="26"/>
     </row>
     <row r="211" spans="1:10" ht="18" customHeight="1">
-      <c r="A211" s="21"/>
-      <c r="B211" s="27"/>
-      <c r="C211" s="69" t="s">
+      <c r="A211" s="19"/>
+      <c r="B211" s="25"/>
+      <c r="C211" s="67" t="s">
         <v>245</v>
       </c>
-      <c r="D211" s="28" t="s">
+      <c r="D211" s="26" t="s">
         <v>272</v>
       </c>
-      <c r="E211" s="28"/>
-      <c r="F211" s="28"/>
-      <c r="G211" s="28"/>
-      <c r="H211" s="28"/>
-      <c r="I211" s="28"/>
-      <c r="J211" s="28"/>
+      <c r="E211" s="26"/>
+      <c r="F211" s="26"/>
+      <c r="G211" s="26"/>
+      <c r="H211" s="26"/>
+      <c r="I211" s="26"/>
+      <c r="J211" s="26"/>
     </row>
     <row r="212" spans="1:10" ht="18" customHeight="1">
-      <c r="A212" s="21"/>
-      <c r="B212" s="27"/>
-      <c r="C212" s="69" t="s">
+      <c r="A212" s="19"/>
+      <c r="B212" s="25"/>
+      <c r="C212" s="67" t="s">
         <v>245</v>
       </c>
-      <c r="D212" s="28" t="s">
+      <c r="D212" s="26" t="s">
         <v>273</v>
       </c>
-      <c r="E212" s="28"/>
-      <c r="F212" s="28"/>
-      <c r="G212" s="28"/>
-      <c r="H212" s="28"/>
-      <c r="I212" s="28"/>
-      <c r="J212" s="28"/>
+      <c r="E212" s="26"/>
+      <c r="F212" s="26"/>
+      <c r="G212" s="26"/>
+      <c r="H212" s="26"/>
+      <c r="I212" s="26"/>
+      <c r="J212" s="26"/>
     </row>
     <row r="213" spans="1:10" ht="18" customHeight="1">
-      <c r="A213" s="21"/>
-      <c r="B213" s="27"/>
-      <c r="C213" s="69" t="s">
+      <c r="A213" s="19"/>
+      <c r="B213" s="25"/>
+      <c r="C213" s="67" t="s">
         <v>245</v>
       </c>
-      <c r="D213" s="28" t="s">
+      <c r="D213" s="26" t="s">
         <v>274</v>
       </c>
-      <c r="E213" s="28"/>
-      <c r="F213" s="28"/>
-      <c r="G213" s="28"/>
-      <c r="H213" s="28"/>
-      <c r="I213" s="28"/>
-      <c r="J213" s="28"/>
+      <c r="E213" s="26"/>
+      <c r="F213" s="26"/>
+      <c r="G213" s="26"/>
+      <c r="H213" s="26"/>
+      <c r="I213" s="26"/>
+      <c r="J213" s="26"/>
     </row>
     <row r="214" spans="1:10" ht="18" customHeight="1">
-      <c r="A214" s="21"/>
-      <c r="B214" s="27"/>
-      <c r="C214" s="69" t="s">
+      <c r="A214" s="19"/>
+      <c r="B214" s="25"/>
+      <c r="C214" s="67" t="s">
         <v>245</v>
       </c>
-      <c r="D214" s="28" t="s">
+      <c r="D214" s="26" t="s">
         <v>275</v>
       </c>
-      <c r="E214" s="28"/>
-      <c r="F214" s="28"/>
-      <c r="H214" s="28"/>
-      <c r="I214" s="28"/>
-      <c r="J214" s="28"/>
+      <c r="E214" s="26"/>
+      <c r="F214" s="26"/>
+      <c r="H214" s="26"/>
+      <c r="I214" s="26"/>
+      <c r="J214" s="26"/>
     </row>
     <row r="215" spans="1:10" ht="18" customHeight="1">
-      <c r="A215" s="21"/>
-      <c r="B215" s="27"/>
-      <c r="C215" s="69"/>
-      <c r="D215" s="28"/>
-      <c r="E215" s="28"/>
-      <c r="F215" s="28"/>
-      <c r="G215" s="28"/>
-      <c r="H215" s="28"/>
-      <c r="I215" s="28"/>
-      <c r="J215" s="28"/>
+      <c r="A215" s="19"/>
+      <c r="B215" s="25"/>
+      <c r="C215" s="67"/>
+      <c r="D215" s="26"/>
+      <c r="E215" s="26"/>
+      <c r="F215" s="26"/>
+      <c r="G215" s="26"/>
+      <c r="H215" s="26"/>
+      <c r="I215" s="26"/>
+      <c r="J215" s="26"/>
     </row>
     <row r="216" spans="1:10" ht="18" customHeight="1">
-      <c r="A216" s="21"/>
-      <c r="B216" s="27"/>
-      <c r="C216" s="69"/>
-      <c r="D216" s="28"/>
-      <c r="E216" s="28"/>
-      <c r="F216" s="28"/>
-      <c r="G216" s="28"/>
-      <c r="H216" s="28"/>
-      <c r="I216" s="28"/>
-      <c r="J216" s="28"/>
+      <c r="A216" s="19"/>
+      <c r="B216" s="25"/>
+      <c r="C216" s="67"/>
+      <c r="D216" s="26"/>
+      <c r="E216" s="26"/>
+      <c r="F216" s="26"/>
+      <c r="G216" s="26"/>
+      <c r="H216" s="26"/>
+      <c r="I216" s="26"/>
+      <c r="J216" s="26"/>
     </row>
     <row r="217" spans="1:10" ht="18" customHeight="1">
-      <c r="A217" s="21"/>
-      <c r="B217" s="27"/>
-      <c r="C217" s="69"/>
-      <c r="D217" s="28"/>
-      <c r="E217" s="28"/>
-      <c r="F217" s="28"/>
-      <c r="G217" s="28"/>
-      <c r="H217" s="28"/>
-      <c r="I217" s="28"/>
-      <c r="J217" s="28"/>
+      <c r="A217" s="19"/>
+      <c r="B217" s="25"/>
+      <c r="C217" s="67"/>
+      <c r="D217" s="26"/>
+      <c r="E217" s="26"/>
+      <c r="F217" s="26"/>
+      <c r="G217" s="26"/>
+      <c r="H217" s="26"/>
+      <c r="I217" s="26"/>
+      <c r="J217" s="26"/>
     </row>
     <row r="218" spans="1:10" ht="18" customHeight="1">
-      <c r="A218" s="21"/>
-      <c r="B218" s="27"/>
-      <c r="C218" s="69"/>
-      <c r="D218" s="28"/>
-      <c r="E218" s="28"/>
-      <c r="F218" s="28"/>
-      <c r="G218" s="28"/>
-      <c r="H218" s="28"/>
-      <c r="I218" s="28"/>
-      <c r="J218" s="28"/>
+      <c r="A218" s="19"/>
+      <c r="B218" s="25"/>
+      <c r="C218" s="67"/>
+      <c r="D218" s="26"/>
+      <c r="E218" s="26"/>
+      <c r="F218" s="26"/>
+      <c r="G218" s="26"/>
+      <c r="H218" s="26"/>
+      <c r="I218" s="26"/>
+      <c r="J218" s="26"/>
     </row>
     <row r="219" spans="1:10" ht="18" customHeight="1">
-      <c r="A219" s="21"/>
-      <c r="B219" s="27"/>
-      <c r="C219" s="69"/>
-      <c r="D219" s="28"/>
-      <c r="E219" s="28"/>
-      <c r="F219" s="28"/>
-      <c r="G219" s="28"/>
-      <c r="H219" s="28"/>
-      <c r="I219" s="28"/>
-      <c r="J219" s="28"/>
+      <c r="A219" s="19"/>
+      <c r="B219" s="25"/>
+      <c r="C219" s="67"/>
+      <c r="D219" s="26"/>
+      <c r="E219" s="26"/>
+      <c r="F219" s="26"/>
+      <c r="G219" s="26"/>
+      <c r="H219" s="26"/>
+      <c r="I219" s="26"/>
+      <c r="J219" s="26"/>
     </row>
     <row r="220" spans="1:10" ht="18" customHeight="1">
-      <c r="A220" s="21"/>
-      <c r="B220" s="27"/>
-      <c r="C220" s="69"/>
-      <c r="D220" s="28"/>
-      <c r="E220" s="28"/>
-      <c r="F220" s="28"/>
-      <c r="G220" s="28"/>
-      <c r="H220" s="28"/>
-      <c r="I220" s="28"/>
-      <c r="J220" s="28"/>
+      <c r="A220" s="19"/>
+      <c r="B220" s="25"/>
+      <c r="C220" s="67"/>
+      <c r="D220" s="26"/>
+      <c r="E220" s="26"/>
+      <c r="F220" s="26"/>
+      <c r="G220" s="26"/>
+      <c r="H220" s="26"/>
+      <c r="I220" s="26"/>
+      <c r="J220" s="26"/>
     </row>
     <row r="221" spans="1:10" ht="18" customHeight="1">
-      <c r="A221" s="85" t="s">
+      <c r="A221" s="83" t="s">
         <v>276</v>
       </c>
-      <c r="B221" s="27"/>
-      <c r="C221" s="69"/>
-      <c r="D221" s="28"/>
-      <c r="E221" s="28"/>
-      <c r="F221" s="28"/>
-      <c r="G221" s="28"/>
-      <c r="H221" s="28"/>
-      <c r="I221" s="28"/>
-      <c r="J221" s="28"/>
+      <c r="B221" s="25"/>
+      <c r="C221" s="67"/>
+      <c r="D221" s="26"/>
+      <c r="E221" s="26"/>
+      <c r="F221" s="26"/>
+      <c r="G221" s="26"/>
+      <c r="H221" s="26"/>
+      <c r="I221" s="26"/>
+      <c r="J221" s="26"/>
     </row>
     <row r="222" spans="1:10" ht="18" customHeight="1">
-      <c r="A222" s="25" t="s">
+      <c r="A222" s="23" t="s">
         <v>277</v>
       </c>
-      <c r="B222" s="21"/>
-      <c r="C222" s="21"/>
-      <c r="D222" s="21"/>
-      <c r="E222" s="21"/>
-      <c r="F222" s="21"/>
-      <c r="G222" s="21"/>
-      <c r="H222" s="21"/>
-      <c r="I222" s="21"/>
-      <c r="J222" s="21"/>
+      <c r="B222" s="19"/>
+      <c r="C222" s="19"/>
+      <c r="D222" s="19"/>
+      <c r="E222" s="19"/>
+      <c r="F222" s="19"/>
+      <c r="G222" s="19"/>
+      <c r="H222" s="19"/>
+      <c r="I222" s="19"/>
+      <c r="J222" s="19"/>
     </row>
     <row r="223" spans="1:10" ht="5.45" customHeight="1">
-      <c r="A223" s="20"/>
-      <c r="B223" s="21"/>
-      <c r="C223" s="27"/>
-      <c r="D223" s="21"/>
-      <c r="E223" s="21"/>
-      <c r="F223" s="21"/>
-      <c r="G223" s="21"/>
-      <c r="H223" s="21"/>
-      <c r="I223" s="21"/>
-      <c r="J223" s="21"/>
+      <c r="A223" s="18"/>
+      <c r="B223" s="19"/>
+      <c r="C223" s="25"/>
+      <c r="D223" s="19"/>
+      <c r="E223" s="19"/>
+      <c r="F223" s="19"/>
+      <c r="G223" s="19"/>
+      <c r="H223" s="19"/>
+      <c r="I223" s="19"/>
+      <c r="J223" s="19"/>
     </row>
     <row r="224" spans="1:10" ht="15" customHeight="1">
-      <c r="A224" s="21"/>
-      <c r="B224" s="20" t="s">
+      <c r="A224" s="19"/>
+      <c r="B224" s="18" t="s">
         <v>278</v>
       </c>
-      <c r="C224" s="27"/>
-      <c r="D224" s="21"/>
-      <c r="E224" s="21"/>
-      <c r="F224" s="21"/>
-      <c r="G224" s="21"/>
-      <c r="H224" s="21"/>
-      <c r="I224" s="21"/>
-      <c r="J224" s="21"/>
+      <c r="C224" s="25"/>
+      <c r="D224" s="19"/>
+      <c r="E224" s="19"/>
+      <c r="F224" s="19"/>
+      <c r="G224" s="19"/>
+      <c r="H224" s="19"/>
+      <c r="I224" s="19"/>
+      <c r="J224" s="19"/>
     </row>
     <row r="225" spans="1:10" ht="9" customHeight="1">
-      <c r="A225" s="21"/>
-      <c r="B225" s="27"/>
-      <c r="C225" s="21"/>
-      <c r="D225" s="21"/>
-      <c r="E225" s="21"/>
-      <c r="F225" s="21"/>
-      <c r="G225" s="21"/>
-      <c r="H225" s="21"/>
-      <c r="I225" s="21"/>
-      <c r="J225" s="21"/>
+      <c r="A225" s="19"/>
+      <c r="B225" s="25"/>
+      <c r="C225" s="19"/>
+      <c r="D225" s="19"/>
+      <c r="E225" s="19"/>
+      <c r="F225" s="19"/>
+      <c r="G225" s="19"/>
+      <c r="H225" s="19"/>
+      <c r="I225" s="19"/>
+      <c r="J225" s="19"/>
     </row>
     <row r="226" spans="1:10" ht="16.899999999999999" customHeight="1">
-      <c r="A226" s="21"/>
-      <c r="B226" s="27"/>
-      <c r="C226" s="21"/>
-      <c r="D226" s="28" t="s">
+      <c r="A226" s="19"/>
+      <c r="B226" s="25"/>
+      <c r="C226" s="19"/>
+      <c r="D226" s="26" t="s">
         <v>47</v>
       </c>
-      <c r="E226" s="28" t="s">
+      <c r="E226" s="26" t="s">
         <v>279</v>
       </c>
-      <c r="F226" s="21"/>
-      <c r="G226" s="21"/>
-      <c r="H226" s="21"/>
-      <c r="I226" s="21"/>
-      <c r="J226" s="21"/>
+      <c r="F226" s="19"/>
+      <c r="G226" s="19"/>
+      <c r="H226" s="19"/>
+      <c r="I226" s="19"/>
+      <c r="J226" s="19"/>
     </row>
     <row r="227" spans="1:10" ht="16.899999999999999" customHeight="1">
-      <c r="A227" s="21"/>
-      <c r="B227" s="27"/>
-      <c r="C227" s="27"/>
-      <c r="D227" s="28" t="s">
+      <c r="A227" s="19"/>
+      <c r="B227" s="25"/>
+      <c r="C227" s="25"/>
+      <c r="D227" s="26" t="s">
         <v>280</v>
       </c>
-      <c r="E227" s="32" t="s">
+      <c r="E227" s="30" t="s">
         <v>281</v>
       </c>
-      <c r="H227" s="45"/>
-      <c r="I227" s="28"/>
-      <c r="J227" s="27"/>
+      <c r="H227" s="43"/>
+      <c r="I227" s="26"/>
+      <c r="J227" s="25"/>
     </row>
     <row r="228" spans="1:10" ht="16.899999999999999" customHeight="1">
-      <c r="A228" s="21"/>
-      <c r="B228" s="27"/>
-      <c r="C228" s="27"/>
-      <c r="D228" s="28" t="s">
+      <c r="A228" s="19"/>
+      <c r="B228" s="25"/>
+      <c r="C228" s="25"/>
+      <c r="D228" s="26" t="s">
         <v>282</v>
       </c>
-      <c r="E228" s="32" t="s">
+      <c r="E228" s="30" t="s">
         <v>283</v>
       </c>
-      <c r="I228" s="28"/>
-      <c r="J228" s="27"/>
+      <c r="I228" s="26"/>
+      <c r="J228" s="25"/>
     </row>
     <row r="229" spans="1:10" ht="16.899999999999999" customHeight="1">
-      <c r="A229" s="21"/>
-      <c r="B229" s="27"/>
-      <c r="C229" s="27"/>
-      <c r="D229" s="28"/>
-      <c r="E229" s="32" t="s">
+      <c r="A229" s="19"/>
+      <c r="B229" s="25"/>
+      <c r="C229" s="25"/>
+      <c r="D229" s="26"/>
+      <c r="E229" s="30" t="s">
         <v>284</v>
       </c>
-      <c r="I229" s="28"/>
-      <c r="J229" s="27"/>
+      <c r="I229" s="26"/>
+      <c r="J229" s="25"/>
     </row>
     <row r="230" spans="1:10" ht="16.899999999999999" customHeight="1">
-      <c r="A230" s="21"/>
-      <c r="B230" s="27"/>
-      <c r="C230" s="27"/>
-      <c r="D230" s="28" t="s">
+      <c r="A230" s="19"/>
+      <c r="B230" s="25"/>
+      <c r="C230" s="25"/>
+      <c r="D230" s="26" t="s">
         <v>285</v>
       </c>
-      <c r="E230" s="32" t="s">
+      <c r="E230" s="30" t="s">
         <v>286</v>
       </c>
-      <c r="I230" s="28"/>
-      <c r="J230" s="27"/>
+      <c r="I230" s="26"/>
+      <c r="J230" s="25"/>
     </row>
     <row r="231" spans="1:10" ht="16.899999999999999" customHeight="1">
-      <c r="A231" s="21"/>
-      <c r="B231" s="27"/>
-      <c r="C231" s="27"/>
-      <c r="D231" s="28"/>
-      <c r="E231" s="32" t="s">
+      <c r="A231" s="19"/>
+      <c r="B231" s="25"/>
+      <c r="C231" s="25"/>
+      <c r="D231" s="26"/>
+      <c r="E231" s="30" t="s">
         <v>287</v>
       </c>
-      <c r="I231" s="28"/>
-      <c r="J231" s="27"/>
+      <c r="I231" s="26"/>
+      <c r="J231" s="25"/>
     </row>
     <row r="232" spans="1:10" ht="16.899999999999999" customHeight="1">
-      <c r="A232" s="21"/>
-      <c r="B232" s="27"/>
-      <c r="C232" s="27"/>
-      <c r="D232" s="28" t="s">
+      <c r="A232" s="19"/>
+      <c r="B232" s="25"/>
+      <c r="C232" s="25"/>
+      <c r="D232" s="26" t="s">
         <v>50</v>
       </c>
-      <c r="E232" s="28" t="s">
+      <c r="E232" s="26" t="s">
         <v>288</v>
       </c>
-      <c r="F232" s="45"/>
-      <c r="G232" s="45"/>
-      <c r="H232" s="45"/>
-      <c r="I232" s="28"/>
-      <c r="J232" s="27"/>
+      <c r="F232" s="43"/>
+      <c r="G232" s="43"/>
+      <c r="H232" s="43"/>
+      <c r="I232" s="26"/>
+      <c r="J232" s="25"/>
     </row>
     <row r="233" spans="1:10" ht="16.899999999999999" customHeight="1">
-      <c r="A233" s="21"/>
-      <c r="B233" s="27"/>
-      <c r="C233" s="27"/>
-      <c r="D233" s="28" t="s">
+      <c r="A233" s="19"/>
+      <c r="B233" s="25"/>
+      <c r="C233" s="25"/>
+      <c r="D233" s="26" t="s">
         <v>51</v>
       </c>
-      <c r="E233" s="32" t="s">
+      <c r="E233" s="30" t="s">
         <v>289</v>
       </c>
-      <c r="G233" s="52"/>
-      <c r="H233" s="45"/>
-      <c r="I233" s="28"/>
-      <c r="J233" s="27"/>
+      <c r="G233" s="50"/>
+      <c r="H233" s="43"/>
+      <c r="I233" s="26"/>
+      <c r="J233" s="25"/>
     </row>
     <row r="234" spans="1:10" ht="16.899999999999999" customHeight="1">
-      <c r="A234" s="21"/>
-      <c r="B234" s="27"/>
-      <c r="C234" s="27"/>
-      <c r="D234" s="28" t="s">
+      <c r="A234" s="19"/>
+      <c r="B234" s="25"/>
+      <c r="C234" s="25"/>
+      <c r="D234" s="26" t="s">
         <v>290</v>
       </c>
-      <c r="E234" s="32" t="s">
+      <c r="E234" s="30" t="s">
         <v>291</v>
       </c>
-      <c r="H234" s="52"/>
-      <c r="I234" s="28"/>
-      <c r="J234" s="27"/>
+      <c r="H234" s="50"/>
+      <c r="I234" s="26"/>
+      <c r="J234" s="25"/>
     </row>
     <row r="235" spans="1:10" ht="16.899999999999999" customHeight="1">
-      <c r="A235" s="21"/>
-      <c r="B235" s="27"/>
-      <c r="C235" s="27"/>
-      <c r="D235" s="28" t="s">
+      <c r="A235" s="19"/>
+      <c r="B235" s="25"/>
+      <c r="C235" s="25"/>
+      <c r="D235" s="26" t="s">
         <v>292</v>
       </c>
-      <c r="E235" s="32" t="s">
+      <c r="E235" s="30" t="s">
         <v>293</v>
       </c>
-      <c r="F235" s="45"/>
-      <c r="G235" s="45"/>
-      <c r="H235" s="45"/>
-      <c r="I235" s="51"/>
-      <c r="J235" s="27"/>
+      <c r="F235" s="43"/>
+      <c r="G235" s="43"/>
+      <c r="H235" s="43"/>
+      <c r="I235" s="49"/>
+      <c r="J235" s="25"/>
     </row>
     <row r="236" spans="1:10" ht="16.899999999999999" customHeight="1">
-      <c r="A236" s="21"/>
-      <c r="B236" s="27"/>
-      <c r="C236" s="27"/>
-      <c r="D236" s="28"/>
-      <c r="E236" s="28" t="s">
+      <c r="A236" s="19"/>
+      <c r="B236" s="25"/>
+      <c r="C236" s="25"/>
+      <c r="D236" s="26"/>
+      <c r="E236" s="26" t="s">
         <v>294</v>
       </c>
-      <c r="F236" s="45"/>
-      <c r="G236" s="45"/>
-      <c r="H236" s="45"/>
-      <c r="I236" s="51"/>
-      <c r="J236" s="27"/>
+      <c r="F236" s="43"/>
+      <c r="G236" s="43"/>
+      <c r="H236" s="43"/>
+      <c r="I236" s="49"/>
+      <c r="J236" s="25"/>
     </row>
     <row r="237" spans="1:10" ht="16.899999999999999" customHeight="1">
-      <c r="A237" s="21"/>
-      <c r="B237" s="27"/>
-      <c r="C237" s="27"/>
-      <c r="D237" s="28" t="s">
+      <c r="A237" s="19"/>
+      <c r="B237" s="25"/>
+      <c r="C237" s="25"/>
+      <c r="D237" s="26" t="s">
         <v>52</v>
       </c>
-      <c r="E237" s="28" t="s">
+      <c r="E237" s="26" t="s">
         <v>295</v>
       </c>
-      <c r="F237" s="45"/>
-      <c r="G237" s="45"/>
-      <c r="H237" s="45"/>
-      <c r="I237" s="51"/>
-      <c r="J237" s="27"/>
+      <c r="F237" s="43"/>
+      <c r="G237" s="43"/>
+      <c r="H237" s="43"/>
+      <c r="I237" s="49"/>
+      <c r="J237" s="25"/>
     </row>
     <row r="238" spans="1:10" ht="16.899999999999999" customHeight="1">
-      <c r="A238" s="21"/>
-      <c r="B238" s="27"/>
-      <c r="C238" s="27"/>
-      <c r="D238" s="28" t="s">
+      <c r="A238" s="19"/>
+      <c r="B238" s="25"/>
+      <c r="C238" s="25"/>
+      <c r="D238" s="26" t="s">
         <v>296</v>
       </c>
-      <c r="E238" s="32" t="s">
+      <c r="E238" s="30" t="s">
         <v>297</v>
       </c>
-      <c r="I238" s="28"/>
-      <c r="J238" s="27"/>
+      <c r="I238" s="26"/>
+      <c r="J238" s="25"/>
     </row>
     <row r="239" spans="1:10" ht="16.899999999999999" customHeight="1">
-      <c r="A239" s="21"/>
-      <c r="B239" s="27"/>
-      <c r="C239" s="27"/>
-      <c r="D239" s="28" t="s">
+      <c r="A239" s="19"/>
+      <c r="B239" s="25"/>
+      <c r="C239" s="25"/>
+      <c r="D239" s="26" t="s">
         <v>298</v>
       </c>
-      <c r="E239" s="32" t="s">
+      <c r="E239" s="30" t="s">
         <v>299</v>
       </c>
-      <c r="F239" s="45"/>
-      <c r="G239" s="45"/>
-      <c r="H239" s="51"/>
-      <c r="I239" s="51"/>
-      <c r="J239" s="27"/>
+      <c r="F239" s="43"/>
+      <c r="G239" s="43"/>
+      <c r="H239" s="49"/>
+      <c r="I239" s="49"/>
+      <c r="J239" s="25"/>
     </row>
     <row r="240" spans="1:10" ht="16.899999999999999" customHeight="1">
-      <c r="A240" s="21"/>
-      <c r="B240" s="27"/>
-      <c r="C240" s="27"/>
-      <c r="D240" s="28"/>
-      <c r="E240" s="32" t="s">
+      <c r="A240" s="19"/>
+      <c r="B240" s="25"/>
+      <c r="C240" s="25"/>
+      <c r="D240" s="26"/>
+      <c r="E240" s="30" t="s">
         <v>300</v>
       </c>
-      <c r="F240" s="45"/>
-      <c r="G240" s="45"/>
-      <c r="H240" s="51"/>
-      <c r="I240" s="51"/>
-      <c r="J240" s="27"/>
+      <c r="F240" s="43"/>
+      <c r="G240" s="43"/>
+      <c r="H240" s="49"/>
+      <c r="I240" s="49"/>
+      <c r="J240" s="25"/>
     </row>
     <row r="241" spans="1:10" ht="16.899999999999999" customHeight="1">
-      <c r="A241" s="21"/>
-      <c r="B241" s="27"/>
-      <c r="C241" s="27"/>
-      <c r="D241" s="28" t="s">
+      <c r="A241" s="19"/>
+      <c r="B241" s="25"/>
+      <c r="C241" s="25"/>
+      <c r="D241" s="26" t="s">
         <v>53</v>
       </c>
-      <c r="E241" s="32" t="s">
+      <c r="E241" s="30" t="s">
         <v>301</v>
       </c>
-      <c r="F241" s="45"/>
-      <c r="G241" s="45"/>
-      <c r="H241" s="51"/>
-      <c r="I241" s="51"/>
-      <c r="J241" s="27"/>
+      <c r="F241" s="43"/>
+      <c r="G241" s="43"/>
+      <c r="H241" s="49"/>
+      <c r="I241" s="49"/>
+      <c r="J241" s="25"/>
     </row>
     <row r="242" spans="1:10" ht="16.899999999999999" customHeight="1">
-      <c r="A242" s="21"/>
-      <c r="B242" s="27"/>
-      <c r="C242" s="45"/>
-      <c r="D242" s="28" t="s">
+      <c r="A242" s="19"/>
+      <c r="B242" s="25"/>
+      <c r="C242" s="43"/>
+      <c r="D242" s="26" t="s">
         <v>54</v>
       </c>
-      <c r="E242" s="28" t="s">
+      <c r="E242" s="26" t="s">
         <v>302</v>
       </c>
-      <c r="F242" s="28"/>
-      <c r="G242" s="28"/>
-      <c r="H242" s="51"/>
-      <c r="I242" s="51"/>
-      <c r="J242" s="86"/>
+      <c r="F242" s="26"/>
+      <c r="G242" s="26"/>
+      <c r="H242" s="49"/>
+      <c r="I242" s="49"/>
+      <c r="J242" s="84"/>
     </row>
     <row r="243" spans="1:10" ht="16.899999999999999" customHeight="1">
-      <c r="A243" s="21"/>
-      <c r="B243" s="27"/>
-      <c r="C243" s="45"/>
-      <c r="D243" s="28"/>
-      <c r="E243" s="28" t="s">
+      <c r="A243" s="19"/>
+      <c r="B243" s="25"/>
+      <c r="C243" s="43"/>
+      <c r="D243" s="26"/>
+      <c r="E243" s="26" t="s">
         <v>303</v>
       </c>
-      <c r="F243" s="28"/>
-      <c r="G243" s="28"/>
-      <c r="H243" s="51"/>
-      <c r="I243" s="51"/>
-      <c r="J243" s="86"/>
+      <c r="F243" s="26"/>
+      <c r="G243" s="26"/>
+      <c r="H243" s="49"/>
+      <c r="I243" s="49"/>
+      <c r="J243" s="84"/>
     </row>
     <row r="244" spans="1:10" ht="16.899999999999999" customHeight="1">
-      <c r="A244" s="21"/>
-      <c r="B244" s="27"/>
-      <c r="C244" s="27"/>
-      <c r="D244" s="28" t="s">
+      <c r="A244" s="19"/>
+      <c r="B244" s="25"/>
+      <c r="C244" s="25"/>
+      <c r="D244" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="E244" s="32" t="s">
+      <c r="E244" s="30" t="s">
         <v>304</v>
       </c>
-      <c r="I244" s="28"/>
-      <c r="J244" s="27"/>
+      <c r="I244" s="26"/>
+      <c r="J244" s="25"/>
     </row>
     <row r="245" spans="1:10" ht="16.899999999999999" customHeight="1">
-      <c r="A245" s="21"/>
-      <c r="B245" s="27"/>
-      <c r="C245" s="27"/>
-      <c r="D245" s="28" t="s">
+      <c r="A245" s="19"/>
+      <c r="B245" s="25"/>
+      <c r="C245" s="25"/>
+      <c r="D245" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="E245" s="32" t="s">
+      <c r="E245" s="30" t="s">
         <v>305</v>
       </c>
-      <c r="F245" s="32"/>
-      <c r="G245" s="32"/>
-      <c r="J245" s="27"/>
+      <c r="F245" s="30"/>
+      <c r="G245" s="30"/>
+      <c r="J245" s="25"/>
     </row>
     <row r="246" spans="1:10" ht="16.899999999999999" customHeight="1">
-      <c r="A246" s="21"/>
-      <c r="B246" s="27"/>
-      <c r="C246" s="27"/>
-      <c r="D246" s="28" t="s">
+      <c r="A246" s="19"/>
+      <c r="B246" s="25"/>
+      <c r="C246" s="25"/>
+      <c r="D246" s="26" t="s">
         <v>306</v>
       </c>
-      <c r="E246" s="28" t="s">
+      <c r="E246" s="26" t="s">
         <v>307</v>
       </c>
-      <c r="F246" s="52"/>
-      <c r="G246" s="52"/>
-      <c r="H246" s="52"/>
-      <c r="I246" s="28"/>
-      <c r="J246" s="27"/>
+      <c r="F246" s="50"/>
+      <c r="G246" s="50"/>
+      <c r="H246" s="50"/>
+      <c r="I246" s="26"/>
+      <c r="J246" s="25"/>
     </row>
     <row r="247" spans="1:10" ht="16.899999999999999" customHeight="1">
-      <c r="A247" s="21"/>
-      <c r="B247" s="27"/>
-      <c r="C247" s="27"/>
-      <c r="D247" s="28" t="s">
+      <c r="A247" s="19"/>
+      <c r="B247" s="25"/>
+      <c r="C247" s="25"/>
+      <c r="D247" s="26" t="s">
         <v>308</v>
       </c>
-      <c r="E247" s="32" t="s">
+      <c r="E247" s="30" t="s">
         <v>309</v>
       </c>
-      <c r="H247" s="52"/>
-      <c r="I247" s="28"/>
-      <c r="J247" s="27"/>
+      <c r="H247" s="50"/>
+      <c r="I247" s="26"/>
+      <c r="J247" s="25"/>
     </row>
     <row r="248" spans="1:10" ht="16.899999999999999" customHeight="1">
-      <c r="A248" s="21"/>
-      <c r="B248" s="27"/>
-      <c r="C248" s="27"/>
-      <c r="D248" s="28" t="s">
+      <c r="A248" s="19"/>
+      <c r="B248" s="25"/>
+      <c r="C248" s="25"/>
+      <c r="D248" s="26" t="s">
         <v>310</v>
       </c>
-      <c r="E248" s="32" t="s">
+      <c r="E248" s="30" t="s">
         <v>311</v>
       </c>
-      <c r="I248" s="27"/>
-      <c r="J248" s="27"/>
+      <c r="I248" s="25"/>
+      <c r="J248" s="25"/>
     </row>
     <row r="249" spans="1:10" ht="16.899999999999999" customHeight="1">
-      <c r="A249" s="21"/>
-      <c r="B249" s="27"/>
-      <c r="C249" s="27"/>
-      <c r="D249" s="28" t="s">
+      <c r="A249" s="19"/>
+      <c r="B249" s="25"/>
+      <c r="C249" s="25"/>
+      <c r="D249" s="26" t="s">
         <v>57</v>
       </c>
-      <c r="E249" s="32" t="s">
+      <c r="E249" s="30" t="s">
         <v>312</v>
       </c>
-      <c r="I249" s="27"/>
-      <c r="J249" s="27"/>
+      <c r="I249" s="25"/>
+      <c r="J249" s="25"/>
     </row>
     <row r="250" spans="1:10" ht="15" customHeight="1">
-      <c r="A250" s="21"/>
-      <c r="B250" s="27"/>
-      <c r="C250" s="27"/>
-      <c r="D250" s="28"/>
-      <c r="E250" s="32"/>
-      <c r="I250" s="27"/>
-      <c r="J250" s="27"/>
+      <c r="A250" s="19"/>
+      <c r="B250" s="25"/>
+      <c r="C250" s="25"/>
+      <c r="D250" s="26"/>
+      <c r="E250" s="30"/>
+      <c r="I250" s="25"/>
+      <c r="J250" s="25"/>
     </row>
     <row r="251" spans="1:10" ht="15" customHeight="1">
-      <c r="A251" s="21"/>
-      <c r="B251" s="27"/>
-      <c r="C251" s="27"/>
-      <c r="D251" s="28"/>
-      <c r="E251" s="28"/>
-      <c r="F251" s="86"/>
-      <c r="G251" s="86"/>
-      <c r="H251" s="86"/>
-      <c r="I251" s="27"/>
-      <c r="J251" s="27"/>
+      <c r="A251" s="19"/>
+      <c r="B251" s="25"/>
+      <c r="C251" s="25"/>
+      <c r="D251" s="26"/>
+      <c r="E251" s="26"/>
+      <c r="F251" s="84"/>
+      <c r="G251" s="84"/>
+      <c r="H251" s="84"/>
+      <c r="I251" s="25"/>
+      <c r="J251" s="25"/>
     </row>
     <row r="252" spans="1:10" ht="15" customHeight="1">
-      <c r="A252" s="21"/>
-      <c r="B252" s="20" t="s">
+      <c r="A252" s="19"/>
+      <c r="B252" s="18" t="s">
         <v>313</v>
       </c>
-      <c r="C252" s="21"/>
-      <c r="D252" s="21"/>
-      <c r="E252" s="45"/>
-      <c r="F252" s="45"/>
-      <c r="G252" s="42"/>
-      <c r="H252" s="45"/>
-      <c r="I252" s="45"/>
-      <c r="J252" s="42"/>
+      <c r="C252" s="19"/>
+      <c r="D252" s="19"/>
+      <c r="E252" s="43"/>
+      <c r="F252" s="43"/>
+      <c r="G252" s="40"/>
+      <c r="H252" s="43"/>
+      <c r="I252" s="43"/>
+      <c r="J252" s="40"/>
     </row>
     <row r="253" spans="1:10" ht="15" customHeight="1">
-      <c r="A253" s="21"/>
-      <c r="B253" s="20"/>
-      <c r="C253" s="21"/>
-      <c r="D253" s="21"/>
-      <c r="E253" s="45"/>
-      <c r="F253" s="45"/>
-      <c r="I253" s="45"/>
-      <c r="J253" s="42"/>
+      <c r="A253" s="19"/>
+      <c r="B253" s="18"/>
+      <c r="C253" s="19"/>
+      <c r="D253" s="19"/>
+      <c r="E253" s="43"/>
+      <c r="F253" s="43"/>
+      <c r="I253" s="43"/>
+      <c r="J253" s="40"/>
     </row>
     <row r="254" spans="1:10" ht="16.899999999999999" customHeight="1">
-      <c r="A254" s="21"/>
-      <c r="B254" s="21"/>
-      <c r="C254" s="21"/>
-      <c r="D254" s="28" t="s">
+      <c r="A254" s="19"/>
+      <c r="B254" s="19"/>
+      <c r="C254" s="19"/>
+      <c r="D254" s="26" t="s">
         <v>314</v>
       </c>
-      <c r="E254" s="28" t="s">
+      <c r="E254" s="26" t="s">
         <v>315</v>
       </c>
-      <c r="F254" s="51"/>
-      <c r="G254" s="28" t="s">
+      <c r="F254" s="49"/>
+      <c r="G254" s="26" t="s">
         <v>292</v>
       </c>
-      <c r="H254" s="28" t="s">
+      <c r="H254" s="26" t="s">
         <v>316</v>
       </c>
-      <c r="I254" s="51"/>
-      <c r="J254" s="42"/>
+      <c r="I254" s="49"/>
+      <c r="J254" s="40"/>
     </row>
     <row r="255" spans="1:10" ht="16.899999999999999" customHeight="1">
-      <c r="A255" s="21"/>
-      <c r="B255" s="21"/>
-      <c r="C255" s="21"/>
-      <c r="D255" s="28" t="s">
+      <c r="A255" s="19"/>
+      <c r="B255" s="19"/>
+      <c r="C255" s="19"/>
+      <c r="D255" s="26" t="s">
         <v>280</v>
       </c>
-      <c r="E255" s="28" t="s">
+      <c r="E255" s="26" t="s">
         <v>317</v>
       </c>
-      <c r="F255" s="51"/>
-      <c r="G255" s="28" t="s">
+      <c r="F255" s="49"/>
+      <c r="G255" s="26" t="s">
         <v>318</v>
       </c>
-      <c r="H255" s="28" t="s">
+      <c r="H255" s="26" t="s">
         <v>316</v>
       </c>
-      <c r="I255" s="51"/>
-      <c r="J255" s="42"/>
+      <c r="I255" s="49"/>
+      <c r="J255" s="40"/>
     </row>
     <row r="256" spans="1:10" ht="16.899999999999999" customHeight="1">
-      <c r="A256" s="21"/>
-      <c r="B256" s="21"/>
-      <c r="C256" s="21"/>
-      <c r="D256" s="28" t="s">
+      <c r="A256" s="19"/>
+      <c r="B256" s="19"/>
+      <c r="C256" s="19"/>
+      <c r="D256" s="26" t="s">
         <v>48</v>
       </c>
-      <c r="E256" s="28" t="s">
+      <c r="E256" s="26" t="s">
         <v>319</v>
       </c>
-      <c r="F256" s="52"/>
-      <c r="G256" s="28" t="s">
+      <c r="F256" s="50"/>
+      <c r="G256" s="26" t="s">
         <v>320</v>
       </c>
-      <c r="H256" s="28" t="s">
+      <c r="H256" s="26" t="s">
         <v>321</v>
       </c>
-      <c r="I256" s="51"/>
-      <c r="J256" s="45"/>
+      <c r="I256" s="49"/>
+      <c r="J256" s="43"/>
     </row>
     <row r="257" spans="1:10" ht="16.899999999999999" customHeight="1">
-      <c r="A257" s="21"/>
-      <c r="B257" s="21"/>
-      <c r="C257" s="21"/>
-      <c r="D257" s="52"/>
-      <c r="E257" s="28" t="s">
+      <c r="A257" s="19"/>
+      <c r="B257" s="19"/>
+      <c r="C257" s="19"/>
+      <c r="D257" s="50"/>
+      <c r="E257" s="26" t="s">
         <v>322</v>
       </c>
-      <c r="F257" s="52"/>
-      <c r="G257" s="28" t="s">
+      <c r="F257" s="50"/>
+      <c r="G257" s="26" t="s">
         <v>296</v>
       </c>
-      <c r="H257" s="28" t="s">
+      <c r="H257" s="26" t="s">
         <v>323</v>
       </c>
-      <c r="I257" s="51"/>
-      <c r="J257" s="45"/>
+      <c r="I257" s="49"/>
+      <c r="J257" s="43"/>
     </row>
     <row r="258" spans="1:10" ht="16.899999999999999" customHeight="1">
-      <c r="A258" s="21"/>
-      <c r="B258" s="21"/>
-      <c r="C258" s="21"/>
-      <c r="D258" s="28" t="s">
+      <c r="A258" s="19"/>
+      <c r="B258" s="19"/>
+      <c r="C258" s="19"/>
+      <c r="D258" s="26" t="s">
         <v>49</v>
       </c>
-      <c r="E258" s="28" t="s">
+      <c r="E258" s="26" t="s">
         <v>316</v>
       </c>
-      <c r="G258" s="28" t="s">
+      <c r="G258" s="26" t="s">
         <v>324</v>
       </c>
-      <c r="H258" s="28" t="s">
+      <c r="H258" s="26" t="s">
         <v>325</v>
       </c>
-      <c r="I258" s="56"/>
-      <c r="J258" s="45"/>
+      <c r="I258" s="54"/>
+      <c r="J258" s="43"/>
     </row>
     <row r="259" spans="1:10" ht="16.899999999999999" customHeight="1">
-      <c r="A259" s="21"/>
-      <c r="B259" s="21"/>
-      <c r="C259" s="21"/>
-      <c r="D259" s="28" t="s">
+      <c r="A259" s="19"/>
+      <c r="B259" s="19"/>
+      <c r="C259" s="19"/>
+      <c r="D259" s="26" t="s">
         <v>326</v>
       </c>
-      <c r="E259" s="28" t="s">
+      <c r="E259" s="26" t="s">
         <v>316</v>
       </c>
-      <c r="F259" s="51"/>
-      <c r="G259" s="28" t="s">
+      <c r="F259" s="49"/>
+      <c r="G259" s="26" t="s">
         <v>327</v>
       </c>
-      <c r="H259" s="28" t="s">
+      <c r="H259" s="26" t="s">
         <v>328</v>
       </c>
-      <c r="I259" s="14"/>
-      <c r="J259" s="42"/>
+      <c r="I259" s="12"/>
+      <c r="J259" s="40"/>
     </row>
     <row r="260" spans="1:10" ht="16.899999999999999" customHeight="1">
-      <c r="A260" s="21"/>
-      <c r="B260" s="21"/>
-      <c r="C260" s="21"/>
-      <c r="D260" s="28" t="s">
+      <c r="A260" s="19"/>
+      <c r="B260" s="19"/>
+      <c r="C260" s="19"/>
+      <c r="D260" s="26" t="s">
         <v>329</v>
       </c>
-      <c r="E260" s="28" t="s">
+      <c r="E260" s="26" t="s">
         <v>316</v>
       </c>
-      <c r="F260" s="51"/>
-      <c r="G260" s="28" t="s">
+      <c r="F260" s="49"/>
+      <c r="G260" s="26" t="s">
         <v>330</v>
       </c>
-      <c r="H260" s="28" t="s">
+      <c r="H260" s="26" t="s">
         <v>331</v>
       </c>
-      <c r="I260" s="14"/>
-      <c r="J260" s="42"/>
+      <c r="I260" s="12"/>
+      <c r="J260" s="40"/>
     </row>
     <row r="261" spans="1:10" ht="16.899999999999999" customHeight="1">
-      <c r="A261" s="21"/>
-      <c r="B261" s="21"/>
-      <c r="C261" s="21"/>
-      <c r="D261" s="28" t="s">
+      <c r="A261" s="19"/>
+      <c r="B261" s="19"/>
+      <c r="C261" s="19"/>
+      <c r="D261" s="26" t="s">
         <v>332</v>
       </c>
-      <c r="E261" s="28" t="s">
+      <c r="E261" s="26" t="s">
         <v>333</v>
       </c>
-      <c r="F261" s="51"/>
-      <c r="G261" s="28" t="s">
+      <c r="F261" s="49"/>
+      <c r="G261" s="26" t="s">
         <v>334</v>
       </c>
-      <c r="H261" s="28" t="s">
+      <c r="H261" s="26" t="s">
         <v>316</v>
       </c>
-      <c r="I261" s="51"/>
-      <c r="J261" s="42"/>
+      <c r="I261" s="49"/>
+      <c r="J261" s="40"/>
     </row>
     <row r="262" spans="1:10" ht="16.899999999999999" customHeight="1">
-      <c r="A262" s="21"/>
-      <c r="B262" s="21"/>
-      <c r="C262" s="21"/>
-      <c r="D262" s="28" t="s">
+      <c r="A262" s="19"/>
+      <c r="B262" s="19"/>
+      <c r="C262" s="19"/>
+      <c r="D262" s="26" t="s">
         <v>335</v>
       </c>
-      <c r="E262" s="28" t="s">
+      <c r="E262" s="26" t="s">
         <v>336</v>
       </c>
-      <c r="F262" s="51"/>
-      <c r="G262" s="28" t="s">
+      <c r="F262" s="49"/>
+      <c r="G262" s="26" t="s">
         <v>337</v>
       </c>
-      <c r="H262" s="28" t="s">
+      <c r="H262" s="26" t="s">
         <v>338</v>
       </c>
-      <c r="I262" s="51"/>
-      <c r="J262" s="42"/>
+      <c r="I262" s="49"/>
+      <c r="J262" s="40"/>
     </row>
     <row r="263" spans="1:10" ht="16.899999999999999" customHeight="1">
-      <c r="A263" s="21"/>
-      <c r="B263" s="21"/>
-      <c r="C263" s="21"/>
-      <c r="D263" s="28" t="s">
+      <c r="A263" s="19"/>
+      <c r="B263" s="19"/>
+      <c r="C263" s="19"/>
+      <c r="D263" s="26" t="s">
         <v>339</v>
       </c>
-      <c r="E263" s="32" t="s">
+      <c r="E263" s="30" t="s">
         <v>340</v>
       </c>
-      <c r="F263" s="51"/>
-      <c r="G263" s="28" t="s">
+      <c r="F263" s="49"/>
+      <c r="G263" s="26" t="s">
         <v>341</v>
       </c>
-      <c r="H263" s="28" t="s">
+      <c r="H263" s="26" t="s">
         <v>342</v>
       </c>
-      <c r="I263" s="51"/>
-      <c r="J263" s="42"/>
+      <c r="I263" s="49"/>
+      <c r="J263" s="40"/>
     </row>
     <row r="264" spans="1:10" ht="16.899999999999999" customHeight="1">
-      <c r="A264" s="21"/>
-      <c r="B264" s="21"/>
-      <c r="C264" s="21"/>
-      <c r="D264" s="52"/>
-      <c r="E264" s="28" t="s">
+      <c r="A264" s="19"/>
+      <c r="B264" s="19"/>
+      <c r="C264" s="19"/>
+      <c r="D264" s="50"/>
+      <c r="E264" s="26" t="s">
         <v>58</v>
       </c>
-      <c r="G264" s="28"/>
-      <c r="H264" s="28"/>
-      <c r="I264" s="51"/>
-      <c r="J264" s="42"/>
+      <c r="G264" s="26"/>
+      <c r="H264" s="26"/>
+      <c r="I264" s="49"/>
+      <c r="J264" s="40"/>
     </row>
     <row r="265" spans="1:10" ht="16.899999999999999" customHeight="1">
-      <c r="A265" s="21"/>
-      <c r="B265" s="21"/>
-      <c r="C265" s="21"/>
-      <c r="D265" s="28" t="s">
+      <c r="A265" s="19"/>
+      <c r="B265" s="19"/>
+      <c r="C265" s="19"/>
+      <c r="D265" s="26" t="s">
         <v>343</v>
       </c>
-      <c r="E265" s="27" t="s">
+      <c r="E265" s="25" t="s">
         <v>344</v>
       </c>
-      <c r="F265" s="51"/>
-      <c r="G265" s="52"/>
-      <c r="I265" s="51"/>
-      <c r="J265" s="45"/>
+      <c r="F265" s="49"/>
+      <c r="G265" s="50"/>
+      <c r="I265" s="49"/>
+      <c r="J265" s="43"/>
     </row>
     <row r="266" spans="1:10" ht="16.899999999999999" customHeight="1">
-      <c r="A266" s="21"/>
-      <c r="B266" s="21"/>
-      <c r="C266" s="21"/>
-      <c r="D266" s="28" t="s">
+      <c r="A266" s="19"/>
+      <c r="B266" s="19"/>
+      <c r="C266" s="19"/>
+      <c r="D266" s="26" t="s">
         <v>345</v>
       </c>
-      <c r="E266" s="28" t="s">
+      <c r="E266" s="26" t="s">
         <v>346</v>
       </c>
-      <c r="F266" s="51"/>
-      <c r="G266" s="52"/>
-      <c r="I266" s="51"/>
-      <c r="J266" s="45"/>
+      <c r="F266" s="49"/>
+      <c r="G266" s="50"/>
+      <c r="I266" s="49"/>
+      <c r="J266" s="43"/>
     </row>
     <row r="267" spans="1:10" ht="16.899999999999999" customHeight="1">
-      <c r="A267" s="21"/>
-      <c r="B267" s="21"/>
-      <c r="C267" s="21"/>
-      <c r="D267" s="28" t="s">
+      <c r="A267" s="19"/>
+      <c r="B267" s="19"/>
+      <c r="C267" s="19"/>
+      <c r="D267" s="26" t="s">
         <v>347</v>
       </c>
-      <c r="E267" s="28" t="s">
+      <c r="E267" s="26" t="s">
         <v>348</v>
       </c>
-      <c r="F267" s="51"/>
-      <c r="G267" s="52"/>
-      <c r="I267" s="51"/>
-      <c r="J267" s="45"/>
+      <c r="F267" s="49"/>
+      <c r="G267" s="50"/>
+      <c r="I267" s="49"/>
+      <c r="J267" s="43"/>
     </row>
     <row r="268" spans="1:10" ht="16.899999999999999" customHeight="1">
-      <c r="A268" s="21"/>
-      <c r="B268" s="45"/>
-      <c r="C268" s="45"/>
-      <c r="D268" s="28" t="s">
+      <c r="A268" s="19"/>
+      <c r="B268" s="43"/>
+      <c r="C268" s="43"/>
+      <c r="D268" s="26" t="s">
         <v>349</v>
       </c>
-      <c r="E268" s="28" t="s">
+      <c r="E268" s="26" t="s">
         <v>316</v>
       </c>
-      <c r="F268" s="51"/>
-      <c r="G268" s="28" t="s">
+      <c r="F268" s="49"/>
+      <c r="G268" s="26" t="s">
         <v>350</v>
       </c>
-      <c r="H268" s="28" t="s">
+      <c r="H268" s="26" t="s">
         <v>351</v>
       </c>
-      <c r="I268" s="51"/>
-      <c r="J268" s="45"/>
+      <c r="I268" s="49"/>
+      <c r="J268" s="43"/>
     </row>
     <row r="269" spans="1:10" ht="16.899999999999999" customHeight="1">
-      <c r="A269" s="21"/>
-      <c r="B269" s="45"/>
-      <c r="C269" s="45"/>
-      <c r="D269" s="28" t="s">
+      <c r="A269" s="19"/>
+      <c r="B269" s="43"/>
+      <c r="C269" s="43"/>
+      <c r="D269" s="26" t="s">
         <v>290</v>
       </c>
-      <c r="E269" s="28" t="s">
+      <c r="E269" s="26" t="s">
         <v>352</v>
       </c>
-      <c r="F269" s="51"/>
-      <c r="G269" s="28" t="s">
+      <c r="F269" s="49"/>
+      <c r="G269" s="26" t="s">
         <v>353</v>
       </c>
-      <c r="H269" s="28" t="s">
+      <c r="H269" s="26" t="s">
         <v>354</v>
       </c>
-      <c r="I269" s="51"/>
-      <c r="J269" s="45"/>
+      <c r="I269" s="49"/>
+      <c r="J269" s="43"/>
     </row>
     <row r="270" spans="1:10" ht="16.899999999999999" customHeight="1">
-      <c r="A270" s="21"/>
-      <c r="B270" s="21"/>
-      <c r="C270" s="21"/>
-      <c r="D270" s="52"/>
-      <c r="F270" s="52"/>
-      <c r="G270" s="28" t="s">
+      <c r="A270" s="19"/>
+      <c r="B270" s="19"/>
+      <c r="C270" s="19"/>
+      <c r="D270" s="50"/>
+      <c r="F270" s="50"/>
+      <c r="G270" s="26" t="s">
         <v>355</v>
       </c>
-      <c r="H270" s="28" t="s">
+      <c r="H270" s="26" t="s">
         <v>356</v>
       </c>
-      <c r="J270" s="42"/>
+      <c r="J270" s="40"/>
     </row>
     <row r="271" spans="1:10" ht="16.899999999999999" customHeight="1">
-      <c r="A271" s="21"/>
-      <c r="B271" s="21"/>
-      <c r="C271" s="21"/>
-      <c r="D271" s="28"/>
-      <c r="E271" s="28"/>
-      <c r="F271" s="51"/>
-      <c r="G271" s="28" t="s">
+      <c r="A271" s="19"/>
+      <c r="B271" s="19"/>
+      <c r="C271" s="19"/>
+      <c r="D271" s="26"/>
+      <c r="E271" s="26"/>
+      <c r="F271" s="49"/>
+      <c r="G271" s="26" t="s">
         <v>357</v>
       </c>
-      <c r="H271" s="28" t="s">
+      <c r="H271" s="26" t="s">
         <v>346</v>
       </c>
-      <c r="J271" s="42"/>
+      <c r="J271" s="40"/>
     </row>
     <row r="272" spans="1:10" ht="16.899999999999999" customHeight="1">
-      <c r="A272" s="21"/>
-      <c r="B272" s="21"/>
-      <c r="C272" s="21"/>
-      <c r="D272" s="32"/>
-      <c r="E272" s="28"/>
-      <c r="F272" s="51"/>
-      <c r="G272" s="28" t="s">
+      <c r="A272" s="19"/>
+      <c r="B272" s="19"/>
+      <c r="C272" s="19"/>
+      <c r="D272" s="30"/>
+      <c r="E272" s="26"/>
+      <c r="F272" s="49"/>
+      <c r="G272" s="26" t="s">
         <v>358</v>
       </c>
-      <c r="H272" s="28" t="s">
+      <c r="H272" s="26" t="s">
         <v>359</v>
       </c>
-      <c r="J272" s="42"/>
+      <c r="J272" s="40"/>
     </row>
     <row r="273" spans="1:10" ht="16.899999999999999" customHeight="1">
-      <c r="A273" s="21"/>
-      <c r="B273" s="21"/>
-      <c r="C273" s="21"/>
-      <c r="D273" s="32"/>
-      <c r="F273" s="51"/>
-      <c r="G273" s="28" t="s">
+      <c r="A273" s="19"/>
+      <c r="B273" s="19"/>
+      <c r="C273" s="19"/>
+      <c r="D273" s="30"/>
+      <c r="F273" s="49"/>
+      <c r="G273" s="26" t="s">
         <v>360</v>
       </c>
-      <c r="H273" s="28" t="s">
+      <c r="H273" s="26" t="s">
         <v>361</v>
       </c>
-      <c r="J273" s="42"/>
+      <c r="J273" s="40"/>
     </row>
     <row r="274" spans="1:10" ht="15" customHeight="1">
-      <c r="A274" s="21"/>
-      <c r="B274" s="21"/>
-      <c r="C274" s="21"/>
-      <c r="D274" s="32"/>
-      <c r="E274" s="28"/>
-      <c r="F274" s="51"/>
-      <c r="J274" s="42"/>
+      <c r="A274" s="19"/>
+      <c r="B274" s="19"/>
+      <c r="C274" s="19"/>
+      <c r="D274" s="30"/>
+      <c r="E274" s="26"/>
+      <c r="F274" s="49"/>
+      <c r="J274" s="40"/>
     </row>
     <row r="275" spans="1:10" ht="15" customHeight="1">
-      <c r="A275" s="21"/>
-      <c r="B275" s="21"/>
-      <c r="C275" s="21"/>
-      <c r="D275" s="32"/>
-      <c r="E275" s="28"/>
-      <c r="F275" s="51"/>
-      <c r="J275" s="42"/>
+      <c r="A275" s="19"/>
+      <c r="B275" s="19"/>
+      <c r="C275" s="19"/>
+      <c r="D275" s="30"/>
+      <c r="E275" s="26"/>
+      <c r="F275" s="49"/>
+      <c r="J275" s="40"/>
     </row>
     <row r="276" spans="1:10" ht="15" customHeight="1">
-      <c r="A276" s="21"/>
-      <c r="B276" s="21"/>
-      <c r="C276" s="21"/>
-      <c r="D276" s="32"/>
-      <c r="E276" s="28"/>
-      <c r="F276" s="51"/>
-      <c r="J276" s="42"/>
+      <c r="A276" s="19"/>
+      <c r="B276" s="19"/>
+      <c r="C276" s="19"/>
+      <c r="D276" s="30"/>
+      <c r="E276" s="26"/>
+      <c r="F276" s="49"/>
+      <c r="J276" s="40"/>
     </row>
     <row r="277" spans="1:10" ht="15" customHeight="1">
-      <c r="A277" s="21"/>
-      <c r="B277" s="21"/>
-      <c r="C277" s="21"/>
-      <c r="D277" s="32"/>
-      <c r="E277" s="28"/>
-      <c r="F277" s="51"/>
-      <c r="J277" s="42"/>
+      <c r="A277" s="19"/>
+      <c r="B277" s="19"/>
+      <c r="C277" s="19"/>
+      <c r="D277" s="30"/>
+      <c r="E277" s="26"/>
+      <c r="F277" s="49"/>
+      <c r="J277" s="40"/>
     </row>
     <row r="278" spans="1:10" ht="15" customHeight="1">
-      <c r="A278" s="21"/>
-      <c r="B278" s="21"/>
-      <c r="C278" s="21"/>
-      <c r="D278" s="32"/>
-      <c r="E278" s="28"/>
-      <c r="F278" s="51"/>
-      <c r="J278" s="42"/>
+      <c r="A278" s="19"/>
+      <c r="B278" s="19"/>
+      <c r="C278" s="19"/>
+      <c r="D278" s="30"/>
+      <c r="E278" s="26"/>
+      <c r="F278" s="49"/>
+      <c r="J278" s="40"/>
     </row>
     <row r="279" spans="1:10" ht="15" customHeight="1">
-      <c r="A279" s="21"/>
-      <c r="B279" s="21"/>
-      <c r="C279" s="21"/>
-      <c r="D279" s="32"/>
-      <c r="E279" s="28"/>
-      <c r="F279" s="51"/>
-      <c r="J279" s="42"/>
+      <c r="A279" s="19"/>
+      <c r="B279" s="19"/>
+      <c r="C279" s="19"/>
+      <c r="D279" s="30"/>
+      <c r="E279" s="26"/>
+      <c r="F279" s="49"/>
+      <c r="J279" s="40"/>
     </row>
     <row r="280" spans="1:10" ht="15" customHeight="1">
-      <c r="A280" s="21"/>
-      <c r="B280" s="21"/>
-      <c r="C280" s="21"/>
-      <c r="D280" s="32"/>
-      <c r="E280" s="28"/>
-      <c r="F280" s="51"/>
-      <c r="J280" s="42"/>
+      <c r="A280" s="19"/>
+      <c r="B280" s="19"/>
+      <c r="C280" s="19"/>
+      <c r="D280" s="30"/>
+      <c r="E280" s="26"/>
+      <c r="F280" s="49"/>
+      <c r="J280" s="40"/>
     </row>
     <row r="281" spans="1:10" ht="15" customHeight="1">
-      <c r="A281" s="21"/>
-      <c r="B281" s="21"/>
-      <c r="C281" s="21"/>
-      <c r="D281" s="28"/>
-      <c r="E281" s="28"/>
-      <c r="F281" s="51"/>
-      <c r="J281" s="42"/>
+      <c r="A281" s="19"/>
+      <c r="B281" s="19"/>
+      <c r="C281" s="19"/>
+      <c r="D281" s="26"/>
+      <c r="E281" s="26"/>
+      <c r="F281" s="49"/>
+      <c r="J281" s="40"/>
     </row>
     <row r="282" spans="1:10" ht="15" customHeight="1">
-      <c r="A282" s="21"/>
-      <c r="B282" s="21"/>
-      <c r="C282" s="21"/>
-      <c r="D282" s="27"/>
-      <c r="E282" s="27"/>
-      <c r="F282" s="45"/>
-      <c r="G282" s="14"/>
-      <c r="H282" s="14"/>
-      <c r="I282" s="14"/>
-      <c r="J282" s="14"/>
+      <c r="A282" s="19"/>
+      <c r="B282" s="19"/>
+      <c r="C282" s="19"/>
+      <c r="D282" s="25"/>
+      <c r="E282" s="25"/>
+      <c r="F282" s="43"/>
+      <c r="G282" s="12"/>
+      <c r="H282" s="12"/>
+      <c r="I282" s="12"/>
+      <c r="J282" s="12"/>
     </row>
     <row r="283" spans="1:10" ht="28.15" customHeight="1">
-      <c r="A283" s="21"/>
-      <c r="B283" s="42"/>
-      <c r="C283" s="45"/>
-      <c r="D283" s="14"/>
-      <c r="E283" s="14"/>
-      <c r="F283" s="87" t="s">
+      <c r="A283" s="19"/>
+      <c r="B283" s="40"/>
+      <c r="C283" s="43"/>
+      <c r="D283" s="12"/>
+      <c r="E283" s="12"/>
+      <c r="F283" s="85" t="s">
         <v>362</v>
       </c>
-      <c r="G283" s="88"/>
-      <c r="H283" s="88"/>
-      <c r="I283" s="14"/>
-      <c r="J283" s="14"/>
+      <c r="G283" s="86"/>
+      <c r="H283" s="86"/>
+      <c r="I283" s="12"/>
+      <c r="J283" s="12"/>
     </row>
     <row r="284" spans="1:10" ht="16.899999999999999" customHeight="1">
-      <c r="A284" s="21"/>
-      <c r="B284" s="89"/>
-      <c r="C284" s="90"/>
-      <c r="D284" s="32" t="s">
+      <c r="A284" s="19"/>
+      <c r="B284" s="87"/>
+      <c r="C284" s="88"/>
+      <c r="D284" s="30" t="s">
         <v>363</v>
       </c>
-      <c r="E284" s="91"/>
-      <c r="F284" s="61"/>
-      <c r="G284" s="32" t="s">
+      <c r="E284" s="89"/>
+      <c r="F284" s="59"/>
+      <c r="G284" s="30" t="s">
         <v>364</v>
       </c>
-      <c r="H284" s="14"/>
-      <c r="I284" s="61"/>
-      <c r="J284" s="61"/>
+      <c r="H284" s="12"/>
+      <c r="I284" s="59"/>
+      <c r="J284" s="59"/>
     </row>
     <row r="285" spans="1:10" ht="16.899999999999999" customHeight="1">
-      <c r="A285" s="21"/>
-      <c r="B285" s="21"/>
-      <c r="C285" s="21"/>
-      <c r="D285" s="32" t="s">
+      <c r="A285" s="19"/>
+      <c r="B285" s="19"/>
+      <c r="C285" s="19"/>
+      <c r="D285" s="30" t="s">
         <v>365</v>
       </c>
-      <c r="E285" s="91"/>
-      <c r="F285" s="91"/>
-      <c r="G285" s="31" t="s">
+      <c r="E285" s="89"/>
+      <c r="F285" s="89"/>
+      <c r="G285" s="29" t="s">
         <v>59</v>
       </c>
-      <c r="H285" s="14"/>
-      <c r="I285" s="33"/>
-      <c r="J285" s="33"/>
+      <c r="H285" s="12"/>
+      <c r="I285" s="31"/>
+      <c r="J285" s="31"/>
     </row>
     <row r="286" spans="1:10" ht="16.899999999999999" customHeight="1">
-      <c r="A286" s="21"/>
-      <c r="B286" s="89"/>
-      <c r="C286" s="90"/>
-      <c r="D286" s="32" t="s">
+      <c r="A286" s="19"/>
+      <c r="B286" s="87"/>
+      <c r="C286" s="88"/>
+      <c r="D286" s="30" t="s">
         <v>366</v>
       </c>
-      <c r="E286" s="91"/>
-      <c r="F286" s="61"/>
-      <c r="G286" s="31" t="s">
+      <c r="E286" s="89"/>
+      <c r="F286" s="59"/>
+      <c r="G286" s="29" t="s">
         <v>367</v>
       </c>
-      <c r="H286" s="14"/>
-      <c r="I286" s="61"/>
-      <c r="J286" s="61"/>
+      <c r="H286" s="12"/>
+      <c r="I286" s="59"/>
+      <c r="J286" s="59"/>
     </row>
     <row r="287" spans="1:10" ht="28.15" customHeight="1">
-      <c r="A287" s="21"/>
-      <c r="B287" s="89"/>
-      <c r="C287" s="90"/>
-      <c r="D287" s="14"/>
-      <c r="E287" s="33"/>
-      <c r="F287" s="33"/>
-      <c r="G287" s="92"/>
-      <c r="H287" s="61"/>
-      <c r="I287" s="109" t="s">
+      <c r="A287" s="19"/>
+      <c r="B287" s="87"/>
+      <c r="C287" s="88"/>
+      <c r="D287" s="12"/>
+      <c r="E287" s="31"/>
+      <c r="F287" s="31"/>
+      <c r="G287" s="90"/>
+      <c r="H287" s="59"/>
+      <c r="I287" s="103" t="s">
         <v>368</v>
       </c>
-      <c r="J287" s="109"/>
+      <c r="J287" s="103"/>
     </row>
     <row r="288" spans="1:10" ht="28.15" customHeight="1">
-      <c r="A288" s="45"/>
-      <c r="B288" s="21"/>
-      <c r="C288" s="21"/>
-      <c r="D288" s="14"/>
-      <c r="E288" s="61"/>
-      <c r="F288" s="33"/>
-      <c r="G288" s="61"/>
-      <c r="H288" s="33"/>
-      <c r="I288" s="14"/>
-      <c r="J288" s="61"/>
+      <c r="A288" s="43"/>
+      <c r="B288" s="19"/>
+      <c r="C288" s="19"/>
+      <c r="D288" s="12"/>
+      <c r="E288" s="59"/>
+      <c r="F288" s="31"/>
+      <c r="G288" s="59"/>
+      <c r="H288" s="31"/>
+      <c r="I288" s="12"/>
+      <c r="J288" s="59"/>
     </row>
     <row r="289" spans="1:10" ht="28.15" customHeight="1">
-      <c r="A289" s="45"/>
-      <c r="B289" s="21"/>
-      <c r="C289" s="21"/>
-      <c r="D289" s="14"/>
-      <c r="E289" s="61"/>
-      <c r="F289" s="33" ph="1"/>
-      <c r="G289" s="61"/>
-      <c r="H289" s="61"/>
-      <c r="I289" s="61"/>
-      <c r="J289" s="61"/>
+      <c r="A289" s="43"/>
+      <c r="B289" s="19"/>
+      <c r="C289" s="19"/>
+      <c r="D289" s="12"/>
+      <c r="E289" s="59"/>
+      <c r="F289" s="31" ph="1"/>
+      <c r="G289" s="59"/>
+      <c r="H289" s="59"/>
+      <c r="I289" s="59"/>
+      <c r="J289" s="59"/>
     </row>
     <row r="290" spans="1:10" ht="28.15" customHeight="1">
-      <c r="A290" s="45"/>
-      <c r="B290" s="21"/>
-      <c r="C290" s="21"/>
-      <c r="D290" s="14"/>
-      <c r="E290" s="61"/>
-      <c r="F290" s="61"/>
-      <c r="G290" s="61"/>
-      <c r="H290" s="61"/>
-      <c r="I290" s="61"/>
-      <c r="J290" s="61"/>
+      <c r="A290" s="43"/>
+      <c r="B290" s="19"/>
+      <c r="C290" s="19"/>
+      <c r="D290" s="12"/>
+      <c r="E290" s="59"/>
+      <c r="F290" s="59"/>
+      <c r="G290" s="59"/>
+      <c r="H290" s="59"/>
+      <c r="I290" s="59"/>
+      <c r="J290" s="59"/>
     </row>
     <row r="291" spans="1:10" ht="28.15" customHeight="1">
-      <c r="A291" s="45"/>
-      <c r="B291" s="21"/>
-      <c r="C291" s="21"/>
-      <c r="D291" s="14"/>
-      <c r="E291" s="61"/>
-      <c r="F291" s="14"/>
-      <c r="G291" s="14"/>
-      <c r="H291" s="61"/>
-      <c r="I291" s="14"/>
-      <c r="J291" s="61"/>
+      <c r="A291" s="43"/>
+      <c r="B291" s="19"/>
+      <c r="C291" s="19"/>
+      <c r="D291" s="12"/>
+      <c r="E291" s="59"/>
+      <c r="F291" s="12"/>
+      <c r="G291" s="12"/>
+      <c r="H291" s="59"/>
+      <c r="I291" s="12"/>
+      <c r="J291" s="59"/>
     </row>
     <row r="292" spans="1:10" ht="28.15" customHeight="1">
-      <c r="A292" s="45"/>
-      <c r="B292" s="21"/>
-      <c r="C292" s="14"/>
-      <c r="D292" s="14"/>
-      <c r="E292" s="61"/>
-      <c r="F292" s="14"/>
-      <c r="G292" s="14"/>
-      <c r="H292" s="61"/>
-      <c r="I292" s="14"/>
-      <c r="J292" s="61"/>
+      <c r="A292" s="43"/>
+      <c r="B292" s="19"/>
+      <c r="C292" s="12"/>
+      <c r="D292" s="12"/>
+      <c r="E292" s="59"/>
+      <c r="F292" s="12"/>
+      <c r="G292" s="12"/>
+      <c r="H292" s="59"/>
+      <c r="I292" s="12"/>
+      <c r="J292" s="59"/>
     </row>
     <row r="293" spans="1:10" ht="28.15" customHeight="1">
-      <c r="A293" s="45"/>
-      <c r="B293" s="21"/>
-      <c r="D293" s="93"/>
-      <c r="E293" s="61"/>
-      <c r="F293" s="14"/>
-      <c r="G293" s="14" t="s">
+      <c r="A293" s="43"/>
+      <c r="B293" s="19"/>
+      <c r="D293" s="91"/>
+      <c r="E293" s="59"/>
+      <c r="F293" s="12"/>
+      <c r="G293" s="12" t="s">
         <v>369</v>
       </c>
-      <c r="H293" s="61"/>
-      <c r="I293" s="14"/>
-      <c r="J293" s="61"/>
+      <c r="H293" s="59"/>
+      <c r="I293" s="12"/>
+      <c r="J293" s="59"/>
     </row>
     <row r="294" spans="1:10" ht="18.600000000000001" customHeight="1">
-      <c r="A294" s="45"/>
-      <c r="B294" s="33"/>
-      <c r="C294" s="14"/>
-      <c r="D294" s="14"/>
-      <c r="E294" s="61"/>
-      <c r="F294" s="14"/>
-      <c r="G294" s="14"/>
-      <c r="H294" s="61"/>
-      <c r="I294" s="14"/>
-      <c r="J294" s="61"/>
+      <c r="A294" s="43"/>
+      <c r="B294" s="31"/>
+      <c r="C294" s="12"/>
+      <c r="D294" s="12"/>
+      <c r="E294" s="59"/>
+      <c r="F294" s="12"/>
+      <c r="G294" s="12"/>
+      <c r="H294" s="59"/>
+      <c r="I294" s="12"/>
+      <c r="J294" s="59"/>
     </row>
     <row r="295" spans="1:10" ht="25.15" customHeight="1">
-      <c r="B295" s="33"/>
-      <c r="C295" s="94" t="s">
+      <c r="B295" s="31"/>
+      <c r="C295" s="92" t="s">
         <v>370</v>
       </c>
-      <c r="E295" s="95"/>
-      <c r="F295" s="95"/>
-      <c r="G295" s="95"/>
-      <c r="H295" s="95"/>
-      <c r="I295" s="95"/>
-      <c r="J295" s="95"/>
+      <c r="E295" s="93"/>
+      <c r="F295" s="93"/>
+      <c r="G295" s="93"/>
+      <c r="H295" s="93"/>
+      <c r="I295" s="93"/>
+      <c r="J295" s="93"/>
     </row>
     <row r="297" spans="1:10">
-      <c r="B297" s="24"/>
-      <c r="C297" s="24"/>
-      <c r="E297" s="95"/>
-      <c r="F297" s="95"/>
-      <c r="G297" s="95"/>
-      <c r="H297" s="95"/>
-      <c r="I297" s="95"/>
-      <c r="J297" s="95"/>
+      <c r="B297" s="22"/>
+      <c r="C297" s="22"/>
+      <c r="E297" s="93"/>
+      <c r="F297" s="93"/>
+      <c r="G297" s="93"/>
+      <c r="H297" s="93"/>
+      <c r="I297" s="93"/>
+      <c r="J297" s="93"/>
     </row>
     <row r="298" spans="1:10">
-      <c r="B298" s="24"/>
-      <c r="C298" s="24"/>
-      <c r="E298" s="95"/>
-      <c r="F298" s="95"/>
-      <c r="G298" s="95"/>
-      <c r="H298" s="95"/>
-      <c r="I298" s="95"/>
-      <c r="J298" s="95"/>
+      <c r="B298" s="22"/>
+      <c r="C298" s="22"/>
+      <c r="E298" s="93"/>
+      <c r="F298" s="93"/>
+      <c r="G298" s="93"/>
+      <c r="H298" s="93"/>
+      <c r="I298" s="93"/>
+      <c r="J298" s="93"/>
     </row>
     <row r="299" spans="1:10">
-      <c r="B299" s="24"/>
-      <c r="C299" s="24"/>
+      <c r="B299" s="22"/>
+      <c r="C299" s="22"/>
     </row>
     <row r="300" spans="1:10">
-      <c r="A300" s="96"/>
-      <c r="B300" s="24"/>
-      <c r="C300" s="24"/>
-      <c r="D300" s="14"/>
+      <c r="A300" s="94"/>
+      <c r="B300" s="22"/>
+      <c r="C300" s="22"/>
+      <c r="D300" s="12"/>
     </row>
     <row r="301" spans="1:10">
-      <c r="B301" s="24"/>
-      <c r="C301" s="24"/>
+      <c r="B301" s="22"/>
+      <c r="C301" s="22"/>
     </row>
     <row r="302" spans="1:10">
-      <c r="B302" s="24"/>
-      <c r="C302" s="24"/>
+      <c r="B302" s="22"/>
+      <c r="C302" s="22"/>
     </row>
     <row r="303" spans="1:10">
-      <c r="B303" s="24"/>
-      <c r="C303" s="24"/>
+      <c r="B303" s="22"/>
+      <c r="C303" s="22"/>
     </row>
     <row r="304" spans="1:10">
-      <c r="B304" s="24"/>
-      <c r="C304" s="24"/>
+      <c r="B304" s="22"/>
+      <c r="C304" s="22"/>
     </row>
     <row r="305" spans="2:3">
-      <c r="B305" s="24"/>
-      <c r="C305" s="24"/>
+      <c r="B305" s="22"/>
+      <c r="C305" s="22"/>
     </row>
     <row r="306" spans="2:3">
-      <c r="B306" s="24"/>
-      <c r="C306" s="24"/>
+      <c r="B306" s="22"/>
+      <c r="C306" s="22"/>
     </row>
     <row r="307" spans="2:3">
-      <c r="B307" s="24"/>
-      <c r="C307" s="24"/>
+      <c r="B307" s="22"/>
+      <c r="C307" s="22"/>
     </row>
     <row r="308" spans="2:3">
-      <c r="B308" s="24"/>
-      <c r="C308" s="24"/>
+      <c r="B308" s="22"/>
+      <c r="C308" s="22"/>
     </row>
     <row r="309" spans="2:3">
-      <c r="B309" s="97"/>
-      <c r="C309" s="24"/>
+      <c r="B309" s="95"/>
+      <c r="C309" s="22"/>
     </row>
     <row r="310" spans="2:3">
-      <c r="B310" s="97"/>
-      <c r="C310" s="24"/>
+      <c r="B310" s="95"/>
+      <c r="C310" s="22"/>
     </row>
     <row r="311" spans="2:3">
-      <c r="B311" s="24"/>
-      <c r="C311" s="24"/>
+      <c r="B311" s="22"/>
+      <c r="C311" s="22"/>
     </row>
     <row r="312" spans="2:3">
-      <c r="B312" s="98"/>
-      <c r="C312" s="24"/>
+      <c r="B312" s="96"/>
+      <c r="C312" s="22"/>
     </row>
     <row r="313" spans="2:3">
-      <c r="B313" s="24"/>
-      <c r="C313" s="24"/>
+      <c r="B313" s="22"/>
+      <c r="C313" s="22"/>
     </row>
     <row r="314" spans="2:3">
-      <c r="B314" s="24"/>
-      <c r="C314" s="24"/>
+      <c r="B314" s="22"/>
+      <c r="C314" s="22"/>
     </row>
     <row r="315" spans="2:3">
-      <c r="B315" s="99"/>
-      <c r="C315" s="24"/>
+      <c r="B315" s="97"/>
+      <c r="C315" s="22"/>
     </row>
     <row r="316" spans="2:3">
-      <c r="B316" s="24"/>
-      <c r="C316" s="24"/>
+      <c r="B316" s="22"/>
+      <c r="C316" s="22"/>
     </row>
     <row r="317" spans="2:3">
-      <c r="B317" s="24"/>
-      <c r="C317" s="33"/>
+      <c r="B317" s="22"/>
+      <c r="C317" s="31"/>
     </row>
     <row r="318" spans="2:3">
-      <c r="B318" s="24"/>
-      <c r="C318" s="33"/>
+      <c r="B318" s="22"/>
+      <c r="C318" s="31"/>
     </row>
     <row r="319" spans="2:3">
-      <c r="B319" s="24"/>
-      <c r="C319" s="33"/>
+      <c r="B319" s="22"/>
+      <c r="C319" s="31"/>
     </row>
     <row r="320" spans="2:3">
-      <c r="B320" s="24"/>
-      <c r="C320" s="24"/>
+      <c r="B320" s="22"/>
+      <c r="C320" s="22"/>
     </row>
     <row r="321" spans="2:7">
-      <c r="B321" s="24"/>
-      <c r="C321" s="24"/>
+      <c r="B321" s="22"/>
+      <c r="C321" s="22"/>
     </row>
     <row r="322" spans="2:7">
-      <c r="B322" s="24"/>
-      <c r="C322" s="24"/>
+      <c r="B322" s="22"/>
+      <c r="C322" s="22"/>
     </row>
     <row r="323" spans="2:7">
-      <c r="B323" s="24"/>
-      <c r="C323" s="24"/>
+      <c r="B323" s="22"/>
+      <c r="C323" s="22"/>
     </row>
     <row r="326" spans="2:7">
-      <c r="G326" s="100"/>
+      <c r="G326" s="98"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -12881,6 +12895,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x0101007E6F24AE15DDCD4DBA743709CB3A799E" ma:contentTypeVersion="4" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="915b839937184c9cb1687a511d5b7ff5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="48af5f5c-16db-4617-b456-65071b0f22d9" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="929c0896e38194c5a683e8c79de89b93" ns2:_="">
     <xsd:import namespace="48af5f5c-16db-4617-b456-65071b0f22d9"/>
@@ -13024,22 +13053,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{05E9192B-779A-41B7-B98B-742D8585BE22}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{273E048F-0434-43F1-B7EA-6A62301E1770}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2674F543-20A1-48ED-942E-D1CC3F8D6F42}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -13055,21 +13086,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{273E048F-0434-43F1-B7EA-6A62301E1770}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{05E9192B-779A-41B7-B98B-742D8585BE22}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>